--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C813C9-D61B-4B2C-ABD5-6C2668748A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC86406C-8E4D-4DA2-B5A2-432527E4F87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Database No.</t>
   </si>
@@ -79,6 +79,18 @@
   </si>
   <si>
     <t>File Download Link</t>
+  </si>
+  <si>
+    <t>Wang</t>
+  </si>
+  <si>
+    <t>Riglet</t>
+  </si>
+  <si>
+    <t>Vielemeyer</t>
+  </si>
+  <si>
+    <t>Jiwei</t>
   </si>
 </sst>
 </file>
@@ -396,8 +408,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="17.21875" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="15" max="15" width="14.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -453,6 +473,38 @@
       </c>
       <c r="R1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,12 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC86406C-8E4D-4DA2-B5A2-432527E4F87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A06526-9F45-4E6A-8FD6-B3C49D639038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Main" sheetId="1" r:id="rId1"/>
+    <sheet name="DB1" sheetId="2" r:id="rId2"/>
+    <sheet name="DB2" sheetId="3" r:id="rId3"/>
+    <sheet name="DB3" sheetId="4" r:id="rId4"/>
+    <sheet name="DB4" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -510,4 +514,40 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2FE9A5-01A0-4F7F-9995-C7997328C5F0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4089E73-0A1E-4CC4-ADF7-E4C53E7D0FFB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884DA4BC-4321-4FB1-9F19-14A0DC4F175F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDBD2763-5675-4526-80AA-7A66C9215AE0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A06526-9F45-4E6A-8FD6-B3C49D639038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7043B2D2-A96E-4BCB-B808-870DD4832902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>Database No.</t>
   </si>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t>Jiwei</t>
+  </si>
+  <si>
+    <t>xxx</t>
   </si>
 </sst>
 </file>
@@ -483,6 +486,9 @@
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
       <c r="C2" t="s">
         <v>19</v>
       </c>
@@ -491,6 +497,9 @@
       <c r="A3">
         <v>2</v>
       </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
       <c r="C3" t="s">
         <v>18</v>
       </c>
@@ -498,6 +507,9 @@
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7043B2D2-A96E-4BCB-B808-870DD4832902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E57EAC-E1DF-434F-99F8-84C6DBC86390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="23260" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>Database No.</t>
   </si>
@@ -416,17 +416,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="17.21875" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="17.1640625" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="15" max="15" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -482,7 +482,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -492,8 +492,11 @@
       <c r="C2" t="s">
         <v>19</v>
       </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -503,8 +506,11 @@
       <c r="C3" t="s">
         <v>18</v>
       </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -514,13 +520,19 @@
       <c r="C4" t="s">
         <v>20</v>
       </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -531,7 +543,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2FE9A5-01A0-4F7F-9995-C7997328C5F0}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -540,7 +552,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4089E73-0A1E-4CC4-ADF7-E4C53E7D0FFB}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -549,7 +561,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884DA4BC-4321-4FB1-9F19-14A0DC4F175F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -558,7 +570,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDBD2763-5675-4526-80AA-7A66C9215AE0}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E57EAC-E1DF-434F-99F8-84C6DBC86390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6AA1532-7CEB-4D4D-BB35-DD20C4316056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="23260" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>Database No.</t>
   </si>
@@ -98,6 +98,9 @@
   </si>
   <si>
     <t>xxx</t>
+  </si>
+  <si>
+    <t>xxxR</t>
   </si>
 </sst>
 </file>
@@ -532,7 +535,7 @@
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6AA1532-7CEB-4D4D-BB35-DD20C4316056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8734A13-E19E-9B4A-97F1-430384377432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="23260" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="23260" windowHeight="12460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
   <si>
     <t>Database No.</t>
   </si>
@@ -101,6 +101,21 @@
   </si>
   <si>
     <t>xxxR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Participant </t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Height</t>
   </si>
 </sst>
 </file>
@@ -426,7 +441,11 @@
     <col min="4" max="4" width="17.1640625" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="15" max="15" width="14.6640625" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="28.5" customWidth="1"/>
+    <col min="16" max="16" width="24.5" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="18" max="18" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
@@ -545,36 +564,176 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2FE9A5-01A0-4F7F-9995-C7997328C5F0}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4089E73-0A1E-4CC4-ADF7-E4C53E7D0FFB}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884DA4BC-4321-4FB1-9F19-14A0DC4F175F}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDBD2763-5675-4526-80AA-7A66C9215AE0}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="46">
   <si>
     <t xml:space="preserve">Database No.</t>
   </si>
@@ -80,22 +80,82 @@
     <t xml:space="preserve">File Download Link</t>
   </si>
   <si>
-    <t xml:space="preserve">xxx</t>
-  </si>
-  <si>
     <t xml:space="preserve">Riglet</t>
   </si>
   <si>
+    <t xml:space="preserve">3D motion analysis dataset of healthy young adult volunteers walking and running on overground and treadmill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overground and Treadmill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slow, comfortable &amp; fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://springernature.figshare.com/collections/3D_motion_analysis_dataset_of_healthy_young_adult_volunteers_walking_and_running_on_overground_and_treadmill/7056797?utm_source=chatgpt.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wang</t>
   </si>
   <si>
+    <t xml:space="preserve">Dataset of walking and running biomechanics with different step widths across different speeds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overground</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple speeds &amp; step widths</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nature.com/articles/s41597-025-05113-6</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vielemeyer</t>
   </si>
   <si>
+    <t xml:space="preserve">A Full-Body Motion Capture Gait Dataset of Healthy Young Adults Walking Ramps Up and Down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ramp with inclinations 0°, 7.5°, 10°, up &amp; down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preferred / self-selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nature.com/articles/s41597-025-06535-y#Bib1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jiwei</t>
   </si>
   <si>
-    <t xml:space="preserve">xxxR</t>
+    <t xml:space="preserve">K2MUSE: A human lower limb multimodal dataset under diverse conditions for facilitating rehabilitation robotics</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Threadmill, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Different inclines (0 LG, +/- 5, and +/- 10)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5 m/s, 1.0 m/s, and 1.5 m/s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://arxiv.org/abs/2504.14602</t>
   </si>
   <si>
     <t xml:space="preserve">Participant </t>
@@ -129,7 +189,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +211,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -195,8 +261,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -389,19 +463,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="33.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="23.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="28.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="24.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="29.91"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -460,60 +536,141 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="82.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="C2" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="D2" s="0" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F2" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>18</v>
-      </c>
       <c r="C3" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>23</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>18</v>
-      </c>
       <c r="C4" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>28</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="S5" s="0" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="S2" r:id="rId1" display="https://springernature.figshare.com/collections/3D_motion_analysis_dataset_of_healthy_young_adult_volunteers_walking_and_running_on_overground_and_treadmill/7056797?utm_source=chatgpt.com"/>
+    <hyperlink ref="S3" r:id="rId2" display="https://www.nature.com/articles/s41597-025-05113-6"/>
+    <hyperlink ref="S4" r:id="rId3" location="Bib1" display="https://www.nature.com/articles/s41597-025-06535-y#Bib1"/>
+    <hyperlink ref="S5" r:id="rId4" display="https://arxiv.org/abs/2504.14602"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -534,19 +691,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -575,19 +732,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -598,7 +755,7 @@
         <v>24</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>74</v>
@@ -615,7 +772,7 @@
         <v>24</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>72</v>
@@ -632,7 +789,7 @@
         <v>23</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>80</v>
@@ -649,7 +806,7 @@
         <v>23</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>60</v>
@@ -666,7 +823,7 @@
         <v>21</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>71</v>
@@ -683,7 +840,7 @@
         <v>20</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>65</v>
@@ -700,7 +857,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>72</v>
@@ -717,7 +874,7 @@
         <v>23</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>85</v>
@@ -734,7 +891,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>76</v>
@@ -751,7 +908,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>80</v>
@@ -768,7 +925,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>75</v>
@@ -785,7 +942,7 @@
         <v>24</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>80</v>
@@ -802,7 +959,7 @@
         <v>21</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>58</v>
@@ -832,19 +989,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -868,19 +1025,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="60">
   <si>
     <t xml:space="preserve">Database No.</t>
   </si>
@@ -107,6 +107,15 @@
     <t xml:space="preserve">Multiple speeds &amp; step widths</t>
   </si>
   <si>
+    <t xml:space="preserve">20–25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165-185 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55-85 kg</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://www.nature.com/articles/s41597-025-05113-6</t>
   </si>
   <si>
@@ -125,31 +134,34 @@
     <t xml:space="preserve">https://www.nature.com/articles/s41597-025-06535-y#Bib1</t>
   </si>
   <si>
+    <t xml:space="preserve">HAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GroundLink: A Dataset Unifying Human Body Movement and Ground Reaction Dynamics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5-2 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47-91 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://csr.bu.edu/groundlink/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://dl.acm.org/doi/epdf/10.1145/3610548.3618247</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jiwei</t>
   </si>
   <si>
     <t xml:space="preserve">K2MUSE: A human lower limb multimodal dataset under diverse conditions for facilitating rehabilitation robotics</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Threadmill, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Different inclines (0 LG, +/- 5, and +/- 10)</t>
-    </r>
+    <t xml:space="preserve">Threadmill, Different inclines (0 LG, +/- 5, and +/- 10)</t>
   </si>
   <si>
     <t xml:space="preserve">0.5 m/s, 1.0 m/s, and 1.5 m/s</t>
@@ -180,6 +192,18 @@
   </si>
   <si>
     <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight(kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Height(m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">na</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F</t>
   </si>
 </sst>
 </file>
@@ -189,7 +213,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,12 +235,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -261,17 +279,29 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -463,205 +493,286 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="33.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="23.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="28.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="24.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="29.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="33.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="36.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="23.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="28.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="24.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="29.91"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="0" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="82.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="I2" s="1" t="n">
+      <c r="I2" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="J2" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="K3" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="L3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>2026</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="E4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="1"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="S6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="1"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C8" s="1"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="S8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>2025</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="I5" s="1" t="n">
+      <c r="I9" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="S5" s="0" t="s">
-        <v>37</v>
+      <c r="S9" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +780,9 @@
     <hyperlink ref="S2" r:id="rId1" display="https://springernature.figshare.com/collections/3D_motion_analysis_dataset_of_healthy_young_adult_volunteers_walking_and_running_on_overground_and_treadmill/7056797?utm_source=chatgpt.com"/>
     <hyperlink ref="S3" r:id="rId2" display="https://www.nature.com/articles/s41597-025-05113-6"/>
     <hyperlink ref="S4" r:id="rId3" location="Bib1" display="https://www.nature.com/articles/s41597-025-06535-y#Bib1"/>
-    <hyperlink ref="S5" r:id="rId4" display="https://arxiv.org/abs/2504.14602"/>
+    <hyperlink ref="R5" r:id="rId4" display="https://csr.bu.edu/groundlink/"/>
+    <hyperlink ref="S5" r:id="rId5" display="https://dl.acm.org/doi/epdf/10.1145/3610548.3618247"/>
+    <hyperlink ref="S9" r:id="rId6" display="https://arxiv.org/abs/2504.14602"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -690,20 +803,20 @@
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>42</v>
+      <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -725,246 +838,246 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>44</v>
+      <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="0" t="n">
+      <c r="C2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="1" t="n">
         <v>74</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>175</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="C3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>72</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>172</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="C4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>178</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="0" t="n">
+      <c r="C5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>170</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="0" t="n">
+      <c r="C6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>71</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>171</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="0" t="n">
+      <c r="C7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>168</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="0" t="n">
+      <c r="C8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>72</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>176</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="C9" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="0" t="n">
+      <c r="C9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>181</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C10" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="0" t="n">
+      <c r="C10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>76</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>183</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="C11" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="0" t="n">
+      <c r="C11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <v>182</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="C12" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="0" t="n">
+      <c r="C12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <v>175</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C13" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="0" t="n">
+      <c r="C13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="1" t="n">
         <v>177</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C14" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="0" t="n">
+      <c r="C14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="1" t="n">
         <v>170</v>
       </c>
     </row>
@@ -988,20 +1101,20 @@
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>42</v>
+      <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1020,24 +1133,147 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.4"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>42</v>
+      <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>69.86</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>66.68</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>53.07</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>71.67</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>48.99</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>1.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shahk\TeamProject\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA21DC1A-BA5A-44DC-94F4-568EF74B087D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE48087E-5742-48A3-A5E8-BCCACA78E40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="67">
   <si>
     <t>Database No.</t>
   </si>
@@ -159,9 +159,6 @@
     <t>https://www.nature.com/articles/s41597-025-06535-y#Bib1</t>
   </si>
   <si>
-    <t>HAN</t>
-  </si>
-  <si>
     <t>GroundLink: A Dataset Unifying Human Body Movement and Ground Reaction Dynamics</t>
   </si>
   <si>
@@ -238,6 +235,12 @@
   </si>
   <si>
     <t>Height (mm)</t>
+  </si>
+  <si>
+    <t>Han</t>
+  </si>
+  <si>
+    <t>Grouvel</t>
   </si>
 </sst>
 </file>
@@ -487,26 +490,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S10"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.81640625" customWidth="1"/>
-    <col min="2" max="2" width="17.81640625" customWidth="1"/>
-    <col min="4" max="4" width="14.36328125" customWidth="1"/>
-    <col min="5" max="5" width="33.90625" customWidth="1"/>
+    <col min="1" max="1" width="5.77734375" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" customWidth="1"/>
+    <col min="5" max="5" width="33.88671875" customWidth="1"/>
     <col min="6" max="6" width="36" customWidth="1"/>
-    <col min="7" max="7" width="23.6328125" customWidth="1"/>
-    <col min="12" max="12" width="14.36328125" customWidth="1"/>
-    <col min="13" max="13" width="12.6328125" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
     <col min="14" max="14" width="20" customWidth="1"/>
-    <col min="15" max="15" width="28.453125" customWidth="1"/>
-    <col min="16" max="16" width="24.54296875" customWidth="1"/>
+    <col min="15" max="15" width="28.44140625" customWidth="1"/>
+    <col min="16" max="16" width="24.5546875" customWidth="1"/>
     <col min="17" max="17" width="20" customWidth="1"/>
     <col min="18" max="18" width="13" customWidth="1"/>
-    <col min="19" max="19" width="29.90625" customWidth="1"/>
+    <col min="19" max="19" width="29.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -562,7 +565,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="82.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -603,7 +606,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -644,50 +647,33 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4">
-        <v>2026</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="1">
-        <v>13</v>
-      </c>
-      <c r="I4" s="1">
-        <v>5</v>
-      </c>
-      <c r="J4" s="1">
-        <v>8</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="S4" s="1"/>
+    </row>
+    <row r="5" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D5">
         <v>2023</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>28</v>
@@ -705,31 +691,22 @@
         <v>3</v>
       </c>
       <c r="K5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" t="s">
         <v>41</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>42</v>
       </c>
-      <c r="M5" t="s">
+      <c r="R5" t="s">
         <v>43</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="S5" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="S6" s="1"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -738,7 +715,7 @@
       <c r="J7" s="1"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -747,21 +724,21 @@
       <c r="J8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:19" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="H9" s="1">
         <v>30</v>
@@ -773,14 +750,43 @@
         <v>20</v>
       </c>
       <c r="S9" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10">
+        <v>2026</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="1">
+        <v>13</v>
+      </c>
+      <c r="I10" s="1">
+        <v>5</v>
+      </c>
+      <c r="J10" s="1">
+        <v>8</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="S2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="S3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="S4" r:id="rId3" location="Bib1" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="S10" r:id="rId3" location="Bib1" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="R5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="S5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="S9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
@@ -793,31 +799,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" customWidth="1"/>
-    <col min="4" max="4" width="14.08984375" customWidth="1"/>
-    <col min="5" max="5" width="12.26953125" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" t="s">
         <v>51</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>52</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>53</v>
       </c>
-      <c r="D1" t="s">
-        <v>54</v>
-      </c>
       <c r="E1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <f t="shared" ref="A2:A31" si="0">ROW(A1)</f>
         <v>1</v>
@@ -826,7 +832,7 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D2">
         <v>53</v>
@@ -835,7 +841,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -844,7 +850,7 @@
         <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D3">
         <v>58</v>
@@ -853,7 +859,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -862,7 +868,7 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D4">
         <v>61</v>
@@ -871,7 +877,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -880,7 +886,7 @@
         <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D5">
         <v>81</v>
@@ -889,7 +895,7 @@
         <v>1870</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -898,7 +904,7 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D6">
         <v>63</v>
@@ -907,7 +913,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -916,7 +922,7 @@
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D7">
         <v>63</v>
@@ -925,7 +931,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -934,7 +940,7 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D8">
         <v>79</v>
@@ -943,7 +949,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -952,7 +958,7 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -961,7 +967,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -970,7 +976,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D10">
         <v>71</v>
@@ -979,7 +985,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -988,7 +994,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D11">
         <v>74</v>
@@ -997,7 +1003,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1006,7 +1012,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D12">
         <v>56</v>
@@ -1015,7 +1021,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1024,7 +1030,7 @@
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13">
         <v>48</v>
@@ -1033,7 +1039,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1042,7 +1048,7 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14">
         <v>74</v>
@@ -1051,7 +1057,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1060,7 +1066,7 @@
         <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15">
         <v>55</v>
@@ -1069,7 +1075,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1078,7 +1084,7 @@
         <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16">
         <v>85</v>
@@ -1087,7 +1093,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1096,7 +1102,7 @@
         <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D17">
         <v>73</v>
@@ -1105,7 +1111,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1114,7 +1120,7 @@
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D18">
         <v>77</v>
@@ -1123,7 +1129,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1132,7 +1138,7 @@
         <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19">
         <v>62</v>
@@ -1141,7 +1147,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1150,7 +1156,7 @@
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20">
         <v>79</v>
@@ -1159,7 +1165,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1168,7 +1174,7 @@
         <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D21">
         <v>76</v>
@@ -1177,7 +1183,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1186,7 +1192,7 @@
         <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22">
         <v>78</v>
@@ -1195,7 +1201,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -1204,7 +1210,7 @@
         <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D23">
         <v>65</v>
@@ -1213,7 +1219,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1222,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D24">
         <v>56</v>
@@ -1231,7 +1237,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -1240,7 +1246,7 @@
         <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D25">
         <v>56</v>
@@ -1249,7 +1255,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -1258,7 +1264,7 @@
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D26">
         <v>78</v>
@@ -1267,7 +1273,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -1276,7 +1282,7 @@
         <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D27">
         <v>71</v>
@@ -1285,7 +1291,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -1294,7 +1300,7 @@
         <v>21</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D28">
         <v>53</v>
@@ -1303,7 +1309,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -1312,7 +1318,7 @@
         <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D29">
         <v>71</v>
@@ -1321,7 +1327,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -1330,7 +1336,7 @@
         <v>31</v>
       </c>
       <c r="C30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D30">
         <v>71</v>
@@ -1339,7 +1345,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1348,7 +1354,7 @@
         <v>38</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D31">
         <v>92</v>
@@ -1366,31 +1372,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.81640625" customWidth="1"/>
-    <col min="4" max="4" width="14.08984375" customWidth="1"/>
-    <col min="5" max="5" width="16.453125" customWidth="1"/>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>59</v>
       </c>
-      <c r="E1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1398,7 +1404,7 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D2">
         <v>74</v>
@@ -1407,7 +1413,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1415,7 +1421,7 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D3">
         <v>72</v>
@@ -1424,7 +1430,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1432,7 +1438,7 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D4">
         <v>80</v>
@@ -1441,7 +1447,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1449,7 +1455,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D5">
         <v>60</v>
@@ -1458,7 +1464,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1466,7 +1472,7 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D6">
         <v>71</v>
@@ -1475,7 +1481,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1483,7 +1489,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D7">
         <v>65</v>
@@ -1492,7 +1498,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1500,7 +1506,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D8">
         <v>72</v>
@@ -1509,7 +1515,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1517,7 +1523,7 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D9">
         <v>85</v>
@@ -1526,7 +1532,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1534,7 +1540,7 @@
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D10">
         <v>76</v>
@@ -1543,7 +1549,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1551,7 +1557,7 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D11">
         <v>80</v>
@@ -1560,7 +1566,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1568,7 +1574,7 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D12">
         <v>75</v>
@@ -1577,7 +1583,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1585,7 +1591,7 @@
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13">
         <v>80</v>
@@ -1594,7 +1600,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1602,7 +1608,7 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14">
         <v>58</v>
@@ -1620,23 +1626,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" t="s">
         <v>52</v>
       </c>
-      <c r="C1" t="s">
-        <v>53</v>
-      </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1648,38 +1654,38 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.6328125" customWidth="1"/>
-    <col min="4" max="4" width="11.36328125" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" t="s">
         <v>52</v>
       </c>
-      <c r="C1" t="s">
-        <v>53</v>
-      </c>
       <c r="D1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" t="s">
         <v>62</v>
       </c>
-      <c r="E1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D2">
         <v>69.86</v>
@@ -1688,15 +1694,15 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D3">
         <v>66.680000000000007</v>
@@ -1705,15 +1711,15 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D4">
         <v>53.07</v>
@@ -1722,15 +1728,15 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D5">
         <v>71.67</v>
@@ -1739,15 +1745,15 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D6">
         <v>90.7</v>
@@ -1756,15 +1762,15 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D7">
         <v>48.99</v>
@@ -1773,15 +1779,15 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D8">
         <v>63.96</v>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE48087E-5742-48A3-A5E8-BCCACA78E40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8BC072-1C99-4149-884D-778F18DA6CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="71">
   <si>
     <t>Database No.</t>
   </si>
@@ -216,12 +216,6 @@
     <t xml:space="preserve">Participant </t>
   </si>
   <si>
-    <t>Weight(KG)</t>
-  </si>
-  <si>
-    <t>Height(CM)</t>
-  </si>
-  <si>
     <t>Weight</t>
   </si>
   <si>
@@ -241,6 +235,24 @@
   </si>
   <si>
     <t>Grouvel</t>
+  </si>
+  <si>
+    <t>Height (cm)</t>
+  </si>
+  <si>
+    <t>Calib pose</t>
+  </si>
+  <si>
+    <t>Walk trials (files)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usable Walk trials </t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Duration per trials</t>
   </si>
 </sst>
 </file>
@@ -652,7 +664,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -667,7 +679,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D5">
         <v>2023</v>
@@ -798,15 +810,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.77734375" customWidth="1"/>
     <col min="4" max="4" width="14.109375" customWidth="1"/>
     <col min="5" max="5" width="12.21875" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" customWidth="1"/>
+    <col min="10" max="10" width="16.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>50</v>
       </c>
@@ -820,10 +836,22 @@
         <v>53</v>
       </c>
       <c r="E1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+      <c r="G1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <f t="shared" ref="A2:A31" si="0">ROW(A1)</f>
         <v>1</v>
@@ -841,7 +869,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -859,7 +887,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -877,7 +905,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -895,7 +923,7 @@
         <v>1870</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -913,7 +941,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -931,7 +959,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -949,7 +977,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -967,7 +995,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -985,7 +1013,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1003,7 +1031,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1021,7 +1049,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1039,7 +1067,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1057,7 +1085,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1075,7 +1103,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1371,15 +1399,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" customWidth="1"/>
+    <col min="9" max="9" width="16.88671875" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>57</v>
       </c>
@@ -1390,13 +1423,25 @@
         <v>52</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+      <c r="G1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1412,8 +1457,14 @@
       <c r="E2">
         <v>175</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1429,8 +1480,14 @@
       <c r="E3">
         <v>172</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1446,8 +1503,14 @@
       <c r="E4">
         <v>178</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1463,8 +1526,14 @@
       <c r="E5">
         <v>170</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1480,8 +1549,14 @@
       <c r="E6">
         <v>171</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1497,8 +1572,14 @@
       <c r="E7">
         <v>168</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1514,8 +1595,14 @@
       <c r="E8">
         <v>176</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1531,8 +1618,14 @@
       <c r="E9">
         <v>181</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1548,8 +1641,14 @@
       <c r="E10">
         <v>183</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1565,8 +1664,14 @@
       <c r="E11">
         <v>182</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1582,8 +1687,14 @@
       <c r="E12">
         <v>175</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1599,8 +1710,14 @@
       <c r="E13">
         <v>177</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1615,6 +1732,12 @@
       </c>
       <c r="E14">
         <v>170</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1625,10 +1748,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>57</v>
       </c>
@@ -1639,10 +1766,132 @@
         <v>52</v>
       </c>
       <c r="D1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E1" t="s">
         <v>54</v>
+      </c>
+      <c r="G1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1653,14 +1902,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>57</v>
       </c>
@@ -1671,18 +1924,30 @@
         <v>52</v>
       </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+      <c r="G1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
         <v>55</v>
@@ -1694,12 +1959,12 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
         <v>56</v>
@@ -1711,12 +1976,12 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
         <v>55</v>
@@ -1728,12 +1993,12 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
         <v>56</v>
@@ -1745,12 +2010,12 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
         <v>56</v>
@@ -1762,12 +2027,12 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
         <v>55</v>
@@ -1779,12 +2044,12 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
         <v>55</v>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8BC072-1C99-4149-884D-778F18DA6CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33DF974-D777-4589-91CA-FAFFA6236BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="70">
   <si>
     <t>Database No.</t>
   </si>
@@ -247,9 +247,6 @@
   </si>
   <si>
     <t xml:space="preserve">Usable Walk trials </t>
-  </si>
-  <si>
-    <t>x</t>
   </si>
   <si>
     <t>Duration per trials</t>
@@ -502,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.77734375" customWidth="1"/>
@@ -577,45 +574,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2">
-        <v>2024</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="1">
-        <v>30</v>
-      </c>
-      <c r="I2" s="1">
-        <v>14</v>
-      </c>
-      <c r="J2" s="1">
-        <v>16</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
@@ -794,9 +755,47 @@
         <v>38</v>
       </c>
     </row>
+    <row r="11" spans="1:19" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11">
+        <v>2024</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="1">
+        <v>30</v>
+      </c>
+      <c r="I11" s="1">
+        <v>14</v>
+      </c>
+      <c r="J11" s="1">
+        <v>16</v>
+      </c>
+      <c r="K11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="S11" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="S3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="S10" r:id="rId3" location="Bib1" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="R5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
@@ -810,7 +809,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.77734375" customWidth="1"/>
@@ -848,547 +847,7 @@
         <v>68</v>
       </c>
       <c r="J1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <f t="shared" ref="A2:A31" si="0">ROW(A1)</f>
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2">
-        <v>53</v>
-      </c>
-      <c r="E2">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>36</v>
-      </c>
-      <c r="C3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3">
-        <v>58</v>
-      </c>
-      <c r="E3">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4">
-        <v>61</v>
-      </c>
-      <c r="E4">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5">
-        <v>81</v>
-      </c>
-      <c r="E5">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6">
-        <v>63</v>
-      </c>
-      <c r="E6">
-        <v>1640</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7">
-        <v>63</v>
-      </c>
-      <c r="E7">
-        <v>1830</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8">
-        <v>79</v>
-      </c>
-      <c r="E8">
-        <v>1840</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9">
-        <v>60</v>
-      </c>
-      <c r="E9">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10">
-        <v>71</v>
-      </c>
-      <c r="E10">
-        <v>1820</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11">
-        <v>74</v>
-      </c>
-      <c r="E11">
-        <v>1740</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12">
-        <v>56</v>
-      </c>
-      <c r="E12">
-        <v>1630</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13">
-        <v>48</v>
-      </c>
-      <c r="E13">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14">
-        <v>74</v>
-      </c>
-      <c r="E14">
-        <v>1760</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>24</v>
-      </c>
-      <c r="C15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15">
-        <v>55</v>
-      </c>
-      <c r="E15">
-        <v>1680</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>41</v>
-      </c>
-      <c r="C16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16">
-        <v>85</v>
-      </c>
-      <c r="E16">
-        <v>1820</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>26</v>
-      </c>
-      <c r="C17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17">
-        <v>73</v>
-      </c>
-      <c r="E17">
-        <v>1780</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B18">
-        <v>26</v>
-      </c>
-      <c r="C18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18">
-        <v>77</v>
-      </c>
-      <c r="E18">
-        <v>1840</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B19">
-        <v>21</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19">
-        <v>62</v>
-      </c>
-      <c r="E19">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B20">
-        <v>23</v>
-      </c>
-      <c r="C20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20">
-        <v>79</v>
-      </c>
-      <c r="E20">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B21">
-        <v>30</v>
-      </c>
-      <c r="C21" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21">
-        <v>76</v>
-      </c>
-      <c r="E21">
-        <v>1820</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B22">
-        <v>25</v>
-      </c>
-      <c r="C22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22">
-        <v>78</v>
-      </c>
-      <c r="E22">
-        <v>1630</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="B23">
-        <v>25</v>
-      </c>
-      <c r="C23" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23">
-        <v>65</v>
-      </c>
-      <c r="E23">
-        <v>1770</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="B24">
-        <v>30</v>
-      </c>
-      <c r="C24" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24">
-        <v>56</v>
-      </c>
-      <c r="E24">
-        <v>1610</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="B25">
-        <v>21</v>
-      </c>
-      <c r="C25" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25">
-        <v>56</v>
-      </c>
-      <c r="E25">
-        <v>1630</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="B26">
-        <v>25</v>
-      </c>
-      <c r="C26" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26">
-        <v>78</v>
-      </c>
-      <c r="E26">
-        <v>1880</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B27">
-        <v>30</v>
-      </c>
-      <c r="C27" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27">
-        <v>71</v>
-      </c>
-      <c r="E27">
-        <v>1690</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B28">
-        <v>21</v>
-      </c>
-      <c r="C28" t="s">
-        <v>55</v>
-      </c>
-      <c r="D28">
-        <v>53</v>
-      </c>
-      <c r="E28">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="B29">
-        <v>35</v>
-      </c>
-      <c r="C29" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29">
-        <v>71</v>
-      </c>
-      <c r="E29">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="B30">
-        <v>31</v>
-      </c>
-      <c r="C30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30">
-        <v>71</v>
-      </c>
-      <c r="E30">
-        <v>1650</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="B31">
-        <v>38</v>
-      </c>
-      <c r="C31" t="s">
-        <v>56</v>
-      </c>
-      <c r="D31">
-        <v>92</v>
-      </c>
-      <c r="E31">
-        <v>1830</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1438,7 +897,7 @@
         <v>68</v>
       </c>
       <c r="J1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -1781,7 +1240,7 @@
         <v>68</v>
       </c>
       <c r="J1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -1809,12 +1268,6 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
-      </c>
-      <c r="G4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -1939,7 +1392,7 @@
         <v>68</v>
       </c>
       <c r="J1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -1957,6 +1410,9 @@
       </c>
       <c r="E2">
         <v>1.68</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -1975,6 +1431,9 @@
       <c r="E3">
         <v>1.7</v>
       </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -1991,6 +1450,9 @@
       </c>
       <c r="E4">
         <v>1.59</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -2009,6 +1471,9 @@
       <c r="E5">
         <v>1.82</v>
       </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -2026,6 +1491,9 @@
       <c r="E6">
         <v>1.95</v>
       </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -2043,6 +1511,9 @@
       <c r="E7">
         <v>1.53</v>
       </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -2059,6 +1530,9 @@
       </c>
       <c r="E8">
         <v>1.75</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33DF974-D777-4589-91CA-FAFFA6236BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6B868E-5AA6-4169-B265-1D253F8CC7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1251,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -1262,13 +1262,19 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>12</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -1278,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -1289,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1300,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -1311,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -1322,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -1333,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -1344,7 +1350,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D0001A-200C-4C9A-BE47-B918FFBC54A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88D27DC-FC7F-430F-B51B-66DAE71764CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="77">
   <si>
     <t>Database No.</t>
   </si>
@@ -237,24 +237,15 @@
     <t>Weight (kg)</t>
   </si>
   <si>
-    <t>Height (mm)</t>
-  </si>
-  <si>
     <t>Calib pose</t>
   </si>
   <si>
     <t>Walk trials (files)</t>
   </si>
   <si>
-    <t>Duration per trials</t>
-  </si>
-  <si>
     <t xml:space="preserve">Participant </t>
   </si>
   <si>
-    <t>Height (cm)</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
@@ -270,9 +261,6 @@
     <t xml:space="preserve">Usable trials </t>
   </si>
   <si>
-    <t>Walk trials</t>
-  </si>
-  <si>
     <t>Duration per trials (s)</t>
   </si>
   <si>
@@ -280,9 +268,6 @@
   </si>
   <si>
     <t>Height (m)</t>
-  </si>
-  <si>
-    <t>Participant</t>
   </si>
   <si>
     <t>1:3 (No ID)</t>
@@ -908,21 +893,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" customWidth="1"/>
-    <col min="9" max="9" width="16.33203125" customWidth="1"/>
-    <col min="10" max="10" width="16.77734375" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" customWidth="1"/>
+    <col min="4" max="5" width="8.77734375" customWidth="1"/>
+    <col min="7" max="10" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
         <v>60</v>
@@ -934,19 +915,22 @@
         <v>62</v>
       </c>
       <c r="E1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" t="s">
         <v>63</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>64</v>
       </c>
-      <c r="H1" t="s">
-        <v>74</v>
-      </c>
       <c r="I1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J1" t="s">
-        <v>66</v>
+        <v>71</v>
+      </c>
+      <c r="K1" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -957,22 +941,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" customWidth="1"/>
-    <col min="9" max="9" width="16.88671875" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" customWidth="1"/>
+    <col min="4" max="10" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
         <v>60</v>
@@ -984,22 +962,25 @@
         <v>62</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" t="s">
         <v>64</v>
       </c>
-      <c r="H1" t="s">
-        <v>65</v>
-      </c>
       <c r="I1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+      <c r="K1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1007,7 +988,7 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D2">
         <v>74</v>
@@ -1021,8 +1002,11 @@
       <c r="H2">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1030,7 +1014,7 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D3">
         <v>72</v>
@@ -1044,8 +1028,11 @@
       <c r="H3">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1053,7 +1040,7 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D4">
         <v>80</v>
@@ -1067,8 +1054,11 @@
       <c r="H4">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1076,7 +1066,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D5">
         <v>60</v>
@@ -1091,7 +1081,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1099,7 +1089,7 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D6">
         <v>71</v>
@@ -1114,7 +1104,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1122,7 +1112,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D7">
         <v>65</v>
@@ -1137,7 +1127,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1145,7 +1135,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D8">
         <v>72</v>
@@ -1160,7 +1150,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1168,7 +1158,7 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D9">
         <v>85</v>
@@ -1183,7 +1173,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1191,7 +1181,7 @@
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D10">
         <v>76</v>
@@ -1206,7 +1196,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1214,7 +1204,7 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D11">
         <v>80</v>
@@ -1229,7 +1219,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1237,7 +1227,7 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D12">
         <v>75</v>
@@ -1252,7 +1242,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1260,7 +1250,7 @@
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D13">
         <v>80</v>
@@ -1275,7 +1265,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1283,7 +1273,7 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D14">
         <v>58</v>
@@ -1314,7 +1304,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
         <v>60</v>
@@ -1326,22 +1316,22 @@
         <v>62</v>
       </c>
       <c r="E1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" t="s">
         <v>64</v>
       </c>
-      <c r="H1" t="s">
-        <v>65</v>
-      </c>
       <c r="I1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -1349,25 +1339,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
         <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -1375,25 +1362,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
         <v>16</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -1401,25 +1385,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
         <v>12</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -1427,16 +1408,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1450,16 +1431,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1473,16 +1454,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1496,16 +1477,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1519,16 +1500,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1542,16 +1523,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1565,16 +1546,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1601,7 +1582,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
         <v>60</v>
@@ -1613,22 +1594,22 @@
         <v>62</v>
       </c>
       <c r="E1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" t="s">
         <v>64</v>
       </c>
-      <c r="H1" t="s">
-        <v>65</v>
-      </c>
       <c r="I1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -1636,10 +1617,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D2">
         <v>69.86</v>
@@ -1651,7 +1632,7 @@
         <v>3</v>
       </c>
       <c r="K2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -1659,10 +1640,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D3">
         <v>66.680000000000007</v>
@@ -1674,7 +1655,7 @@
         <v>4</v>
       </c>
       <c r="K3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -1682,10 +1663,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D4">
         <v>53.07</v>
@@ -1702,10 +1683,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D5">
         <v>71.67</v>
@@ -1722,10 +1703,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D6">
         <v>90.7</v>
@@ -1742,10 +1723,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D7">
         <v>48.99</v>
@@ -1762,10 +1743,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D8">
         <v>63.96</v>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC68D7D-1D9E-6049-977F-E8711D01C835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView xWindow="160" yWindow="920" windowWidth="29080" windowHeight="18040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Main" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="DB1" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="DB2" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="DB3" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="DB4" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Main" sheetId="1" r:id="rId1"/>
+    <sheet name="DB1" sheetId="2" r:id="rId2"/>
+    <sheet name="DB2" sheetId="3" r:id="rId3"/>
+    <sheet name="DB3" sheetId="4" r:id="rId4"/>
+    <sheet name="DB4" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -24,105 +29,105 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="78">
-  <si>
-    <t xml:space="preserve">Database No.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Related Paper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Authors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year of Publication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Database Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walking Type (overground or threadmill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Participants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Female P.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Male P.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Height range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weight range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geographical Region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trials per Participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No. Markers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No. Force Plates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File Download Link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dataset of walking and running biomechanics with different step widths across different speeds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overground</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multiple speeds &amp; step widths</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20–25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165-185 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55-85 kg</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="79">
+  <si>
+    <t>Database No.</t>
+  </si>
+  <si>
+    <t>Related Paper</t>
+  </si>
+  <si>
+    <t>Authors</t>
+  </si>
+  <si>
+    <t>Year of Publication</t>
+  </si>
+  <si>
+    <t>Database Name</t>
+  </si>
+  <si>
+    <t>Walking Type (overground or threadmill)</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>Participants</t>
+  </si>
+  <si>
+    <t>Female P.</t>
+  </si>
+  <si>
+    <t>Male P.</t>
+  </si>
+  <si>
+    <t>Age range</t>
+  </si>
+  <si>
+    <t>Height range</t>
+  </si>
+  <si>
+    <t>Weight range</t>
+  </si>
+  <si>
+    <t>Geographical Region</t>
+  </si>
+  <si>
+    <t>Trials per Participant</t>
+  </si>
+  <si>
+    <t>No. Markers</t>
+  </si>
+  <si>
+    <t>No. Force Plates</t>
+  </si>
+  <si>
+    <t>File Download Link</t>
+  </si>
+  <si>
+    <t>Wang</t>
+  </si>
+  <si>
+    <t>Dataset of walking and running biomechanics with different step widths across different speeds</t>
+  </si>
+  <si>
+    <t>Overground</t>
+  </si>
+  <si>
+    <t>Multiple speeds &amp; step widths</t>
+  </si>
+  <si>
+    <t>20–25</t>
+  </si>
+  <si>
+    <t>165-185 cm</t>
+  </si>
+  <si>
+    <t>55-85 kg</t>
   </si>
   <si>
     <t xml:space="preserve">38 cutaneous reflective markers </t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.nature.com/articles/s41597-025-05113-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grouvel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A dataset of asymptomatic human gait and movements obtained from markers, IMUs, insoles and force plates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multiple speeds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7 ± 6.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74 ± 0.06 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.0 ± 13.9 kg</t>
+    <t>https://www.nature.com/articles/s41597-025-05113-6</t>
+  </si>
+  <si>
+    <t>Grouvel</t>
+  </si>
+  <si>
+    <t>A dataset of asymptomatic human gait and movements obtained from markers, IMUs, insoles and force plates</t>
+  </si>
+  <si>
+    <t>Multiple speeds</t>
+  </si>
+  <si>
+    <t>29.7 ± 6.4</t>
+  </si>
+  <si>
+    <t>1.74 ± 0.06 m</t>
+  </si>
+  <si>
+    <t>68.0 ± 13.9 kg</t>
   </si>
   <si>
     <r>
@@ -143,171 +148,156 @@
         <family val="1"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">37 cutaneous markers, 32 cluster markers</t>
+      <t>37 cutaneous markers, 32 cluster markers</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">https://www.nature.com/articles/s41597-023-02077-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Han</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GroundLink: A Dataset Unifying Human Body Movement and Ground Reaction Dynamics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preferred / self-selected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18-32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5-2 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47-91 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://csr.bu.edu/groundlink/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://dl.acm.org/doi/epdf/10.1145/3610548.3618247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jiwei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K2MUSE: A human lower limb multimodal dataset under diverse conditions for facilitating rehabilitation robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threadmill, Different inclines (0 LG, +/- 5, and +/- 10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5 m/s, 1.0 m/s, and 1.5 m/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://arxiv.org/abs/2504.14602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vielemeyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Full-Body Motion Capture Gait Dataset of Healthy Young Adults Walking Ramps Up and Down</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ramp with inclinations 0°, 7.5°, 10°, up &amp; down</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.nature.com/articles/s41597-025-06535-y#Bib1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riglet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3D motion analysis dataset of healthy young adult volunteers walking and running on overground and treadmill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overground and Treadmill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slow, comfortable &amp; fast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 -41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73 ± 0.09 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.2 ± 11.1 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://springernature.figshare.com/collections/3D_motion_analysis_dataset_of_healthy_young_adult_volunteers_walking_and_running_on_overground_and_treadmill/7056797?utm_source=chatgpt.com</t>
+    <t>https://www.nature.com/articles/s41597-023-02077-3</t>
+  </si>
+  <si>
+    <t>Han</t>
+  </si>
+  <si>
+    <t>GroundLink: A Dataset Unifying Human Body Movement and Ground Reaction Dynamics</t>
+  </si>
+  <si>
+    <t>Preferred / self-selected</t>
+  </si>
+  <si>
+    <t>18-32</t>
+  </si>
+  <si>
+    <t>1.5-2 m</t>
+  </si>
+  <si>
+    <t>47-91 kg</t>
+  </si>
+  <si>
+    <t>https://csr.bu.edu/groundlink/</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/epdf/10.1145/3610548.3618247</t>
+  </si>
+  <si>
+    <t>Jiwei</t>
+  </si>
+  <si>
+    <t>K2MUSE: A human lower limb multimodal dataset under diverse conditions for facilitating rehabilitation robotics</t>
+  </si>
+  <si>
+    <t>Threadmill, Different inclines (0 LG, +/- 5, and +/- 10)</t>
+  </si>
+  <si>
+    <t>0.5 m/s, 1.0 m/s, and 1.5 m/s</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2504.14602</t>
+  </si>
+  <si>
+    <t>Vielemeyer</t>
+  </si>
+  <si>
+    <t>A Full-Body Motion Capture Gait Dataset of Healthy Young Adults Walking Ramps Up and Down</t>
+  </si>
+  <si>
+    <t>ramp with inclinations 0°, 7.5°, 10°, up &amp; down</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41597-025-06535-y#Bib1</t>
+  </si>
+  <si>
+    <t>Riglet</t>
+  </si>
+  <si>
+    <t>3D motion analysis dataset of healthy young adult volunteers walking and running on overground and treadmill</t>
+  </si>
+  <si>
+    <t>Overground and Treadmill</t>
+  </si>
+  <si>
+    <t>Slow, comfortable &amp; fast</t>
+  </si>
+  <si>
+    <t>21 -41</t>
+  </si>
+  <si>
+    <t>1.73 ± 0.09 m</t>
+  </si>
+  <si>
+    <t>68.2 ± 11.1 kg</t>
+  </si>
+  <si>
+    <t>https://springernature.figshare.com/collections/3D_motion_analysis_dataset_of_healthy_young_adult_volunteers_walking_and_running_on_overground_and_treadmill/7056797?utm_source=chatgpt.com</t>
   </si>
   <si>
     <t xml:space="preserve">Participant </t>
   </si>
   <si>
-    <t xml:space="preserve">Age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weight (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Height (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calib pose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walk trials (files)</t>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Weight (kg)</t>
+  </si>
+  <si>
+    <t>Height (m)</t>
+  </si>
+  <si>
+    <t>Calib pose</t>
+  </si>
+  <si>
+    <t>Walk trials (files)</t>
   </si>
   <si>
     <t xml:space="preserve">Usable trials </t>
   </si>
   <si>
-    <t xml:space="preserve">Duration per trials (s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wrong trials (reason)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-all ('LoadingError')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T04_Cal_relabeled (missing GRF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">na</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1:3 (No ID)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (First half No ID)</t>
+    <t>Duration per trials (s)</t>
+  </si>
+  <si>
+    <t>Wrong trials (reason)</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>3-all ('LoadingError')</t>
+  </si>
+  <si>
+    <t>T04_Cal_relabeled (missing GRF)</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>1:3 (No ID)</t>
+  </si>
+  <si>
+    <t>4 (First half No ID)</t>
+  </si>
+  <si>
+    <t>T02_-130 (MarkerFitterError)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="12"/>
@@ -323,6 +313,13 @@
       <family val="1"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -333,7 +330,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -341,118 +338,84 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Normal 2" xfId="20"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -484,7 +447,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -508,7 +471,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -568,137 +531,136 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S11"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="33.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="23.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="12.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="28.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="24.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="29.88"/>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" customWidth="1"/>
+    <col min="5" max="5" width="33.83203125" customWidth="1"/>
+    <col min="6" max="6" width="36" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" customWidth="1"/>
+    <col min="8" max="8" width="13.5" customWidth="1"/>
+    <col min="10" max="10" width="9.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="28.5" customWidth="1"/>
+    <col min="16" max="16" width="24.5" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="18" max="18" width="13" customWidth="1"/>
+    <col min="19" max="19" width="29.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="0" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+    <row r="3" spans="1:19" ht="48" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3">
         <v>13</v>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="I3" s="1">
         <v>0</v>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" s="1">
         <v>13</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" t="s">
         <v>24</v>
       </c>
       <c r="P3" s="1" t="s">
@@ -708,41 +670,41 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+    <row r="4" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4">
         <v>2023</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4" s="1">
         <v>10</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="I4" s="1">
         <v>4</v>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="J4" s="1">
         <v>6</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="P4" s="1" t="s">
@@ -752,14 +714,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+    <row r="5" spans="1:19" ht="48" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5">
         <v>2023</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -771,35 +733,35 @@
       <c r="G5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="1">
         <v>7</v>
       </c>
-      <c r="I5" s="1" t="n">
+      <c r="I5" s="1">
         <v>4</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="1">
         <v>3</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" t="s">
         <v>39</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" t="s">
         <v>40</v>
       </c>
-      <c r="P5" s="1" t="n">
+      <c r="P5" s="1">
         <v>96</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="R5" t="s">
         <v>41</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -808,7 +770,7 @@
       <c r="J7" s="1"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -817,11 +779,11 @@
       <c r="J8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="0" t="s">
+    <row r="9" spans="1:19" ht="48" x14ac:dyDescent="0.2">
+      <c r="C9" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -833,24 +795,24 @@
       <c r="G9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="H9" s="1">
         <v>30</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="I9" s="1">
         <v>10</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="1">
         <v>20</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="S9" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="0" t="s">
+    <row r="10" spans="1:19" ht="48" x14ac:dyDescent="0.2">
+      <c r="C10" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10">
         <v>2026</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -862,51 +824,51 @@
       <c r="G10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="H10" s="1">
         <v>13</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="I10" s="1">
         <v>5</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="1">
         <v>8</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="82.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C11" s="0" t="s">
+    <row r="11" spans="1:19" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C11" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11">
         <v>2024</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="H11" s="1">
         <v>30</v>
       </c>
-      <c r="I11" s="1" t="n">
+      <c r="I11" s="1">
         <v>14</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="1">
         <v>16</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" t="s">
         <v>56</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="M11" s="3" t="s">
         <v>58</v>
       </c>
       <c r="S11" s="1" t="s">
@@ -915,923 +877,889 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S3" r:id="rId1" display="https://www.nature.com/articles/s41597-025-05113-6"/>
-    <hyperlink ref="S4" r:id="rId2" display="https://www.nature.com/articles/s41597-023-02077-3"/>
-    <hyperlink ref="R5" r:id="rId3" display="https://csr.bu.edu/groundlink/"/>
-    <hyperlink ref="S5" r:id="rId4" display="https://dl.acm.org/doi/epdf/10.1145/3610548.3618247"/>
-    <hyperlink ref="S9" r:id="rId5" display="https://arxiv.org/abs/2504.14602"/>
-    <hyperlink ref="S10" r:id="rId6" location="Bib1" display="https://www.nature.com/articles/s41597-025-06535-y#Bib1"/>
-    <hyperlink ref="S11" r:id="rId7" display="https://springernature.figshare.com/collections/3D_motion_analysis_dataset_of_healthy_young_adult_volunteers_walking_and_running_on_overground_and_treadmill/7056797?utm_source=chatgpt.com"/>
+    <hyperlink ref="S3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="S4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="R5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="S5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="S9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="S10" r:id="rId6" location="Bib1" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="S11" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
   </hyperlinks>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>69</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="28.38"/>
+    <col min="11" max="11" width="28.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2">
         <v>24</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2">
         <v>74</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2">
         <v>175</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2">
         <v>21</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3">
         <v>24</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3">
         <v>72</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3">
         <v>172</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3">
         <v>23</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4">
         <v>23</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4">
         <v>80</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4">
         <v>178</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4">
         <v>1</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4">
         <v>24</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5">
         <v>23</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5">
         <v>60</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5">
         <v>170</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="K5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6">
         <v>21</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6">
         <v>71</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6">
         <v>171</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6">
         <v>1</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6">
         <v>25</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7">
         <v>20</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7">
         <v>65</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7">
         <v>168</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7">
         <v>1</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7">
         <v>24</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8">
         <v>25</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8">
         <v>72</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8">
         <v>176</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8">
         <v>1</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8">
         <v>19</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9">
         <v>23</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9">
         <v>85</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9">
         <v>181</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9">
         <v>1</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9">
         <v>21</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10">
         <v>24</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10">
         <v>76</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10">
         <v>183</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10">
         <v>1</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10">
         <v>23</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11">
         <v>20</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11">
         <v>80</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11">
         <v>182</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11">
         <v>1</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11">
         <v>23</v>
       </c>
-      <c r="K11" s="0" t="n">
+      <c r="K11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12">
         <v>23</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12">
         <v>75</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12">
         <v>175</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12">
         <v>1</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12">
         <v>27</v>
       </c>
-      <c r="K12" s="0" t="s">
+      <c r="K12" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13">
         <v>24</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13">
         <v>80</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13">
         <v>177</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="G13">
         <v>1</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13">
         <v>28</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14">
         <v>21</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" t="s">
         <v>70</v>
       </c>
-      <c r="D14" s="0" t="n">
+      <c r="D14">
         <v>58</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14">
         <v>170</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="G14">
         <v>1</v>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="H14">
         <v>27</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="19.2"/>
+    <col min="11" max="11" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="G2" s="0" t="n">
+      <c r="B2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2">
         <v>18</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="G3" s="0" t="n">
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3">
         <v>0</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3">
         <v>16</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="G4" s="0" t="n">
+      <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4">
         <v>12</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="G5" s="0" t="n">
+      <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5">
         <v>0</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5">
         <v>19</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="G6" s="0" t="n">
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6">
         <v>19</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7" s="0" t="n">
+      <c r="B7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7">
         <v>0</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7">
         <v>17</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="G8" s="0" t="n">
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8">
         <v>0</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8">
         <v>15</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="G9" s="0" t="n">
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9">
         <v>0</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9">
         <v>15</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="G10" s="0" t="n">
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10">
         <v>0</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10">
         <v>19</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="G11" s="0" t="n">
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11">
         <v>0</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="24.06"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2">
         <v>69.86</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2">
         <v>1.68</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2">
         <v>3</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="0" t="n">
-        <v>66.68</v>
-      </c>
-      <c r="E3" s="0" t="n">
+      <c r="D3">
+        <v>66.680000000000007</v>
+      </c>
+      <c r="E3">
         <v>1.7</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3">
         <v>4</v>
       </c>
-      <c r="K3" s="0" t="s">
+      <c r="K3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4">
         <v>53.07</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4">
         <v>1.59</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5">
         <v>71.67</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5">
         <v>1.82</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6">
         <v>90.7</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6">
         <v>1.95</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7">
         <v>48.99</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7">
         <v>1.53</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8">
         <v>63.96</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8">
         <v>1.75</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC68D7D-1D9E-6049-977F-E8711D01C835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19410FCA-7AB1-2A4B-B61E-47033874DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="920" windowWidth="29080" windowHeight="18040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="160" yWindow="920" windowWidth="29080" windowHeight="18040" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="80">
   <si>
     <t>Database No.</t>
   </si>
@@ -285,6 +285,9 @@
   </si>
   <si>
     <t>T02_-130 (MarkerFitterError)</t>
+  </si>
+  <si>
+    <t>No ID</t>
   </si>
 </sst>
 </file>
@@ -1677,6 +1680,9 @@
       <c r="H4">
         <v>3</v>
       </c>
+      <c r="K4" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19410FCA-7AB1-2A4B-B61E-47033874DF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EAC4367-606B-43BF-BE1A-3B63AEFEF53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="920" windowWidth="29080" windowHeight="18040" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="81">
   <si>
     <t>Database No.</t>
   </si>
@@ -94,9 +94,6 @@
     <t>Overground</t>
   </si>
   <si>
-    <t>Multiple speeds &amp; step widths</t>
-  </si>
-  <si>
     <t>20–25</t>
   </si>
   <si>
@@ -116,9 +113,6 @@
   </si>
   <si>
     <t>A dataset of asymptomatic human gait and movements obtained from markers, IMUs, insoles and force plates</t>
-  </si>
-  <si>
-    <t>Multiple speeds</t>
   </si>
   <si>
     <t>29.7 ± 6.4</t>
@@ -289,12 +283,21 @@
   <si>
     <t>No ID</t>
   </si>
+  <si>
+    <t>Preferred &amp; step widths</t>
+  </si>
+  <si>
+    <t>Multiple speeds: slow gait, comfortable gait, fast gait</t>
+  </si>
+  <si>
+    <t>Self-selected spontaneous (C4) and fast (C5)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,6 +326,14 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -341,19 +352,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
@@ -547,28 +563,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="17.83203125" customWidth="1"/>
+    <col min="1" max="1" width="5.77734375" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" customWidth="1"/>
     <col min="4" max="4" width="14.33203125" customWidth="1"/>
-    <col min="5" max="5" width="33.83203125" customWidth="1"/>
+    <col min="5" max="5" width="33.77734375" customWidth="1"/>
     <col min="6" max="6" width="36" customWidth="1"/>
     <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="8" width="13.5" customWidth="1"/>
-    <col min="10" max="10" width="9.83203125" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" customWidth="1"/>
+    <col min="10" max="10" width="9.77734375" customWidth="1"/>
     <col min="11" max="11" width="12.6640625" customWidth="1"/>
     <col min="12" max="12" width="14.33203125" customWidth="1"/>
     <col min="13" max="13" width="12.6640625" customWidth="1"/>
     <col min="14" max="14" width="20" customWidth="1"/>
-    <col min="15" max="15" width="28.5" customWidth="1"/>
-    <col min="16" max="16" width="24.5" customWidth="1"/>
+    <col min="15" max="15" width="28.44140625" customWidth="1"/>
+    <col min="16" max="16" width="24.44140625" customWidth="1"/>
     <col min="17" max="17" width="20" customWidth="1"/>
     <col min="18" max="18" width="13" customWidth="1"/>
-    <col min="19" max="19" width="29.83203125" customWidth="1"/>
+    <col min="19" max="19" width="29.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -624,12 +640,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" ht="48" x14ac:dyDescent="0.2">
+      <c r="G2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -646,7 +665,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="H3">
         <v>13</v>
@@ -658,39 +677,39 @@
         <v>13</v>
       </c>
       <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s">
         <v>22</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>23</v>
       </c>
-      <c r="M3" t="s">
+      <c r="P3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S3" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4">
         <v>2023</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
         <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="H4" s="1">
         <v>10</v>
@@ -702,39 +721,39 @@
         <v>6</v>
       </c>
       <c r="K4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="P4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="S4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="48" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>2023</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H5" s="1">
         <v>7</v>
@@ -746,25 +765,25 @@
         <v>3</v>
       </c>
       <c r="K5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" t="s">
         <v>38</v>
-      </c>
-      <c r="L5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M5" t="s">
-        <v>40</v>
       </c>
       <c r="P5" s="1">
         <v>96</v>
       </c>
       <c r="R5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -773,7 +792,7 @@
       <c r="J7" s="1"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -782,21 +801,21 @@
       <c r="J8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:19" ht="48" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="H9" s="1">
         <v>30</v>
@@ -808,24 +827,24 @@
         <v>20</v>
       </c>
       <c r="S9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="48" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D10">
         <v>2026</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H10" s="1">
         <v>13</v>
@@ -837,24 +856,24 @@
         <v>8</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D11">
         <v>2024</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" t="s">
         <v>53</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" t="s">
-        <v>55</v>
       </c>
       <c r="H11" s="1">
         <v>30</v>
@@ -866,16 +885,16 @@
         <v>16</v>
       </c>
       <c r="K11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="S11" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -896,38 +915,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
         <v>60</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>62</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>67</v>
-      </c>
-      <c r="J1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K1" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -939,44 +958,44 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="11" max="11" width="28.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
         <v>60</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>62</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>67</v>
       </c>
-      <c r="J1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -984,7 +1003,7 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D2">
         <v>74</v>
@@ -999,10 +1018,10 @@
         <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1010,7 +1029,7 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D3">
         <v>72</v>
@@ -1028,7 +1047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1036,7 +1055,7 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D4">
         <v>80</v>
@@ -1054,7 +1073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1062,7 +1081,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D5">
         <v>60</v>
@@ -1077,10 +1096,10 @@
         <v>17</v>
       </c>
       <c r="K5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1088,7 +1107,7 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D6">
         <v>71</v>
@@ -1103,7 +1122,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1111,7 +1130,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D7">
         <v>65</v>
@@ -1126,7 +1145,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1134,7 +1153,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D8">
         <v>72</v>
@@ -1149,7 +1168,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1157,7 +1176,7 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D9">
         <v>85</v>
@@ -1172,7 +1191,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1180,7 +1199,7 @@
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D10">
         <v>76</v>
@@ -1195,7 +1214,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1203,7 +1222,7 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D11">
         <v>80</v>
@@ -1221,7 +1240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1229,7 +1248,7 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D12">
         <v>75</v>
@@ -1244,10 +1263,10 @@
         <v>27</v>
       </c>
       <c r="K12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1255,7 +1274,7 @@
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D13">
         <v>80</v>
@@ -1270,7 +1289,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1278,7 +1297,7 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D14">
         <v>58</v>
@@ -1302,58 +1321,58 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="11" max="11" width="19.1640625" customWidth="1"/>
+    <col min="11" max="11" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
         <v>60</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>62</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>67</v>
       </c>
-      <c r="J1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1362,21 +1381,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1385,21 +1404,21 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1408,21 +1427,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1431,21 +1450,21 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1454,21 +1473,21 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1477,21 +1496,21 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1500,21 +1519,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1523,21 +1542,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1546,21 +1565,21 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1578,52 +1597,52 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="11" max="11" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
         <v>60</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>62</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>67</v>
       </c>
-      <c r="J1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D2">
         <v>69.86</v>
@@ -1635,18 +1654,18 @@
         <v>3</v>
       </c>
       <c r="K2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D3">
         <v>66.680000000000007</v>
@@ -1658,18 +1677,18 @@
         <v>4</v>
       </c>
       <c r="K3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D4">
         <v>53.07</v>
@@ -1681,18 +1700,18 @@
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D5">
         <v>71.67</v>
@@ -1704,15 +1723,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D6">
         <v>90.7</v>
@@ -1724,15 +1743,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D7">
         <v>48.99</v>
@@ -1744,15 +1763,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D8">
         <v>63.96</v>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EAC4367-606B-43BF-BE1A-3B63AEFEF53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6966347-513D-4FED-BBDA-268D7F849F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/TeamProject/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6966347-513D-4FED-BBDA-268D7F849F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF009508-D356-0346-BFB3-6CF22E7AFCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27420" windowHeight="17500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="93">
   <si>
     <t>Database No.</t>
-  </si>
-  <si>
-    <t>Related Paper</t>
   </si>
   <si>
     <t>Authors</t>
@@ -292,12 +289,69 @@
   <si>
     <t>Self-selected spontaneous (C4) and fast (C5)</t>
   </si>
+  <si>
+    <t>A multimodal dataset of human gait at different walking speeds established on injury-free adult participants</t>
+  </si>
+  <si>
+    <t>Schreiber &amp; Moissenet</t>
+  </si>
+  <si>
+    <t>19-67</t>
+  </si>
+  <si>
+    <t>1.74 ± 0.09 m</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">71.0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="EuclidSymbol"/>
+      </rPr>
+      <t xml:space="preserve">± </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="MinionPro"/>
+      </rPr>
+      <t xml:space="preserve">12.3 kg </t>
+    </r>
+  </si>
+  <si>
+    <t>5 trials each with 5 different speeds</t>
+  </si>
+  <si>
+    <t>Luxembourg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52 reflective markers </t>
+  </si>
+  <si>
+    <t>https://figshare.com/articles/dataset/A_multimodal_dataset_of_human_gait_at_different_walking_speeds/7734767</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1-C5 variable trails </t>
+  </si>
+  <si>
+    <t>only C4 &amp; C5 (variable trials)</t>
+  </si>
+  <si>
+    <t>Duration per trials(s)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,6 +388,36 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="MinionPro"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="EuclidSymbol"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -357,7 +441,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -367,6 +451,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -562,119 +656,164 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S11"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.77734375" customWidth="1"/>
-    <col min="2" max="2" width="17.77734375" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" customWidth="1"/>
-    <col min="5" max="5" width="33.77734375" customWidth="1"/>
-    <col min="6" max="6" width="36" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" customWidth="1"/>
-    <col min="10" max="10" width="9.77734375" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
-    <col min="15" max="15" width="28.44140625" customWidth="1"/>
-    <col min="16" max="16" width="24.44140625" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
-    <col min="18" max="18" width="13" customWidth="1"/>
-    <col min="19" max="19" width="29.77734375" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" customWidth="1"/>
+    <col min="4" max="4" width="33.83203125" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="14" max="14" width="28.5" customWidth="1"/>
+    <col min="15" max="15" width="24.5" customWidth="1"/>
+    <col min="16" max="16" width="20" customWidth="1"/>
+    <col min="17" max="17" width="40.83203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="29.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:18" s="6" customFormat="1" ht="17">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:18" ht="64">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="G2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2">
+        <v>2019</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2">
+        <v>50</v>
+      </c>
+      <c r="H2">
+        <v>24</v>
+      </c>
+      <c r="I2">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P2">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="48">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3">
+        <v>2025</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D3">
-        <v>2025</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>13</v>
+      </c>
+      <c r="J3" t="s">
         <v>20</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H3">
-        <v>13</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0</v>
-      </c>
-      <c r="J3" s="1">
-        <v>13</v>
       </c>
       <c r="K3" t="s">
         <v>21</v>
@@ -682,87 +821,87 @@
       <c r="L3" t="s">
         <v>22</v>
       </c>
-      <c r="M3" t="s">
+      <c r="O3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="S3" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="46.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:18" ht="51">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4">
+        <v>2023</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D4">
-        <v>2023</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="1">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1">
+        <v>4</v>
+      </c>
+      <c r="I4" s="1">
+        <v>6</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H4" s="1">
-        <v>10</v>
-      </c>
-      <c r="I4" s="1">
-        <v>4</v>
-      </c>
-      <c r="J4" s="1">
-        <v>6</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="O4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="R4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="S4" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:18" ht="48">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5">
+        <v>2023</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D5">
-        <v>2023</v>
-      </c>
       <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="1">
+        <v>7</v>
+      </c>
+      <c r="H5" s="1">
+        <v>4</v>
+      </c>
+      <c r="I5" s="1">
+        <v>3</v>
+      </c>
+      <c r="J5" t="s">
         <v>35</v>
-      </c>
-      <c r="H5" s="1">
-        <v>7</v>
-      </c>
-      <c r="I5" s="1">
-        <v>4</v>
-      </c>
-      <c r="J5" s="1">
-        <v>3</v>
       </c>
       <c r="K5" t="s">
         <v>36</v>
@@ -770,43 +909,41 @@
       <c r="L5" t="s">
         <v>37</v>
       </c>
-      <c r="M5" t="s">
+      <c r="O5" s="1">
+        <v>96</v>
+      </c>
+      <c r="Q5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="P5" s="1">
-        <v>96</v>
-      </c>
-      <c r="R5" t="s">
+      <c r="R5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S5" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:18">
+      <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="S7" s="1"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="R7" s="1"/>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="9" spans="1:19" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="C9" t="s">
+      <c r="R8" s="1"/>
+    </row>
+    <row r="9" spans="1:18" ht="48">
+      <c r="B9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9">
+        <v>2025</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="D9">
-        <v>2025</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>42</v>
@@ -814,98 +951,95 @@
       <c r="F9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="1">
+        <v>30</v>
+      </c>
+      <c r="H9" s="1">
+        <v>10</v>
+      </c>
+      <c r="I9" s="1">
+        <v>20</v>
+      </c>
+      <c r="R9" t="s">
         <v>44</v>
       </c>
-      <c r="H9" s="1">
-        <v>30</v>
-      </c>
-      <c r="I9" s="1">
-        <v>10</v>
-      </c>
-      <c r="J9" s="1">
-        <v>20</v>
-      </c>
-      <c r="S9" t="s">
+    </row>
+    <row r="10" spans="1:18" ht="48">
+      <c r="B10" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="C10" t="s">
+      <c r="C10">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="D10">
-        <v>2026</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="1">
+        <v>13</v>
+      </c>
+      <c r="H10" s="1">
+        <v>5</v>
+      </c>
+      <c r="I10" s="1">
+        <v>8</v>
+      </c>
+      <c r="R10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="1">
-        <v>13</v>
-      </c>
-      <c r="I10" s="1">
-        <v>5</v>
-      </c>
-      <c r="J10" s="1">
-        <v>8</v>
-      </c>
-      <c r="S10" s="1" t="s">
+    </row>
+    <row r="11" spans="1:18" ht="82.5" customHeight="1">
+      <c r="B11" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" t="s">
+      <c r="C11">
+        <v>2024</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D11">
-        <v>2024</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" t="s">
         <v>51</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="1">
+        <v>30</v>
+      </c>
+      <c r="H11" s="1">
+        <v>14</v>
+      </c>
+      <c r="I11" s="1">
+        <v>16</v>
+      </c>
+      <c r="J11" t="s">
         <v>53</v>
       </c>
-      <c r="H11" s="1">
-        <v>30</v>
-      </c>
-      <c r="I11" s="1">
-        <v>14</v>
-      </c>
-      <c r="J11" s="1">
-        <v>16</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="K11" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="L11" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="3" t="s">
+      <c r="R11" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="S4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="R5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="S5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="S9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="S10" r:id="rId6" location="Bib1" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="S11" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="R3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="R4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="Q5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="R5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="R9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="R10" r:id="rId6" location="Bib1" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="R11" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -914,39 +1048,1351 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J51"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="24.33203125" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" customWidth="1"/>
+    <col min="10" max="10" width="19.83203125" customWidth="1"/>
+    <col min="14" max="14" width="8.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" s="5" customFormat="1">
+      <c r="A1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>31</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2">
+        <v>67</v>
+      </c>
+      <c r="E2">
+        <v>1.66</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="16">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>48</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3">
+        <v>65.400000000000006</v>
+      </c>
+      <c r="E3">
+        <v>1.64</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="16">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>28</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4">
+        <v>50</v>
+      </c>
+      <c r="E4">
+        <v>1.56</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="16">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>23</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5">
+        <v>72.5</v>
+      </c>
+      <c r="E5">
+        <v>1.77</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="16">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>25</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6">
+        <v>73.5</v>
+      </c>
+      <c r="E6">
+        <v>1.83</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="16">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>23</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7">
+        <v>73</v>
+      </c>
+      <c r="E7">
+        <v>1.76</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>90</v>
+      </c>
+      <c r="H7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="16">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>44</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8">
         <v>65</v>
       </c>
-      <c r="J1" t="s">
-        <v>66</v>
-      </c>
-      <c r="K1" t="s">
-        <v>67</v>
+      <c r="E8">
+        <v>1.69</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="16">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>30</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9">
+        <v>57.1</v>
+      </c>
+      <c r="E9">
+        <v>1.66</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="16">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>57</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10">
+        <v>86</v>
+      </c>
+      <c r="E10">
+        <v>1.88</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="16">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>59</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11">
+        <v>63.4</v>
+      </c>
+      <c r="E11">
+        <v>1.8</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>90</v>
+      </c>
+      <c r="H11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="16">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>26</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12">
+        <v>61.3</v>
+      </c>
+      <c r="E12">
+        <v>1.7</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="16">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>29</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13">
+        <v>92</v>
+      </c>
+      <c r="E13">
+        <v>1.8</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="16">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>22</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14">
+        <v>67</v>
+      </c>
+      <c r="E14">
+        <v>1.58</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="16">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>26</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15">
+        <v>73.8</v>
+      </c>
+      <c r="E15">
+        <v>1.76</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>90</v>
+      </c>
+      <c r="H15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>48</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16">
+        <v>59.8</v>
+      </c>
+      <c r="E16">
+        <v>1.71</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="16">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>33</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17">
+        <v>87.5</v>
+      </c>
+      <c r="E17">
+        <v>1.92</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="16">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>31</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18">
+        <v>80.5</v>
+      </c>
+      <c r="E18">
+        <v>1.66</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>90</v>
+      </c>
+      <c r="H18" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="16">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>38</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19">
+        <v>89.9</v>
+      </c>
+      <c r="E19">
+        <v>1.89</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>90</v>
+      </c>
+      <c r="H19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="16">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>62</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20">
+        <v>60.7</v>
+      </c>
+      <c r="E20">
+        <v>1.7</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>90</v>
+      </c>
+      <c r="H20" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="16">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>21</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21">
+        <v>67.2</v>
+      </c>
+      <c r="E21">
+        <v>1.77</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>90</v>
+      </c>
+      <c r="H21" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="16">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>24</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22">
+        <v>63.5</v>
+      </c>
+      <c r="E22">
+        <v>1.6</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>90</v>
+      </c>
+      <c r="H22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="16">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>21</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23">
+        <v>89.6</v>
+      </c>
+      <c r="E23">
+        <v>1.84</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>90</v>
+      </c>
+      <c r="H23" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="16">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>19</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24">
+        <v>56.5</v>
+      </c>
+      <c r="E24">
+        <v>1.55</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="16">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>40</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25">
+        <v>61.8</v>
+      </c>
+      <c r="E25">
+        <v>1.65</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
+        <v>90</v>
+      </c>
+      <c r="H25" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="16">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>40</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26">
+        <v>61.5</v>
+      </c>
+      <c r="E26">
+        <v>1.64</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
+        <v>90</v>
+      </c>
+      <c r="H26" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="16">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>32</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27">
+        <v>72.2</v>
+      </c>
+      <c r="E27">
+        <v>1.74</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27" t="s">
+        <v>90</v>
+      </c>
+      <c r="H27" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="16">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>28</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28">
+        <v>61.9</v>
+      </c>
+      <c r="E28">
+        <v>1.64</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28" t="s">
+        <v>90</v>
+      </c>
+      <c r="H28" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="16">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>25</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29">
+        <v>88</v>
+      </c>
+      <c r="E29">
+        <v>1.91</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
+        <v>90</v>
+      </c>
+      <c r="H29" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="16">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>25</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30">
+        <v>79.5</v>
+      </c>
+      <c r="E30">
+        <v>1.82</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30" t="s">
+        <v>90</v>
+      </c>
+      <c r="H30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="16">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>21</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31">
+        <v>62.8</v>
+      </c>
+      <c r="E31">
+        <v>1.72</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" t="s">
+        <v>90</v>
+      </c>
+      <c r="H31" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="16">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>39</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32">
+        <v>74</v>
+      </c>
+      <c r="E32">
+        <v>1.74</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>90</v>
+      </c>
+      <c r="H32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="16">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>52</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33">
+        <v>87.2</v>
+      </c>
+      <c r="E33">
+        <v>1.77</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33" t="s">
+        <v>90</v>
+      </c>
+      <c r="H33" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="16">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>35</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34">
+        <v>62</v>
+      </c>
+      <c r="E34">
+        <v>1.7</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H34" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="16">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>48</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D35">
+        <v>89.4</v>
+      </c>
+      <c r="E35">
+        <v>1.9</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35" t="s">
+        <v>90</v>
+      </c>
+      <c r="H35" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="16">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>63</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D36">
+        <v>60.2</v>
+      </c>
+      <c r="E36">
+        <v>1.66</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36" t="s">
+        <v>90</v>
+      </c>
+      <c r="H36" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="16">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>58</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37">
+        <v>73</v>
+      </c>
+      <c r="E37">
+        <v>1.69</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37" t="s">
+        <v>90</v>
+      </c>
+      <c r="H37" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="16">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>50</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38">
+        <v>68</v>
+      </c>
+      <c r="E38">
+        <v>1.73</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38" t="s">
+        <v>90</v>
+      </c>
+      <c r="H38" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="16">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>46</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D39">
+        <v>76</v>
+      </c>
+      <c r="E39">
+        <v>1.69</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39" t="s">
+        <v>90</v>
+      </c>
+      <c r="H39" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="16">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>41</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40">
+        <v>60.5</v>
+      </c>
+      <c r="E40">
+        <v>1.67</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40" t="s">
+        <v>90</v>
+      </c>
+      <c r="H40" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="16">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>43</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41">
+        <v>95</v>
+      </c>
+      <c r="E41">
+        <v>1.79</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" t="s">
+        <v>90</v>
+      </c>
+      <c r="H41" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="16">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>30</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42">
+        <v>58</v>
+      </c>
+      <c r="E42">
+        <v>1.69</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42" t="s">
+        <v>90</v>
+      </c>
+      <c r="H42" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="16">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>64</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43">
+        <v>51.5</v>
+      </c>
+      <c r="E43">
+        <v>1.71</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" t="s">
+        <v>90</v>
+      </c>
+      <c r="H43" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="16">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>51</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D44">
+        <v>65.5</v>
+      </c>
+      <c r="E44">
+        <v>1.72</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44" t="s">
+        <v>90</v>
+      </c>
+      <c r="H44" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="16">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>24</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45">
+        <v>86</v>
+      </c>
+      <c r="E45">
+        <v>1.87</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45" t="s">
+        <v>90</v>
+      </c>
+      <c r="H45" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="16">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>26</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D46">
+        <v>50.8</v>
+      </c>
+      <c r="E46">
+        <v>1.72</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" t="s">
+        <v>90</v>
+      </c>
+      <c r="H46" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="16">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>38</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D47">
+        <v>81.5</v>
+      </c>
+      <c r="E47">
+        <v>1.77</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47" t="s">
+        <v>90</v>
+      </c>
+      <c r="H47" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="16">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>42</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D48">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="E48">
+        <v>1.76</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48" t="s">
+        <v>90</v>
+      </c>
+      <c r="H48" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="16">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>31</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49">
+        <v>74.8</v>
+      </c>
+      <c r="E49">
+        <v>1.88</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49" t="s">
+        <v>90</v>
+      </c>
+      <c r="H49" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="16">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>67</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50">
+        <v>98</v>
+      </c>
+      <c r="E50">
+        <v>1.83</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50" t="s">
+        <v>90</v>
+      </c>
+      <c r="H50" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="16">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>21</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D51">
+        <v>74</v>
+      </c>
+      <c r="E51">
+        <v>1.78</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51" t="s">
+        <v>90</v>
+      </c>
+      <c r="H51" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -958,44 +2404,46 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
+    <col min="9" max="9" width="14.1640625" customWidth="1"/>
+    <col min="10" max="10" width="19.1640625" customWidth="1"/>
     <col min="11" max="11" width="28.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>59</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>61</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>64</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>65</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>66</v>
       </c>
-      <c r="K1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1003,7 +2451,7 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D2">
         <v>74</v>
@@ -1018,10 +2466,10 @@
         <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1029,7 +2477,7 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D3">
         <v>72</v>
@@ -1047,7 +2495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1055,7 +2503,7 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D4">
         <v>80</v>
@@ -1073,7 +2521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1081,7 +2529,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D5">
         <v>60</v>
@@ -1096,10 +2544,10 @@
         <v>17</v>
       </c>
       <c r="K5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1107,7 +2555,7 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D6">
         <v>71</v>
@@ -1122,7 +2570,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1130,7 +2578,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D7">
         <v>65</v>
@@ -1145,7 +2593,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1153,7 +2601,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D8">
         <v>72</v>
@@ -1168,7 +2616,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1176,7 +2624,7 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D9">
         <v>85</v>
@@ -1191,7 +2639,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1199,7 +2647,7 @@
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D10">
         <v>76</v>
@@ -1214,7 +2662,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1222,7 +2670,7 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D11">
         <v>80</v>
@@ -1240,7 +2688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1248,7 +2696,7 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D12">
         <v>75</v>
@@ -1263,10 +2711,10 @@
         <v>27</v>
       </c>
       <c r="K12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1274,7 +2722,7 @@
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D13">
         <v>80</v>
@@ -1289,7 +2737,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1297,7 +2745,7 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14">
         <v>58</v>
@@ -1321,58 +2769,58 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="11" max="11" width="19.109375" customWidth="1"/>
+    <col min="11" max="11" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>59</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>61</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>64</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>65</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>66</v>
       </c>
-      <c r="K1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1381,21 +2829,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1404,21 +2852,21 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1427,21 +2875,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1450,21 +2898,21 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1473,21 +2921,21 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1496,21 +2944,21 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1519,21 +2967,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1542,21 +2990,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1565,21 +3013,21 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1597,52 +3045,52 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="11" max="11" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>59</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>61</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>64</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>65</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>66</v>
       </c>
-      <c r="K1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
         <v>72</v>
-      </c>
-      <c r="C2" t="s">
-        <v>73</v>
       </c>
       <c r="D2">
         <v>69.86</v>
@@ -1654,18 +3102,18 @@
         <v>3</v>
       </c>
       <c r="K2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D3">
         <v>66.680000000000007</v>
@@ -1677,18 +3125,18 @@
         <v>4</v>
       </c>
       <c r="K3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" t="s">
         <v>72</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
       </c>
       <c r="D4">
         <v>53.07</v>
@@ -1700,18 +3148,18 @@
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D5">
         <v>71.67</v>
@@ -1723,15 +3171,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D6">
         <v>90.7</v>
@@ -1743,15 +3191,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" t="s">
         <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
       </c>
       <c r="D7">
         <v>48.99</v>
@@ -1763,15 +3211,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
         <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>73</v>
       </c>
       <c r="D8">
         <v>63.96</v>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/TeamProject/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF009508-D356-0346-BFB3-6CF22E7AFCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE757F6-8ABE-4F17-9A9B-888006D49CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="27420" windowHeight="17500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-36" yWindow="0" windowWidth="14724" windowHeight="12336" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="90">
   <si>
     <t>Database No.</t>
   </si>
@@ -337,21 +337,12 @@
   <si>
     <t>W</t>
   </si>
-  <si>
-    <t xml:space="preserve">C1-C5 variable trails </t>
-  </si>
-  <si>
-    <t>only C4 &amp; C5 (variable trials)</t>
-  </si>
-  <si>
-    <t>Duration per trials(s)</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -400,13 +391,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -441,7 +425,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -454,13 +438,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -657,81 +638,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.1640625" customWidth="1"/>
-    <col min="4" max="4" width="33.83203125" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="4" max="4" width="33.77734375" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="23.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="14.33203125" customWidth="1"/>
     <col min="12" max="12" width="12.6640625" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="28.5" customWidth="1"/>
-    <col min="15" max="15" width="24.5" customWidth="1"/>
+    <col min="14" max="14" width="28.44140625" customWidth="1"/>
+    <col min="15" max="15" width="24.44140625" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="40.83203125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="29.83203125" customWidth="1"/>
+    <col min="17" max="17" width="40.77734375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="29.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="6" customFormat="1" ht="17">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:18" s="5" customFormat="1" ht="15.6">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="64">
+    <row r="2" spans="1:18" ht="43.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -784,7 +765,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="48">
+    <row r="3" spans="1:18" ht="43.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -828,7 +809,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="51">
+    <row r="4" spans="1:18" ht="46.8">
       <c r="A4">
         <v>3</v>
       </c>
@@ -872,7 +853,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="48">
+    <row r="5" spans="1:18" ht="43.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -935,7 +916,7 @@
       <c r="I8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="48">
+    <row r="9" spans="1:18" ht="57.6">
       <c r="B9" s="1" t="s">
         <v>40</v>
       </c>
@@ -964,7 +945,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="48">
+    <row r="10" spans="1:18" ht="43.2">
       <c r="B10" s="1" t="s">
         <v>45</v>
       </c>
@@ -1048,61 +1029,61 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="24.33203125" customWidth="1"/>
-    <col min="9" max="9" width="19.33203125" customWidth="1"/>
-    <col min="10" max="10" width="19.83203125" customWidth="1"/>
-    <col min="14" max="14" width="8.83203125" customWidth="1"/>
+    <col min="5" max="6" width="12" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="24.33203125" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" customWidth="1"/>
+    <col min="11" max="11" width="19.77734375" customWidth="1"/>
+    <col min="15" max="15" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16">
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>31</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D2">
@@ -1111,24 +1092,21 @@
       <c r="E2">
         <v>1.66</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="16">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>48</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D3">
@@ -1137,24 +1115,21 @@
       <c r="E3">
         <v>1.64</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="16">
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <v>28</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D4">
@@ -1163,24 +1138,21 @@
       <c r="E4">
         <v>1.56</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>90</v>
-      </c>
-      <c r="H4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="16">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
         <v>23</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D5">
@@ -1189,24 +1161,21 @@
       <c r="E5">
         <v>1.77</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>90</v>
-      </c>
-      <c r="H5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="16">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
         <v>25</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D6">
@@ -1215,24 +1184,21 @@
       <c r="E6">
         <v>1.83</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="16">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
         <v>23</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D7">
@@ -1241,24 +1207,21 @@
       <c r="E7">
         <v>1.76</v>
       </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>90</v>
-      </c>
-      <c r="H7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="16">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
         <v>44</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D8">
@@ -1267,24 +1230,21 @@
       <c r="E8">
         <v>1.69</v>
       </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>90</v>
-      </c>
-      <c r="H8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="16">
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
         <v>30</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D9">
@@ -1293,24 +1253,21 @@
       <c r="E9">
         <v>1.66</v>
       </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="16">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
         <v>57</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D10">
@@ -1319,24 +1276,21 @@
       <c r="E10">
         <v>1.88</v>
       </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="16">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
         <v>59</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D11">
@@ -1345,24 +1299,21 @@
       <c r="E11">
         <v>1.8</v>
       </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>90</v>
-      </c>
-      <c r="H11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="16">
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
         <v>26</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D12">
@@ -1371,24 +1322,21 @@
       <c r="E12">
         <v>1.7</v>
       </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>90</v>
-      </c>
-      <c r="H12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="16">
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
         <v>29</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D13">
@@ -1397,24 +1345,21 @@
       <c r="E13">
         <v>1.8</v>
       </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>90</v>
-      </c>
-      <c r="H13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="16">
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
         <v>22</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D14">
@@ -1423,24 +1368,21 @@
       <c r="E14">
         <v>1.58</v>
       </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>90</v>
-      </c>
-      <c r="H14" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="16">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
         <v>26</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D15">
@@ -1449,24 +1391,21 @@
       <c r="E15">
         <v>1.76</v>
       </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
-        <v>90</v>
-      </c>
-      <c r="H15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="16">
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
         <v>48</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D16">
@@ -1475,24 +1414,21 @@
       <c r="E16">
         <v>1.71</v>
       </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>90</v>
-      </c>
-      <c r="H16" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="16">
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
         <v>33</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D17">
@@ -1501,24 +1437,21 @@
       <c r="E17">
         <v>1.92</v>
       </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="16">
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
         <v>31</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D18">
@@ -1527,24 +1460,21 @@
       <c r="E18">
         <v>1.66</v>
       </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18" t="s">
-        <v>90</v>
-      </c>
-      <c r="H18" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="16">
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
         <v>38</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D19">
@@ -1553,24 +1483,21 @@
       <c r="E19">
         <v>1.89</v>
       </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
-        <v>90</v>
-      </c>
-      <c r="H19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="16">
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
         <v>62</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D20">
@@ -1579,24 +1506,21 @@
       <c r="E20">
         <v>1.7</v>
       </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20" t="s">
-        <v>90</v>
-      </c>
-      <c r="H20" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="16">
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
         <v>21</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D21">
@@ -1605,24 +1529,21 @@
       <c r="E21">
         <v>1.77</v>
       </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21" t="s">
-        <v>90</v>
-      </c>
-      <c r="H21" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="16">
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
         <v>24</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D22">
@@ -1631,24 +1552,21 @@
       <c r="E22">
         <v>1.6</v>
       </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22" t="s">
-        <v>90</v>
-      </c>
-      <c r="H22" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="16">
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
         <v>21</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D23">
@@ -1657,24 +1575,21 @@
       <c r="E23">
         <v>1.84</v>
       </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23" t="s">
-        <v>90</v>
-      </c>
-      <c r="H23" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="16">
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
         <v>19</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D24">
@@ -1683,24 +1598,21 @@
       <c r="E24">
         <v>1.55</v>
       </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24" t="s">
-        <v>90</v>
-      </c>
-      <c r="H24" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="16">
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
         <v>40</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D25">
@@ -1709,24 +1621,21 @@
       <c r="E25">
         <v>1.65</v>
       </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25" t="s">
-        <v>90</v>
-      </c>
-      <c r="H25" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="16">
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
         <v>40</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D26">
@@ -1735,24 +1644,21 @@
       <c r="E26">
         <v>1.64</v>
       </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26" t="s">
-        <v>90</v>
-      </c>
-      <c r="H26" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="16">
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27">
         <v>32</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D27">
@@ -1761,24 +1667,21 @@
       <c r="E27">
         <v>1.74</v>
       </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27" t="s">
-        <v>90</v>
-      </c>
-      <c r="H27" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="16">
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28">
         <v>28</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D28">
@@ -1787,24 +1690,21 @@
       <c r="E28">
         <v>1.64</v>
       </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28" t="s">
-        <v>90</v>
-      </c>
-      <c r="H28" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="16">
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29">
         <v>25</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D29">
@@ -1813,24 +1713,21 @@
       <c r="E29">
         <v>1.91</v>
       </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29" t="s">
-        <v>90</v>
-      </c>
-      <c r="H29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="16">
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30">
         <v>25</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D30">
@@ -1839,24 +1736,21 @@
       <c r="E30">
         <v>1.82</v>
       </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30" t="s">
-        <v>90</v>
-      </c>
-      <c r="H30" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="16">
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31">
         <v>21</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D31">
@@ -1865,24 +1759,21 @@
       <c r="E31">
         <v>1.72</v>
       </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="G31" t="s">
-        <v>90</v>
-      </c>
-      <c r="H31" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="16">
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32">
         <v>39</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D32">
@@ -1891,24 +1782,21 @@
       <c r="E32">
         <v>1.74</v>
       </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32" t="s">
-        <v>90</v>
-      </c>
-      <c r="H32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="16">
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33">
         <v>52</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D33">
@@ -1917,24 +1805,21 @@
       <c r="E33">
         <v>1.77</v>
       </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="G33" t="s">
-        <v>90</v>
-      </c>
-      <c r="H33" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="16">
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34">
         <v>35</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D34">
@@ -1943,24 +1828,21 @@
       <c r="E34">
         <v>1.7</v>
       </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="G34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H34" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="16">
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35">
         <v>48</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D35">
@@ -1969,24 +1851,21 @@
       <c r="E35">
         <v>1.9</v>
       </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-      <c r="G35" t="s">
-        <v>90</v>
-      </c>
-      <c r="H35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="16">
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36">
         <v>63</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D36">
@@ -1995,24 +1874,21 @@
       <c r="E36">
         <v>1.66</v>
       </c>
-      <c r="F36">
-        <v>1</v>
-      </c>
-      <c r="G36" t="s">
-        <v>90</v>
-      </c>
-      <c r="H36" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="16">
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37">
         <v>58</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D37">
@@ -2021,24 +1897,21 @@
       <c r="E37">
         <v>1.69</v>
       </c>
-      <c r="F37">
-        <v>1</v>
-      </c>
-      <c r="G37" t="s">
-        <v>90</v>
-      </c>
-      <c r="H37" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="16">
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38">
         <v>50</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D38">
@@ -2047,24 +1920,21 @@
       <c r="E38">
         <v>1.73</v>
       </c>
-      <c r="F38">
-        <v>1</v>
-      </c>
-      <c r="G38" t="s">
-        <v>90</v>
-      </c>
-      <c r="H38" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="16">
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39">
         <v>46</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D39">
@@ -2073,24 +1943,21 @@
       <c r="E39">
         <v>1.69</v>
       </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-      <c r="G39" t="s">
-        <v>90</v>
-      </c>
-      <c r="H39" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="16">
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40">
         <v>41</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D40">
@@ -2099,24 +1966,21 @@
       <c r="E40">
         <v>1.67</v>
       </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
-      <c r="G40" t="s">
-        <v>90</v>
-      </c>
-      <c r="H40" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="16">
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41">
         <v>43</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D41">
@@ -2125,24 +1989,21 @@
       <c r="E41">
         <v>1.79</v>
       </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-      <c r="G41" t="s">
-        <v>90</v>
-      </c>
-      <c r="H41" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="16">
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42">
         <v>30</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D42">
@@ -2151,24 +2012,21 @@
       <c r="E42">
         <v>1.69</v>
       </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-      <c r="G42" t="s">
-        <v>90</v>
-      </c>
-      <c r="H42" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="16">
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43">
         <v>64</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D43">
@@ -2177,24 +2035,21 @@
       <c r="E43">
         <v>1.71</v>
       </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="G43" t="s">
-        <v>90</v>
-      </c>
-      <c r="H43" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="16">
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44">
         <v>51</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D44">
@@ -2203,24 +2058,21 @@
       <c r="E44">
         <v>1.72</v>
       </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-      <c r="G44" t="s">
-        <v>90</v>
-      </c>
-      <c r="H44" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="16">
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45">
         <v>24</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D45">
@@ -2229,24 +2081,21 @@
       <c r="E45">
         <v>1.87</v>
       </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
-      <c r="G45" t="s">
-        <v>90</v>
-      </c>
-      <c r="H45" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="16">
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46">
         <v>26</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D46">
@@ -2255,24 +2104,21 @@
       <c r="E46">
         <v>1.72</v>
       </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-      <c r="G46" t="s">
-        <v>90</v>
-      </c>
-      <c r="H46" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="16">
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47">
         <v>38</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D47">
@@ -2281,24 +2127,21 @@
       <c r="E47">
         <v>1.77</v>
       </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-      <c r="G47" t="s">
-        <v>90</v>
-      </c>
-      <c r="H47" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="16">
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48">
         <v>42</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D48">
@@ -2307,24 +2150,21 @@
       <c r="E48">
         <v>1.76</v>
       </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
-      <c r="G48" t="s">
-        <v>90</v>
-      </c>
-      <c r="H48" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="16">
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49">
         <v>31</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C49" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D49">
@@ -2333,24 +2173,21 @@
       <c r="E49">
         <v>1.88</v>
       </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-      <c r="G49" t="s">
-        <v>90</v>
-      </c>
-      <c r="H49" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="16">
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50">
         <v>67</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C50" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D50">
@@ -2359,24 +2196,21 @@
       <c r="E50">
         <v>1.83</v>
       </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-      <c r="G50" t="s">
-        <v>90</v>
-      </c>
-      <c r="H50" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="16">
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51">
         <v>21</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C51" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D51">
@@ -2385,14 +2219,11 @@
       <c r="E51">
         <v>1.78</v>
       </c>
-      <c r="F51">
-        <v>1</v>
-      </c>
-      <c r="G51" t="s">
-        <v>90</v>
-      </c>
-      <c r="H51" t="s">
-        <v>91</v>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2404,10 +2235,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="9" max="9" width="14.1640625" customWidth="1"/>
-    <col min="10" max="10" width="19.1640625" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" customWidth="1"/>
+    <col min="10" max="10" width="19.109375" customWidth="1"/>
     <col min="11" max="11" width="28.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2769,9 +2600,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="11" max="11" width="19.1640625" customWidth="1"/>
+    <col min="11" max="11" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -3045,7 +2876,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="11" max="11" width="24" customWidth="1"/>
   </cols>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE757F6-8ABE-4F17-9A9B-888006D49CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77ADC58E-6F4B-4E56-816D-9865C1EE2D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36" yWindow="0" windowWidth="14724" windowHeight="12336" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,19 @@
     <sheet name="DB3" sheetId="4" r:id="rId4"/>
     <sheet name="DB4" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -254,9 +265,6 @@
     <t>M</t>
   </si>
   <si>
-    <t>3-all ('LoadingError')</t>
-  </si>
-  <si>
     <t>T04_Cal_relabeled (missing GRF)</t>
   </si>
   <si>
@@ -270,9 +278,6 @@
   </si>
   <si>
     <t>1:3 (No ID)</t>
-  </si>
-  <si>
-    <t>4 (First half No ID)</t>
   </si>
   <si>
     <t>T02_-130 (MarkerFitterError)</t>
@@ -336,6 +341,12 @@
   </si>
   <si>
     <t>W</t>
+  </si>
+  <si>
+    <t>4 (1st half No ID, 2nd half wrong)</t>
+  </si>
+  <si>
+    <t>3-all ('LoadingError'), 4 in total</t>
   </si>
 </sst>
 </file>
@@ -717,19 +728,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C2">
         <v>2019</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G2">
         <v>50</v>
@@ -741,28 +752,28 @@
         <v>26</v>
       </c>
       <c r="J2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" t="s">
         <v>82</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N2" t="s">
         <v>83</v>
       </c>
-      <c r="L2" t="s">
-        <v>84</v>
-      </c>
-      <c r="M2" t="s">
-        <v>86</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>85</v>
-      </c>
-      <c r="O2" t="s">
-        <v>87</v>
       </c>
       <c r="P2">
         <v>2</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="43.2">
@@ -782,7 +793,7 @@
         <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G3">
         <v>13</v>
@@ -826,7 +837,7 @@
         <v>19</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G4" s="1">
         <v>10</v>
@@ -1107,7 +1118,7 @@
         <v>48</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D3">
         <v>65.400000000000006</v>
@@ -1130,7 +1141,7 @@
         <v>28</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D4">
         <v>50</v>
@@ -1222,7 +1233,7 @@
         <v>44</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D8">
         <v>65</v>
@@ -1245,7 +1256,7 @@
         <v>30</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D9">
         <v>57.1</v>
@@ -1314,7 +1325,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D12">
         <v>61.3</v>
@@ -1360,7 +1371,7 @@
         <v>22</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D14">
         <v>67</v>
@@ -1383,7 +1394,7 @@
         <v>26</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D15">
         <v>73.8</v>
@@ -1406,7 +1417,7 @@
         <v>48</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D16">
         <v>59.8</v>
@@ -1452,7 +1463,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D18">
         <v>80.5</v>
@@ -1498,7 +1509,7 @@
         <v>62</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D20">
         <v>60.7</v>
@@ -1544,7 +1555,7 @@
         <v>24</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D22">
         <v>63.5</v>
@@ -1590,7 +1601,7 @@
         <v>19</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D24">
         <v>56.5</v>
@@ -1613,7 +1624,7 @@
         <v>40</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D25">
         <v>61.8</v>
@@ -1636,7 +1647,7 @@
         <v>40</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D26">
         <v>61.5</v>
@@ -1682,7 +1693,7 @@
         <v>28</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D28">
         <v>61.9</v>
@@ -1751,7 +1762,7 @@
         <v>21</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D31">
         <v>62.8</v>
@@ -1820,7 +1831,7 @@
         <v>35</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D34">
         <v>62</v>
@@ -1866,7 +1877,7 @@
         <v>63</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D36">
         <v>60.2</v>
@@ -1889,7 +1900,7 @@
         <v>58</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D37">
         <v>73</v>
@@ -1912,7 +1923,7 @@
         <v>50</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D38">
         <v>68</v>
@@ -1935,7 +1946,7 @@
         <v>46</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D39">
         <v>76</v>
@@ -1958,7 +1969,7 @@
         <v>41</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D40">
         <v>60.5</v>
@@ -2004,7 +2015,7 @@
         <v>30</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D42">
         <v>58</v>
@@ -2027,7 +2038,7 @@
         <v>64</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D43">
         <v>51.5</v>
@@ -2296,8 +2307,11 @@
       <c r="H2">
         <v>21</v>
       </c>
+      <c r="I2">
+        <v>17</v>
+      </c>
       <c r="K2" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2375,7 +2389,7 @@
         <v>17</v>
       </c>
       <c r="K5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2542,7 +2556,7 @@
         <v>27</v>
       </c>
       <c r="K12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2642,16 +2656,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -2665,16 +2679,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2688,16 +2702,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2711,16 +2725,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2734,16 +2748,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2757,16 +2771,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2780,16 +2794,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2803,16 +2817,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2826,16 +2840,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2849,16 +2863,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2918,10 +2932,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
         <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
       </c>
       <c r="D2">
         <v>69.86</v>
@@ -2932,8 +2946,11 @@
       <c r="H2">
         <v>3</v>
       </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
       <c r="K2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2941,7 +2958,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
         <v>67</v>
@@ -2955,8 +2972,11 @@
       <c r="H3">
         <v>4</v>
       </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
       <c r="K3" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2964,10 +2984,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" t="s">
         <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>72</v>
       </c>
       <c r="D4">
         <v>53.07</v>
@@ -2979,7 +2999,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2987,7 +3007,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
         <v>67</v>
@@ -3007,7 +3027,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
         <v>67</v>
@@ -3027,10 +3047,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
         <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
       </c>
       <c r="D7">
         <v>48.99</v>
@@ -3047,10 +3067,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" t="s">
         <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
       </c>
       <c r="D8">
         <v>63.96</v>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77ADC58E-6F4B-4E56-816D-9865C1EE2D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A9B790-7151-41C9-B567-910EE126AD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -2336,6 +2336,9 @@
       <c r="H3">
         <v>23</v>
       </c>
+      <c r="I3">
+        <v>23</v>
+      </c>
       <c r="K3">
         <v>0</v>
       </c>
@@ -2360,6 +2363,9 @@
         <v>1</v>
       </c>
       <c r="H4">
+        <v>24</v>
+      </c>
+      <c r="I4">
         <v>24</v>
       </c>
       <c r="K4">

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A9B790-7151-41C9-B567-910EE126AD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F41193-90DF-484F-926D-B45044908842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
   <si>
     <t>Database No.</t>
   </si>
@@ -347,6 +347,12 @@
   </si>
   <si>
     <t>3-all ('LoadingError'), 4 in total</t>
+  </si>
+  <si>
+    <t>Walk trials C4-C5 (files)</t>
+  </si>
+  <si>
+    <t>Walk trials C1-C3 (files)</t>
   </si>
 </sst>
 </file>
@@ -1040,7 +1046,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -1052,10 +1058,11 @@
     <col min="9" max="9" width="24.33203125" customWidth="1"/>
     <col min="10" max="10" width="19.33203125" customWidth="1"/>
     <col min="11" max="11" width="19.77734375" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" customWidth="1"/>
     <col min="15" max="15" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>57</v>
       </c>
@@ -1075,7 +1082,7 @@
         <v>62</v>
       </c>
       <c r="H1" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="I1" t="s">
         <v>64</v>
@@ -1086,8 +1093,11 @@
       <c r="K1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="N1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1107,10 +1117,13 @@
         <v>1</v>
       </c>
       <c r="H2">
+        <v>15</v>
+      </c>
+      <c r="N2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1130,10 +1143,13 @@
         <v>1</v>
       </c>
       <c r="H3">
+        <v>11</v>
+      </c>
+      <c r="N3">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1153,10 +1169,13 @@
         <v>1</v>
       </c>
       <c r="H4">
+        <v>13</v>
+      </c>
+      <c r="N4">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1176,10 +1195,13 @@
         <v>1</v>
       </c>
       <c r="H5">
+        <v>14</v>
+      </c>
+      <c r="N5">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:14">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1199,10 +1221,13 @@
         <v>0</v>
       </c>
       <c r="H6">
+        <v>15</v>
+      </c>
+      <c r="N6">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1222,10 +1247,13 @@
         <v>1</v>
       </c>
       <c r="H7">
+        <v>13</v>
+      </c>
+      <c r="N7">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:14">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1245,10 +1273,13 @@
         <v>1</v>
       </c>
       <c r="H8">
+        <v>14</v>
+      </c>
+      <c r="N8">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:14">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1268,10 +1299,13 @@
         <v>0</v>
       </c>
       <c r="H9">
+        <v>15</v>
+      </c>
+      <c r="N9">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:14">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1291,10 +1325,13 @@
         <v>0</v>
       </c>
       <c r="H10">
+        <v>15</v>
+      </c>
+      <c r="N10">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:14">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1314,10 +1351,13 @@
         <v>1</v>
       </c>
       <c r="H11">
+        <v>13</v>
+      </c>
+      <c r="N11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:14">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1337,10 +1377,13 @@
         <v>1</v>
       </c>
       <c r="H12">
+        <v>13</v>
+      </c>
+      <c r="N12">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:14">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1360,10 +1403,13 @@
         <v>1</v>
       </c>
       <c r="H13">
+        <v>14</v>
+      </c>
+      <c r="N13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:14">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1383,10 +1429,13 @@
         <v>0</v>
       </c>
       <c r="H14">
+        <v>15</v>
+      </c>
+      <c r="N14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:14">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1406,10 +1455,13 @@
         <v>1</v>
       </c>
       <c r="H15">
+        <v>12</v>
+      </c>
+      <c r="N15">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:14">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1429,10 +1481,13 @@
         <v>1</v>
       </c>
       <c r="H16">
+        <v>15</v>
+      </c>
+      <c r="N16">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:14">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1452,10 +1507,13 @@
         <v>1</v>
       </c>
       <c r="H17">
+        <v>14</v>
+      </c>
+      <c r="N17">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:14">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1475,10 +1533,13 @@
         <v>1</v>
       </c>
       <c r="H18">
+        <v>15</v>
+      </c>
+      <c r="N18">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:14">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1498,10 +1559,13 @@
         <v>1</v>
       </c>
       <c r="H19">
+        <v>15</v>
+      </c>
+      <c r="N19">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:14">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1521,10 +1585,13 @@
         <v>1</v>
       </c>
       <c r="H20">
+        <v>15</v>
+      </c>
+      <c r="N20">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:14">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1544,10 +1611,13 @@
         <v>1</v>
       </c>
       <c r="H21">
+        <v>13</v>
+      </c>
+      <c r="N21">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:14">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1567,10 +1637,13 @@
         <v>1</v>
       </c>
       <c r="H22">
+        <v>13</v>
+      </c>
+      <c r="N22">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:14">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1590,10 +1663,13 @@
         <v>1</v>
       </c>
       <c r="H23">
+        <v>11</v>
+      </c>
+      <c r="N23">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:14">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1613,10 +1689,13 @@
         <v>1</v>
       </c>
       <c r="H24">
+        <v>13</v>
+      </c>
+      <c r="N24">
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:14">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1636,10 +1715,13 @@
         <v>0</v>
       </c>
       <c r="H25">
+        <v>15</v>
+      </c>
+      <c r="N25">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:14">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1659,10 +1741,13 @@
         <v>1</v>
       </c>
       <c r="H26">
+        <v>14</v>
+      </c>
+      <c r="N26">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:14">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1682,10 +1767,13 @@
         <v>0</v>
       </c>
       <c r="H27">
+        <v>15</v>
+      </c>
+      <c r="N27">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:14">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1705,10 +1793,13 @@
         <v>0</v>
       </c>
       <c r="H28">
+        <v>15</v>
+      </c>
+      <c r="N28">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:14">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1728,10 +1819,13 @@
         <v>1</v>
       </c>
       <c r="H29">
+        <v>15</v>
+      </c>
+      <c r="N29">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:14">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1751,10 +1845,13 @@
         <v>1</v>
       </c>
       <c r="H30">
+        <v>13</v>
+      </c>
+      <c r="N30">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:14">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1774,10 +1871,13 @@
         <v>1</v>
       </c>
       <c r="H31">
+        <v>11</v>
+      </c>
+      <c r="N31">
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:14">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1794,13 +1894,16 @@
         <v>1.74</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32">
+        <v>15</v>
+      </c>
+      <c r="N32">
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:14">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1820,10 +1923,13 @@
         <v>0</v>
       </c>
       <c r="H33">
+        <v>15</v>
+      </c>
+      <c r="N33">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:14">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1840,13 +1946,16 @@
         <v>1.7</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
+        <v>15</v>
+      </c>
+      <c r="N34">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:14">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1866,10 +1975,13 @@
         <v>1</v>
       </c>
       <c r="H35">
+        <v>15</v>
+      </c>
+      <c r="N35">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:14">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1889,10 +2001,13 @@
         <v>1</v>
       </c>
       <c r="H36">
+        <v>15</v>
+      </c>
+      <c r="N36">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:14">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1912,10 +2027,13 @@
         <v>1</v>
       </c>
       <c r="H37">
+        <v>14</v>
+      </c>
+      <c r="N37">
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:14">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1935,10 +2053,13 @@
         <v>0</v>
       </c>
       <c r="H38">
+        <v>15</v>
+      </c>
+      <c r="N38">
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:14">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1958,10 +2079,13 @@
         <v>1</v>
       </c>
       <c r="H39">
+        <v>12</v>
+      </c>
+      <c r="N39">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:14">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1981,10 +2105,13 @@
         <v>1</v>
       </c>
       <c r="H40">
+        <v>15</v>
+      </c>
+      <c r="N40">
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:14">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2004,10 +2131,13 @@
         <v>1</v>
       </c>
       <c r="H41">
+        <v>15</v>
+      </c>
+      <c r="N41">
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:14">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2027,10 +2157,13 @@
         <v>1</v>
       </c>
       <c r="H42">
+        <v>14</v>
+      </c>
+      <c r="N42">
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:14">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2050,10 +2183,13 @@
         <v>1</v>
       </c>
       <c r="H43">
+        <v>13</v>
+      </c>
+      <c r="N43">
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:14">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2073,10 +2209,13 @@
         <v>1</v>
       </c>
       <c r="H44">
+        <v>14</v>
+      </c>
+      <c r="N44">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:14">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2096,10 +2235,13 @@
         <v>1</v>
       </c>
       <c r="H45">
+        <v>13</v>
+      </c>
+      <c r="N45">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:14">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2119,10 +2261,13 @@
         <v>1</v>
       </c>
       <c r="H46">
+        <v>13</v>
+      </c>
+      <c r="N46">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:14">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2142,10 +2287,13 @@
         <v>1</v>
       </c>
       <c r="H47">
+        <v>14</v>
+      </c>
+      <c r="N47">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:14">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2165,10 +2313,13 @@
         <v>1</v>
       </c>
       <c r="H48">
+        <v>13</v>
+      </c>
+      <c r="N48">
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:14">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2188,10 +2339,13 @@
         <v>1</v>
       </c>
       <c r="H49">
+        <v>13</v>
+      </c>
+      <c r="N49">
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:14">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2211,10 +2365,13 @@
         <v>1</v>
       </c>
       <c r="H50">
+        <v>14</v>
+      </c>
+      <c r="N50">
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:14">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2234,6 +2391,9 @@
         <v>0</v>
       </c>
       <c r="H51">
+        <v>15</v>
+      </c>
+      <c r="N51">
         <v>10</v>
       </c>
     </row>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F41193-90DF-484F-926D-B45044908842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1DEBBE-F192-4550-9A6E-2862CEA70DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -292,9 +292,6 @@
     <t>Multiple speeds: slow gait, comfortable gait, fast gait</t>
   </si>
   <si>
-    <t>Self-selected spontaneous (C4) and fast (C5)</t>
-  </si>
-  <si>
     <t>A multimodal dataset of human gait at different walking speeds established on injury-free adult participants</t>
   </si>
   <si>
@@ -354,12 +351,15 @@
   <si>
     <t>Walk trials C1-C3 (files)</t>
   </si>
+  <si>
+    <t>0–0.4 m.s−1 (C1), 0.4–0.8 m.s−1 (C2), 0.8–1.2 m.s−1 (C3). Self-selected spontaneous (C4) and fast (C5)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -419,6 +419,13 @@
       <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -442,7 +449,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -459,6 +466,7 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -729,24 +737,24 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="43.2">
+    <row r="2" spans="1:18" ht="72">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2">
         <v>2019</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="G2">
         <v>50</v>
@@ -758,28 +766,28 @@
         <v>26</v>
       </c>
       <c r="J2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" t="s">
         <v>80</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>81</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N2" t="s">
         <v>82</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>84</v>
-      </c>
-      <c r="N2" t="s">
-        <v>83</v>
-      </c>
-      <c r="O2" t="s">
-        <v>85</v>
       </c>
       <c r="P2">
         <v>2</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>86</v>
+      <c r="Q2" s="4" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="43.2">
@@ -1038,6 +1046,7 @@
     <hyperlink ref="R9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="R10" r:id="rId6" location="Bib1" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="R11" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="Q2" r:id="rId8" xr:uid="{44AB234F-BA16-4A5C-A6A5-B63142A430E8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1046,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -1082,7 +1091,7 @@
         <v>62</v>
       </c>
       <c r="H1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I1" t="s">
         <v>64</v>
@@ -1094,7 +1103,7 @@
         <v>66</v>
       </c>
       <c r="N1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1131,7 +1140,7 @@
         <v>48</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D3">
         <v>65.400000000000006</v>
@@ -1157,7 +1166,7 @@
         <v>28</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D4">
         <v>50</v>
@@ -1261,7 +1270,7 @@
         <v>44</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D8">
         <v>65</v>
@@ -1287,7 +1296,7 @@
         <v>30</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D9">
         <v>57.1</v>
@@ -1365,7 +1374,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D12">
         <v>61.3</v>
@@ -1417,7 +1426,7 @@
         <v>22</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D14">
         <v>67</v>
@@ -1443,7 +1452,7 @@
         <v>26</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D15">
         <v>73.8</v>
@@ -1469,7 +1478,7 @@
         <v>48</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D16">
         <v>59.8</v>
@@ -1521,7 +1530,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D18">
         <v>80.5</v>
@@ -1573,7 +1582,7 @@
         <v>62</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D20">
         <v>60.7</v>
@@ -1625,7 +1634,7 @@
         <v>24</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D22">
         <v>63.5</v>
@@ -1677,7 +1686,7 @@
         <v>19</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D24">
         <v>56.5</v>
@@ -1703,7 +1712,7 @@
         <v>40</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D25">
         <v>61.8</v>
@@ -1729,7 +1738,7 @@
         <v>40</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D26">
         <v>61.5</v>
@@ -1781,7 +1790,7 @@
         <v>28</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D28">
         <v>61.9</v>
@@ -1859,7 +1868,7 @@
         <v>21</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D31">
         <v>62.8</v>
@@ -1937,7 +1946,7 @@
         <v>35</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D34">
         <v>62</v>
@@ -1989,7 +1998,7 @@
         <v>63</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D36">
         <v>60.2</v>
@@ -2015,7 +2024,7 @@
         <v>58</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D37">
         <v>73</v>
@@ -2041,7 +2050,7 @@
         <v>50</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D38">
         <v>68</v>
@@ -2067,7 +2076,7 @@
         <v>46</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D39">
         <v>76</v>
@@ -2093,7 +2102,7 @@
         <v>41</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D40">
         <v>60.5</v>
@@ -2145,7 +2154,7 @@
         <v>30</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D42">
         <v>58</v>
@@ -2171,7 +2180,7 @@
         <v>64</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D43">
         <v>51.5</v>
@@ -2395,6 +2404,12 @@
       </c>
       <c r="N51">
         <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="H52" s="8">
+        <f>SUM(H2:H51)</f>
+        <v>696</v>
       </c>
     </row>
   </sheetData>
@@ -2405,7 +2420,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="9" max="9" width="14.109375" customWidth="1"/>
@@ -2471,7 +2486,7 @@
         <v>17</v>
       </c>
       <c r="K2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2769,6 +2784,12 @@
       </c>
       <c r="H14">
         <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="H15" s="8">
+        <f>SUM(H1:H14)</f>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -2779,7 +2800,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="11" max="11" width="19.109375" customWidth="1"/>
@@ -3047,6 +3068,15 @@
         <v>17</v>
       </c>
     </row>
+    <row r="12" spans="1:11">
+      <c r="H12" s="8">
+        <f>SUM(H2:H11)</f>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="H13" s="8"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3055,7 +3085,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="11" max="11" width="24" customWidth="1"/>
@@ -3142,7 +3172,7 @@
         <v>3</v>
       </c>
       <c r="K3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3246,6 +3276,12 @@
       </c>
       <c r="H8">
         <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="H9" s="8">
+        <f>SUM(H1:H8)</f>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1DEBBE-F192-4550-9A6E-2862CEA70DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD54C56-D4C2-4FF0-B3D0-0A3DD8804CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="93">
   <si>
     <t>Database No.</t>
   </si>
@@ -250,16 +250,7 @@
     <t>Calib pose</t>
   </si>
   <si>
-    <t>Walk trials (files)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Usable trials </t>
-  </si>
-  <si>
-    <t>Duration per trials (s)</t>
-  </si>
-  <si>
-    <t>Wrong trials (reason)</t>
   </si>
   <si>
     <t>M</t>
@@ -353,6 +344,18 @@
   </si>
   <si>
     <t>0–0.4 m.s−1 (C1), 0.4–0.8 m.s−1 (C2), 0.8–1.2 m.s−1 (C3). Self-selected spontaneous (C4) and fast (C5)</t>
+  </si>
+  <si>
+    <t>Wrong trials - processing (reason)</t>
+  </si>
+  <si>
+    <t>Wrong trials - visual inspection (reason)</t>
+  </si>
+  <si>
+    <t>Excluded trials (reason: speed / step-width)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walk trials </t>
   </si>
 </sst>
 </file>
@@ -742,19 +745,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C2">
         <v>2019</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G2">
         <v>50</v>
@@ -766,28 +769,28 @@
         <v>26</v>
       </c>
       <c r="J2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M2" t="s">
+        <v>80</v>
+      </c>
+      <c r="N2" t="s">
         <v>79</v>
       </c>
-      <c r="K2" t="s">
-        <v>80</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="O2" t="s">
         <v>81</v>
-      </c>
-      <c r="M2" t="s">
-        <v>83</v>
-      </c>
-      <c r="N2" t="s">
-        <v>82</v>
-      </c>
-      <c r="O2" t="s">
-        <v>84</v>
       </c>
       <c r="P2">
         <v>2</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="43.2">
@@ -807,7 +810,7 @@
         <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G3">
         <v>13</v>
@@ -851,7 +854,7 @@
         <v>19</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G4" s="1">
         <v>10</v>
@@ -1055,23 +1058,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
     <col min="2" max="2" width="10.77734375" customWidth="1"/>
     <col min="3" max="3" width="10.44140625" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
-    <col min="5" max="6" width="12" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" customWidth="1"/>
     <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="9" max="9" width="24.33203125" customWidth="1"/>
-    <col min="10" max="10" width="19.33203125" customWidth="1"/>
-    <col min="11" max="11" width="19.77734375" customWidth="1"/>
-    <col min="14" max="14" width="16.6640625" customWidth="1"/>
-    <col min="15" max="15" width="8.77734375" customWidth="1"/>
+    <col min="9" max="9" width="29.33203125" customWidth="1"/>
+    <col min="10" max="10" width="34.44140625" customWidth="1"/>
+    <col min="11" max="11" width="37.109375" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" customWidth="1"/>
+    <col min="16" max="16" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>57</v>
       </c>
@@ -1091,22 +1097,25 @@
         <v>62</v>
       </c>
       <c r="H1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1" t="s">
         <v>90</v>
       </c>
-      <c r="I1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" t="s">
-        <v>65</v>
-      </c>
       <c r="K1" t="s">
-        <v>66</v>
-      </c>
-      <c r="N1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+        <v>91</v>
+      </c>
+      <c r="L1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1114,7 +1123,7 @@
         <v>31</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D2">
         <v>67</v>
@@ -1128,11 +1137,11 @@
       <c r="H2">
         <v>15</v>
       </c>
-      <c r="N2">
+      <c r="P2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1140,7 +1149,7 @@
         <v>48</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D3">
         <v>65.400000000000006</v>
@@ -1154,11 +1163,11 @@
       <c r="H3">
         <v>11</v>
       </c>
-      <c r="N3">
+      <c r="P3">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1166,7 +1175,7 @@
         <v>28</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D4">
         <v>50</v>
@@ -1180,11 +1189,11 @@
       <c r="H4">
         <v>13</v>
       </c>
-      <c r="N4">
+      <c r="P4">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1192,7 +1201,7 @@
         <v>23</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D5">
         <v>72.5</v>
@@ -1206,11 +1215,11 @@
       <c r="H5">
         <v>14</v>
       </c>
-      <c r="N5">
+      <c r="P5">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1218,7 +1227,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D6">
         <v>73.5</v>
@@ -1232,11 +1241,11 @@
       <c r="H6">
         <v>15</v>
       </c>
-      <c r="N6">
+      <c r="P6">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1244,7 +1253,7 @@
         <v>23</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D7">
         <v>73</v>
@@ -1258,11 +1267,11 @@
       <c r="H7">
         <v>13</v>
       </c>
-      <c r="N7">
+      <c r="P7">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1270,7 +1279,7 @@
         <v>44</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D8">
         <v>65</v>
@@ -1284,11 +1293,11 @@
       <c r="H8">
         <v>14</v>
       </c>
-      <c r="N8">
+      <c r="P8">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1296,7 +1305,7 @@
         <v>30</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D9">
         <v>57.1</v>
@@ -1310,11 +1319,11 @@
       <c r="H9">
         <v>15</v>
       </c>
-      <c r="N9">
+      <c r="P9">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1322,7 +1331,7 @@
         <v>57</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D10">
         <v>86</v>
@@ -1336,11 +1345,11 @@
       <c r="H10">
         <v>15</v>
       </c>
-      <c r="N10">
+      <c r="P10">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1348,7 +1357,7 @@
         <v>59</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D11">
         <v>63.4</v>
@@ -1362,11 +1371,11 @@
       <c r="H11">
         <v>13</v>
       </c>
-      <c r="N11">
+      <c r="P11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1374,7 +1383,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D12">
         <v>61.3</v>
@@ -1388,11 +1397,11 @@
       <c r="H12">
         <v>13</v>
       </c>
-      <c r="N12">
+      <c r="P12">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1400,7 +1409,7 @@
         <v>29</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D13">
         <v>92</v>
@@ -1414,11 +1423,11 @@
       <c r="H13">
         <v>14</v>
       </c>
-      <c r="N13">
+      <c r="P13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1426,7 +1435,7 @@
         <v>22</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D14">
         <v>67</v>
@@ -1440,11 +1449,11 @@
       <c r="H14">
         <v>15</v>
       </c>
-      <c r="N14">
+      <c r="P14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:16">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1452,7 +1461,7 @@
         <v>26</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D15">
         <v>73.8</v>
@@ -1466,11 +1475,11 @@
       <c r="H15">
         <v>12</v>
       </c>
-      <c r="N15">
+      <c r="P15">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1478,7 +1487,7 @@
         <v>48</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D16">
         <v>59.8</v>
@@ -1492,11 +1501,11 @@
       <c r="H16">
         <v>15</v>
       </c>
-      <c r="N16">
+      <c r="P16">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:16">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1504,7 +1513,7 @@
         <v>33</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D17">
         <v>87.5</v>
@@ -1518,11 +1527,11 @@
       <c r="H17">
         <v>14</v>
       </c>
-      <c r="N17">
+      <c r="P17">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:16">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1530,7 +1539,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D18">
         <v>80.5</v>
@@ -1544,11 +1553,11 @@
       <c r="H18">
         <v>15</v>
       </c>
-      <c r="N18">
+      <c r="P18">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:16">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1556,7 +1565,7 @@
         <v>38</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D19">
         <v>89.9</v>
@@ -1570,11 +1579,11 @@
       <c r="H19">
         <v>15</v>
       </c>
-      <c r="N19">
+      <c r="P19">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:16">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1582,7 +1591,7 @@
         <v>62</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D20">
         <v>60.7</v>
@@ -1596,11 +1605,11 @@
       <c r="H20">
         <v>15</v>
       </c>
-      <c r="N20">
+      <c r="P20">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:16">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1608,7 +1617,7 @@
         <v>21</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D21">
         <v>67.2</v>
@@ -1622,11 +1631,11 @@
       <c r="H21">
         <v>13</v>
       </c>
-      <c r="N21">
+      <c r="P21">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:16">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1634,7 +1643,7 @@
         <v>24</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D22">
         <v>63.5</v>
@@ -1648,11 +1657,11 @@
       <c r="H22">
         <v>13</v>
       </c>
-      <c r="N22">
+      <c r="P22">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:16">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1660,7 +1669,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D23">
         <v>89.6</v>
@@ -1674,11 +1683,11 @@
       <c r="H23">
         <v>11</v>
       </c>
-      <c r="N23">
+      <c r="P23">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:16">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1686,7 +1695,7 @@
         <v>19</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D24">
         <v>56.5</v>
@@ -1700,11 +1709,11 @@
       <c r="H24">
         <v>13</v>
       </c>
-      <c r="N24">
+      <c r="P24">
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:16">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1712,7 +1721,7 @@
         <v>40</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D25">
         <v>61.8</v>
@@ -1726,11 +1735,11 @@
       <c r="H25">
         <v>15</v>
       </c>
-      <c r="N25">
+      <c r="P25">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:16">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1738,7 +1747,7 @@
         <v>40</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D26">
         <v>61.5</v>
@@ -1752,11 +1761,11 @@
       <c r="H26">
         <v>14</v>
       </c>
-      <c r="N26">
+      <c r="P26">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:16">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1764,7 +1773,7 @@
         <v>32</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D27">
         <v>72.2</v>
@@ -1778,11 +1787,11 @@
       <c r="H27">
         <v>15</v>
       </c>
-      <c r="N27">
+      <c r="P27">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:16">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1790,7 +1799,7 @@
         <v>28</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D28">
         <v>61.9</v>
@@ -1804,11 +1813,11 @@
       <c r="H28">
         <v>15</v>
       </c>
-      <c r="N28">
+      <c r="P28">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:16">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1816,7 +1825,7 @@
         <v>25</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D29">
         <v>88</v>
@@ -1830,11 +1839,11 @@
       <c r="H29">
         <v>15</v>
       </c>
-      <c r="N29">
+      <c r="P29">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:16">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1842,7 +1851,7 @@
         <v>25</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D30">
         <v>79.5</v>
@@ -1856,11 +1865,11 @@
       <c r="H30">
         <v>13</v>
       </c>
-      <c r="N30">
+      <c r="P30">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:16">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1868,7 +1877,7 @@
         <v>21</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D31">
         <v>62.8</v>
@@ -1882,11 +1891,11 @@
       <c r="H31">
         <v>11</v>
       </c>
-      <c r="N31">
+      <c r="P31">
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:16">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1894,7 +1903,7 @@
         <v>39</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D32">
         <v>74</v>
@@ -1908,11 +1917,11 @@
       <c r="H32">
         <v>15</v>
       </c>
-      <c r="N32">
+      <c r="P32">
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:16">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1920,7 +1929,7 @@
         <v>52</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D33">
         <v>87.2</v>
@@ -1934,11 +1943,11 @@
       <c r="H33">
         <v>15</v>
       </c>
-      <c r="N33">
+      <c r="P33">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:16">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1946,7 +1955,7 @@
         <v>35</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D34">
         <v>62</v>
@@ -1960,11 +1969,11 @@
       <c r="H34">
         <v>15</v>
       </c>
-      <c r="N34">
+      <c r="P34">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:16">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1972,7 +1981,7 @@
         <v>48</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D35">
         <v>89.4</v>
@@ -1986,11 +1995,11 @@
       <c r="H35">
         <v>15</v>
       </c>
-      <c r="N35">
+      <c r="P35">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:16">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1998,7 +2007,7 @@
         <v>63</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D36">
         <v>60.2</v>
@@ -2012,11 +2021,11 @@
       <c r="H36">
         <v>15</v>
       </c>
-      <c r="N36">
+      <c r="P36">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:16">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2024,7 +2033,7 @@
         <v>58</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D37">
         <v>73</v>
@@ -2038,11 +2047,11 @@
       <c r="H37">
         <v>14</v>
       </c>
-      <c r="N37">
+      <c r="P37">
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:16">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2050,7 +2059,7 @@
         <v>50</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D38">
         <v>68</v>
@@ -2064,11 +2073,11 @@
       <c r="H38">
         <v>15</v>
       </c>
-      <c r="N38">
+      <c r="P38">
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:16">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2076,7 +2085,7 @@
         <v>46</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D39">
         <v>76</v>
@@ -2090,11 +2099,11 @@
       <c r="H39">
         <v>12</v>
       </c>
-      <c r="N39">
+      <c r="P39">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:16">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2102,7 +2111,7 @@
         <v>41</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D40">
         <v>60.5</v>
@@ -2116,11 +2125,11 @@
       <c r="H40">
         <v>15</v>
       </c>
-      <c r="N40">
+      <c r="P40">
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:16">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2128,7 +2137,7 @@
         <v>43</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D41">
         <v>95</v>
@@ -2142,11 +2151,11 @@
       <c r="H41">
         <v>15</v>
       </c>
-      <c r="N41">
+      <c r="P41">
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:16">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2154,7 +2163,7 @@
         <v>30</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D42">
         <v>58</v>
@@ -2168,11 +2177,11 @@
       <c r="H42">
         <v>14</v>
       </c>
-      <c r="N42">
+      <c r="P42">
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:16">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2180,7 +2189,7 @@
         <v>64</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D43">
         <v>51.5</v>
@@ -2194,11 +2203,11 @@
       <c r="H43">
         <v>13</v>
       </c>
-      <c r="N43">
+      <c r="P43">
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:16">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2206,7 +2215,7 @@
         <v>51</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D44">
         <v>65.5</v>
@@ -2220,11 +2229,11 @@
       <c r="H44">
         <v>14</v>
       </c>
-      <c r="N44">
+      <c r="P44">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:16">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2232,7 +2241,7 @@
         <v>24</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D45">
         <v>86</v>
@@ -2246,11 +2255,11 @@
       <c r="H45">
         <v>13</v>
       </c>
-      <c r="N45">
+      <c r="P45">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:16">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2258,7 +2267,7 @@
         <v>26</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D46">
         <v>50.8</v>
@@ -2272,11 +2281,11 @@
       <c r="H46">
         <v>13</v>
       </c>
-      <c r="N46">
+      <c r="P46">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:16">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2284,7 +2293,7 @@
         <v>38</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D47">
         <v>81.5</v>
@@ -2298,11 +2307,11 @@
       <c r="H47">
         <v>14</v>
       </c>
-      <c r="N47">
+      <c r="P47">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:16">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2310,7 +2319,7 @@
         <v>42</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D48">
         <v>66.099999999999994</v>
@@ -2324,11 +2333,11 @@
       <c r="H48">
         <v>13</v>
       </c>
-      <c r="N48">
+      <c r="P48">
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:16">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2336,7 +2345,7 @@
         <v>31</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D49">
         <v>74.8</v>
@@ -2350,11 +2359,11 @@
       <c r="H49">
         <v>13</v>
       </c>
-      <c r="N49">
+      <c r="P49">
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:16">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2362,7 +2371,7 @@
         <v>67</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D50">
         <v>98</v>
@@ -2376,11 +2385,11 @@
       <c r="H50">
         <v>14</v>
       </c>
-      <c r="N50">
+      <c r="P50">
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:16">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2388,7 +2397,7 @@
         <v>21</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D51">
         <v>74</v>
@@ -2402,11 +2411,11 @@
       <c r="H51">
         <v>15</v>
       </c>
-      <c r="N51">
+      <c r="P51">
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:16">
       <c r="H52" s="8">
         <f>SUM(H2:H51)</f>
         <v>696</v>
@@ -2420,15 +2429,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="9" max="9" width="14.109375" customWidth="1"/>
-    <col min="10" max="10" width="19.109375" customWidth="1"/>
-    <col min="11" max="11" width="28.33203125" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" customWidth="1"/>
+    <col min="9" max="9" width="30.6640625" customWidth="1"/>
+    <col min="10" max="10" width="33.21875" customWidth="1"/>
+    <col min="11" max="11" width="36.6640625" customWidth="1"/>
+    <col min="12" max="12" width="15.44140625" customWidth="1"/>
+    <col min="14" max="14" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>57</v>
       </c>
@@ -2448,19 +2460,22 @@
         <v>62</v>
       </c>
       <c r="H1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L1" t="s">
         <v>63</v>
       </c>
-      <c r="I1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2468,7 +2483,7 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D2">
         <v>74</v>
@@ -2482,14 +2497,14 @@
       <c r="H2">
         <v>21</v>
       </c>
-      <c r="I2">
+      <c r="J2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L2">
         <v>17</v>
       </c>
-      <c r="K2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2497,7 +2512,7 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D3">
         <v>72</v>
@@ -2511,14 +2526,14 @@
       <c r="H3">
         <v>23</v>
       </c>
-      <c r="I3">
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="L3">
         <v>23</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2526,7 +2541,7 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D4">
         <v>80</v>
@@ -2540,14 +2555,14 @@
       <c r="H4">
         <v>24</v>
       </c>
-      <c r="I4">
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="L4">
         <v>24</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2555,7 +2570,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D5">
         <v>60</v>
@@ -2569,11 +2584,11 @@
       <c r="H5">
         <v>17</v>
       </c>
-      <c r="K5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="J5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2581,7 +2596,7 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D6">
         <v>71</v>
@@ -2596,7 +2611,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2604,7 +2619,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D7">
         <v>65</v>
@@ -2619,7 +2634,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2627,7 +2642,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D8">
         <v>72</v>
@@ -2642,7 +2657,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:12">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2650,7 +2665,7 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D9">
         <v>85</v>
@@ -2665,7 +2680,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:12">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2673,7 +2688,7 @@
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D10">
         <v>76</v>
@@ -2688,7 +2703,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:12">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2696,7 +2711,7 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D11">
         <v>80</v>
@@ -2710,11 +2725,11 @@
       <c r="H11">
         <v>23</v>
       </c>
-      <c r="K11">
+      <c r="J11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:12">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2722,7 +2737,7 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D12">
         <v>75</v>
@@ -2736,11 +2751,11 @@
       <c r="H12">
         <v>27</v>
       </c>
-      <c r="K12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="J12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2748,7 +2763,7 @@
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D13">
         <v>80</v>
@@ -2763,7 +2778,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:12">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2771,7 +2786,7 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D14">
         <v>58</v>
@@ -2786,7 +2801,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:12">
       <c r="H15" s="8">
         <f>SUM(H1:H14)</f>
         <v>302</v>
@@ -2800,13 +2815,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="11" max="11" width="19.109375" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" customWidth="1"/>
+    <col min="9" max="9" width="28.88671875" customWidth="1"/>
+    <col min="10" max="10" width="33.21875" customWidth="1"/>
+    <col min="11" max="11" width="36.6640625" customWidth="1"/>
+    <col min="12" max="12" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>57</v>
       </c>
@@ -2826,33 +2845,36 @@
         <v>62</v>
       </c>
       <c r="H1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L1" t="s">
         <v>63</v>
       </c>
-      <c r="I1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -2861,21 +2883,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2884,21 +2906,21 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2907,21 +2929,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2930,21 +2952,21 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2953,21 +2975,21 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2976,21 +2998,21 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2999,21 +3021,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:12">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3022,21 +3044,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:12">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3045,21 +3067,21 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:12">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -3068,13 +3090,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:12">
       <c r="H12" s="8">
         <f>SUM(H2:H11)</f>
         <v>167</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:12">
       <c r="H13" s="8"/>
     </row>
   </sheetData>
@@ -3085,13 +3107,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" customWidth="1"/>
+    <col min="9" max="9" width="29.77734375" customWidth="1"/>
+    <col min="10" max="10" width="34" customWidth="1"/>
+    <col min="11" max="11" width="36.77734375" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>57</v>
       </c>
@@ -3111,27 +3137,30 @@
         <v>62</v>
       </c>
       <c r="H1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L1" t="s">
         <v>63</v>
       </c>
-      <c r="I1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D2">
         <v>69.86</v>
@@ -3142,22 +3171,22 @@
       <c r="H2">
         <v>3</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="s">
+        <v>69</v>
+      </c>
+      <c r="L2">
         <v>0</v>
       </c>
-      <c r="K2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D3">
         <v>66.680000000000007</v>
@@ -3168,22 +3197,22 @@
       <c r="H3">
         <v>4</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L3">
         <v>3</v>
       </c>
-      <c r="K3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D4">
         <v>53.07</v>
@@ -3194,19 +3223,19 @@
       <c r="H4">
         <v>3</v>
       </c>
-      <c r="K4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="I4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D5">
         <v>71.67</v>
@@ -3218,15 +3247,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D6">
         <v>90.7</v>
@@ -3238,15 +3267,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D7">
         <v>48.99</v>
@@ -3258,15 +3287,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D8">
         <v>63.96</v>
@@ -3278,7 +3307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:12">
       <c r="H9" s="8">
         <f>SUM(H1:H8)</f>
         <v>18</v>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD54C56-D4C2-4FF0-B3D0-0A3DD8804CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3759B50E-66CA-4D62-9A7B-EB7BDC3280A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1072,7 +1072,7 @@
     <col min="9" max="9" width="29.33203125" customWidth="1"/>
     <col min="10" max="10" width="34.44140625" customWidth="1"/>
     <col min="11" max="11" width="37.109375" customWidth="1"/>
-    <col min="12" max="12" width="15.6640625" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" customWidth="1"/>
     <col min="13" max="13" width="8.77734375" customWidth="1"/>
     <col min="16" max="16" width="16.6640625" customWidth="1"/>
   </cols>
@@ -1137,6 +1137,9 @@
       <c r="H2">
         <v>15</v>
       </c>
+      <c r="L2">
+        <v>9</v>
+      </c>
       <c r="P2">
         <v>10</v>
       </c>
@@ -1163,6 +1166,9 @@
       <c r="H3">
         <v>11</v>
       </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
       <c r="P3">
         <v>9</v>
       </c>
@@ -1189,6 +1195,9 @@
       <c r="H4">
         <v>13</v>
       </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
       <c r="P4">
         <v>9</v>
       </c>
@@ -1215,6 +1224,9 @@
       <c r="H5">
         <v>14</v>
       </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
       <c r="P5">
         <v>9</v>
       </c>
@@ -1241,6 +1253,9 @@
       <c r="H6">
         <v>15</v>
       </c>
+      <c r="L6">
+        <v>6</v>
+      </c>
       <c r="P6">
         <v>10</v>
       </c>
@@ -1267,6 +1282,9 @@
       <c r="H7">
         <v>13</v>
       </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
       <c r="P7">
         <v>9</v>
       </c>
@@ -1293,6 +1311,9 @@
       <c r="H8">
         <v>14</v>
       </c>
+      <c r="L8">
+        <v>4</v>
+      </c>
       <c r="P8">
         <v>9</v>
       </c>
@@ -1319,6 +1340,9 @@
       <c r="H9">
         <v>15</v>
       </c>
+      <c r="L9">
+        <v>9</v>
+      </c>
       <c r="P9">
         <v>10</v>
       </c>
@@ -1345,6 +1369,9 @@
       <c r="H10">
         <v>15</v>
       </c>
+      <c r="L10">
+        <v>9</v>
+      </c>
       <c r="P10">
         <v>10</v>
       </c>
@@ -1370,6 +1397,9 @@
       </c>
       <c r="H11">
         <v>13</v>
+      </c>
+      <c r="L11">
+        <v>4</v>
       </c>
       <c r="P11">
         <v>9</v>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3759B50E-66CA-4D62-9A7B-EB7BDC3280A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C030D6DE-5098-41C9-B831-0E035D95FD20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3050,6 +3050,9 @@
       <c r="H8">
         <v>15</v>
       </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
@@ -3072,6 +3075,9 @@
       </c>
       <c r="H9">
         <v>15</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:12">

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C030D6DE-5098-41C9-B831-0E035D95FD20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49931A1C-06FC-4BCE-92DB-2F6EA8A12911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="DB1" sheetId="2" r:id="rId2"/>
     <sheet name="DB2" sheetId="3" r:id="rId3"/>
-    <sheet name="DB3" sheetId="4" r:id="rId4"/>
-    <sheet name="DB4" sheetId="5" r:id="rId5"/>
+    <sheet name="DB3" sheetId="6" r:id="rId4"/>
+    <sheet name="DB4" sheetId="7" r:id="rId5"/>
+    <sheet name="DB Grouvel" sheetId="4" r:id="rId6"/>
+    <sheet name="DB Han" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="94">
   <si>
     <t>Database No.</t>
   </si>
@@ -356,6 +358,9 @@
   </si>
   <si>
     <t xml:space="preserve">Walk trials </t>
+  </si>
+  <si>
+    <t>Simonlehner</t>
   </si>
 </sst>
 </file>
@@ -430,12 +435,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -452,7 +463,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -470,6 +481,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -665,7 +677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.77734375" customWidth="1"/>
@@ -837,95 +849,17 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="46.8">
-      <c r="A4">
+    <row r="4" spans="1:18">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4">
-        <v>2023</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G4" s="1">
-        <v>10</v>
-      </c>
-      <c r="H4" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="9">
         <v>4</v>
-      </c>
-      <c r="I4" s="1">
-        <v>6</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="43.2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5">
-        <v>2023</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="1">
-        <v>7</v>
-      </c>
-      <c r="H5" s="1">
-        <v>4</v>
-      </c>
-      <c r="I5" s="1">
-        <v>3</v>
-      </c>
-      <c r="J5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" t="s">
-        <v>37</v>
-      </c>
-      <c r="O5" s="1">
-        <v>96</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1040,12 +974,97 @@
         <v>56</v>
       </c>
     </row>
+    <row r="12" spans="1:18" ht="46.8">
+      <c r="B12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12">
+        <v>2023</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>4</v>
+      </c>
+      <c r="I12" s="1">
+        <v>6</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="43.2">
+      <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13">
+        <v>2023</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="1">
+        <v>7</v>
+      </c>
+      <c r="H13" s="1">
+        <v>4</v>
+      </c>
+      <c r="I13" s="1">
+        <v>3</v>
+      </c>
+      <c r="J13" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" t="s">
+        <v>36</v>
+      </c>
+      <c r="L13" t="s">
+        <v>37</v>
+      </c>
+      <c r="O13" s="1">
+        <v>96</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="R3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="R4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="Q5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="R5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="R12" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="Q13" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="R13" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="R9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="R10" r:id="rId6" location="Bib1" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="R11" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
@@ -2844,6 +2863,102 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3518C62A-2ABA-4532-ADB0-E26CA60F7C0C}">
+  <dimension ref="A1:P1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5634500B-8BBC-4D8B-92B7-7498A6AEDFBA}">
+  <dimension ref="A1:P1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -3141,7 +3256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L9"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49931A1C-06FC-4BCE-92DB-2F6EA8A12911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3450F48-C74F-480D-9B75-F88F06CADCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1088,9 +1088,9 @@
     <col min="6" max="6" width="5.33203125" customWidth="1"/>
     <col min="7" max="7" width="11.88671875" customWidth="1"/>
     <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="9" max="9" width="29.33203125" customWidth="1"/>
-    <col min="10" max="10" width="34.44140625" customWidth="1"/>
-    <col min="11" max="11" width="37.109375" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="16.77734375" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="9.33203125" customWidth="1"/>
     <col min="13" max="13" width="8.77734375" customWidth="1"/>
     <col min="16" max="16" width="16.6640625" customWidth="1"/>
@@ -1157,7 +1157,7 @@
         <v>15</v>
       </c>
       <c r="L2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P2">
         <v>10</v>
@@ -1244,7 +1244,7 @@
         <v>14</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>9</v>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3450F48-C74F-480D-9B75-F88F06CADCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56767C10-220C-4409-9C20-B0CC92373D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="95">
   <si>
     <t>Database No.</t>
   </si>
@@ -361,6 +361,9 @@
   </si>
   <si>
     <t>Simonlehner</t>
+  </si>
+  <si>
+    <t>"ID not run" for the others</t>
   </si>
 </sst>
 </file>
@@ -1156,6 +1159,9 @@
       <c r="H2">
         <v>15</v>
       </c>
+      <c r="I2" t="s">
+        <v>94</v>
+      </c>
       <c r="L2">
         <v>8</v>
       </c>
@@ -1185,6 +1191,9 @@
       <c r="H3">
         <v>11</v>
       </c>
+      <c r="I3" t="s">
+        <v>94</v>
+      </c>
       <c r="L3">
         <v>4</v>
       </c>
@@ -1214,6 +1223,9 @@
       <c r="H4">
         <v>13</v>
       </c>
+      <c r="I4" t="s">
+        <v>94</v>
+      </c>
       <c r="L4">
         <v>1</v>
       </c>
@@ -1243,6 +1255,9 @@
       <c r="H5">
         <v>14</v>
       </c>
+      <c r="I5" t="s">
+        <v>94</v>
+      </c>
       <c r="L5">
         <v>6</v>
       </c>
@@ -1272,6 +1287,9 @@
       <c r="H6">
         <v>15</v>
       </c>
+      <c r="I6" t="s">
+        <v>94</v>
+      </c>
       <c r="L6">
         <v>6</v>
       </c>
@@ -1301,6 +1319,9 @@
       <c r="H7">
         <v>13</v>
       </c>
+      <c r="I7" t="s">
+        <v>94</v>
+      </c>
       <c r="L7">
         <v>8</v>
       </c>
@@ -1330,6 +1351,9 @@
       <c r="H8">
         <v>14</v>
       </c>
+      <c r="I8" t="s">
+        <v>94</v>
+      </c>
       <c r="L8">
         <v>4</v>
       </c>
@@ -1359,6 +1383,9 @@
       <c r="H9">
         <v>15</v>
       </c>
+      <c r="I9" t="s">
+        <v>94</v>
+      </c>
       <c r="L9">
         <v>9</v>
       </c>
@@ -1388,6 +1415,9 @@
       <c r="H10">
         <v>15</v>
       </c>
+      <c r="I10" t="s">
+        <v>94</v>
+      </c>
       <c r="L10">
         <v>9</v>
       </c>
@@ -1416,6 +1446,9 @@
       </c>
       <c r="H11">
         <v>13</v>
+      </c>
+      <c r="I11" t="s">
+        <v>94</v>
       </c>
       <c r="L11">
         <v>4</v>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56767C10-220C-4409-9C20-B0CC92373D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E090A3D7-8968-4926-9F35-EF4FB270876D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="95">
   <si>
     <t>Database No.</t>
   </si>
@@ -2897,7 +2897,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3518C62A-2ABA-4532-ADB0-E26CA60F7C0C}">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2936,6 +2936,178 @@
       </c>
       <c r="P1" t="s">
         <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6">
+        <v>61</v>
+      </c>
+      <c r="E6">
+        <v>167</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7">
+        <v>71.8</v>
+      </c>
+      <c r="E7">
+        <v>174</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8">
+        <v>100.5</v>
+      </c>
+      <c r="E8">
+        <v>182</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9">
+        <v>60.7</v>
+      </c>
+      <c r="E9">
+        <v>165</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,23 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shahzaibali/Desktop/TeamProject/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEB6682-670E-1D46-BC25-19AC66065210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Main" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="DB1" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="DB2" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="DB3" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="DB4" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="DB Grouvel" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="DB Han" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Main" sheetId="1" r:id="rId1"/>
+    <sheet name="DB1" sheetId="2" r:id="rId2"/>
+    <sheet name="DB2" sheetId="3" r:id="rId3"/>
+    <sheet name="DB3" sheetId="4" r:id="rId4"/>
+    <sheet name="DB4" sheetId="5" r:id="rId5"/>
+    <sheet name="DB Grouvel" sheetId="6" r:id="rId6"/>
+    <sheet name="DB Han" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -26,75 +42,75 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="95">
-  <si>
-    <t xml:space="preserve">Database No.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Authors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Year of Publication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Database Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walking Type (overground or threadmill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Participants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Female P.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Male P.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Height range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weight range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geographical Region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trials per Participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No. Markers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No. Force Plates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File Download Link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schreiber &amp; Moissenet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A multimodal dataset of human gait at different walking speeds established on injury-free adult participants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overground</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0–0.4 m.s−1 (C1), 0.4–0.8 m.s−1 (C2), 0.8–1.2 m.s−1 (C3). Self-selected spontaneous (C4) and fast (C5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19-67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74 ± 0.09 m</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="97">
+  <si>
+    <t>Database No.</t>
+  </si>
+  <si>
+    <t>Authors</t>
+  </si>
+  <si>
+    <t>Year of Publication</t>
+  </si>
+  <si>
+    <t>Database Name</t>
+  </si>
+  <si>
+    <t>Walking Type (overground or threadmill)</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>Participants</t>
+  </si>
+  <si>
+    <t>Female P.</t>
+  </si>
+  <si>
+    <t>Male P.</t>
+  </si>
+  <si>
+    <t>Age range</t>
+  </si>
+  <si>
+    <t>Height range</t>
+  </si>
+  <si>
+    <t>Weight range</t>
+  </si>
+  <si>
+    <t>Geographical Region</t>
+  </si>
+  <si>
+    <t>Trials per Participant</t>
+  </si>
+  <si>
+    <t>No. Markers</t>
+  </si>
+  <si>
+    <t>No. Force Plates</t>
+  </si>
+  <si>
+    <t>File Download Link</t>
+  </si>
+  <si>
+    <t>Schreiber &amp; Moissenet</t>
+  </si>
+  <si>
+    <t>A multimodal dataset of human gait at different walking speeds established on injury-free adult participants</t>
+  </si>
+  <si>
+    <t>Overground</t>
+  </si>
+  <si>
+    <t>0–0.4 m.s−1 (C1), 0.4–0.8 m.s−1 (C2), 0.8–1.2 m.s−1 (C3). Self-selected spontaneous (C4) and fast (C5)</t>
+  </si>
+  <si>
+    <t>19-67</t>
+  </si>
+  <si>
+    <t>1.74 ± 0.09 m</t>
   </si>
   <si>
     <r>
@@ -112,7 +128,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="EuclidSymbol"/>
-        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">± </t>
@@ -122,122 +137,121 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="MinionPro"/>
-        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">12.3 kg </t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Luxembourg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 trials each with 5 different speeds</t>
+    <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>5 trials each with 5 different speeds</t>
   </si>
   <si>
     <t xml:space="preserve">52 reflective markers </t>
   </si>
   <si>
-    <t xml:space="preserve">https://figshare.com/articles/dataset/A_multimodal_dataset_of_human_gait_at_different_walking_speeds/7734767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dataset of walking and running biomechanics with different step widths across different speeds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preferred &amp; step widths</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20–25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165-185 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55-85 kg</t>
+    <t>https://figshare.com/articles/dataset/A_multimodal_dataset_of_human_gait_at_different_walking_speeds/7734767</t>
+  </si>
+  <si>
+    <t>Wang</t>
+  </si>
+  <si>
+    <t>Dataset of walking and running biomechanics with different step widths across different speeds</t>
+  </si>
+  <si>
+    <t>Preferred &amp; step widths</t>
+  </si>
+  <si>
+    <t>20–25</t>
+  </si>
+  <si>
+    <t>165-185 cm</t>
+  </si>
+  <si>
+    <t>55-85 kg</t>
   </si>
   <si>
     <t xml:space="preserve">38 cutaneous reflective markers </t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.nature.com/articles/s41597-025-05113-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simonlehner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jiwei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K2MUSE: A human lower limb multimodal dataset under diverse conditions for facilitating rehabilitation robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threadmill, Different inclines (0 LG, +/- 5, and +/- 10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5 m/s, 1.0 m/s, and 1.5 m/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://arxiv.org/abs/2504.14602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vielemeyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Full-Body Motion Capture Gait Dataset of Healthy Young Adults Walking Ramps Up and Down</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ramp with inclinations 0°, 7.5°, 10°, up &amp; down</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preferred / self-selected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.nature.com/articles/s41597-025-06535-y#Bib1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riglet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3D motion analysis dataset of healthy young adult volunteers walking and running on overground and treadmill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overground and Treadmill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slow, comfortable &amp; fast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 -41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73 ± 0.09 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.2 ± 11.1 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://springernature.figshare.com/collections/3D_motion_analysis_dataset_of_healthy_young_adult_volunteers_walking_and_running_on_overground_and_treadmill/7056797?utm_source=chatgpt.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grouvel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A dataset of asymptomatic human gait and movements obtained from markers, IMUs, insoles and force plates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multiple speeds: slow gait, comfortable gait, fast gait</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7 ± 6.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74 ± 0.06 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.0 ± 13.9 kg</t>
+    <t>https://www.nature.com/articles/s41597-025-05113-6</t>
+  </si>
+  <si>
+    <t>Simonlehner</t>
+  </si>
+  <si>
+    <t>Jiwei</t>
+  </si>
+  <si>
+    <t>K2MUSE: A human lower limb multimodal dataset under diverse conditions for facilitating rehabilitation robotics</t>
+  </si>
+  <si>
+    <t>Threadmill, Different inclines (0 LG, +/- 5, and +/- 10)</t>
+  </si>
+  <si>
+    <t>0.5 m/s, 1.0 m/s, and 1.5 m/s</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2504.14602</t>
+  </si>
+  <si>
+    <t>Vielemeyer</t>
+  </si>
+  <si>
+    <t>A Full-Body Motion Capture Gait Dataset of Healthy Young Adults Walking Ramps Up and Down</t>
+  </si>
+  <si>
+    <t>ramp with inclinations 0°, 7.5°, 10°, up &amp; down</t>
+  </si>
+  <si>
+    <t>Preferred / self-selected</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41597-025-06535-y#Bib1</t>
+  </si>
+  <si>
+    <t>Riglet</t>
+  </si>
+  <si>
+    <t>3D motion analysis dataset of healthy young adult volunteers walking and running on overground and treadmill</t>
+  </si>
+  <si>
+    <t>Overground and Treadmill</t>
+  </si>
+  <si>
+    <t>Slow, comfortable &amp; fast</t>
+  </si>
+  <si>
+    <t>21 -41</t>
+  </si>
+  <si>
+    <t>1.73 ± 0.09 m</t>
+  </si>
+  <si>
+    <t>68.2 ± 11.1 kg</t>
+  </si>
+  <si>
+    <t>https://springernature.figshare.com/collections/3D_motion_analysis_dataset_of_healthy_young_adult_volunteers_walking_and_running_on_overground_and_treadmill/7056797?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>Grouvel</t>
+  </si>
+  <si>
+    <t>A dataset of asymptomatic human gait and movements obtained from markers, IMUs, insoles and force plates</t>
+  </si>
+  <si>
+    <t>Multiple speeds: slow gait, comfortable gait, fast gait</t>
+  </si>
+  <si>
+    <t>29.7 ± 6.4</t>
+  </si>
+  <si>
+    <t>1.74 ± 0.06 m</t>
+  </si>
+  <si>
+    <t>68.0 ± 13.9 kg</t>
   </si>
   <si>
     <r>
@@ -258,118 +272,120 @@
         <family val="1"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">37 cutaneous markers, 32 cluster markers</t>
+      <t>37 cutaneous markers, 32 cluster markers</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">https://www.nature.com/articles/s41597-023-02077-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Han</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GroundLink: A Dataset Unifying Human Body Movement and Ground Reaction Dynamics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18-32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5-2 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47-91 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://csr.bu.edu/groundlink/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://dl.acm.org/doi/epdf/10.1145/3610548.3618247</t>
+    <t>https://www.nature.com/articles/s41597-023-02077-3</t>
+  </si>
+  <si>
+    <t>Han</t>
+  </si>
+  <si>
+    <t>GroundLink: A Dataset Unifying Human Body Movement and Ground Reaction Dynamics</t>
+  </si>
+  <si>
+    <t>18-32</t>
+  </si>
+  <si>
+    <t>1.5-2 m</t>
+  </si>
+  <si>
+    <t>47-91 kg</t>
+  </si>
+  <si>
+    <t>https://csr.bu.edu/groundlink/</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/epdf/10.1145/3610548.3618247</t>
   </si>
   <si>
     <t xml:space="preserve">Participant </t>
   </si>
   <si>
-    <t xml:space="preserve">Age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weight (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Height (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calib pose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walk trials C1-C3 (files)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wrong trials - processing (reason)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wrong trials - visual inspection (reason)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excluded trials (reason: speed / step-width)</t>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Weight (kg)</t>
+  </si>
+  <si>
+    <t>Height (m)</t>
+  </si>
+  <si>
+    <t>Calib pose</t>
+  </si>
+  <si>
+    <t>Walk trials C1-C3 (files)</t>
+  </si>
+  <si>
+    <t>Wrong trials - processing (reason)</t>
+  </si>
+  <si>
+    <t>Wrong trials - visual inspection (reason)</t>
+  </si>
+  <si>
+    <t>Excluded trials (reason: speed / step-width)</t>
   </si>
   <si>
     <t xml:space="preserve">Usable trials </t>
   </si>
   <si>
-    <t xml:space="preserve">Walk trials C4-C5 (files)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"ID not run" for the others</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W</t>
+    <t>Walk trials C4-C5 (files)</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>"ID not run" for the others</t>
+  </si>
+  <si>
+    <t>W</t>
   </si>
   <si>
     <t xml:space="preserve">Walk trials </t>
   </si>
   <si>
-    <t xml:space="preserve">3-all ('LoadingError'), 4 in total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T02_-130 (MarkerFitterError)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T04_Cal_relabeled (missing GRF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">na</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1:3 (No ID)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (1st half No ID, 2nd half wrong)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No ID</t>
+    <t>3-all ('LoadingError'), 4 in total</t>
+  </si>
+  <si>
+    <t>T02_-130 (MarkerFitterError)</t>
+  </si>
+  <si>
+    <t>T04_Cal_relabeled (missing GRF)</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>1:3 (No ID)</t>
+  </si>
+  <si>
+    <t>4 (1st half No ID, 2nd half wrong)</t>
+  </si>
+  <si>
+    <t>No ID</t>
+  </si>
+  <si>
+    <t>Mass</t>
+  </si>
+  <si>
+    <t>Height</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-  </numFmts>
-  <fonts count="12">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -378,22 +394,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -404,18 +405,16 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="EuclidSymbol"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="MinionPro"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
@@ -444,12 +443,27 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -467,7 +481,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -475,94 +489,39 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="22">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellStyleXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="8">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Normal 2" xfId="21"/>
-    <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -621,60 +580,76 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -706,7 +681,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -730,7 +705,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -790,42 +765,41 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="33.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="23.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="28.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="24.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="40.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="29.78"/>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" customWidth="1"/>
+    <col min="4" max="4" width="33.83203125" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="14" max="14" width="28.5" customWidth="1"/>
+    <col min="15" max="15" width="24.5" customWidth="1"/>
+    <col min="16" max="16" width="20" customWidth="1"/>
+    <col min="17" max="17" width="40.83203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="29.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -878,94 +852,94 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+    <row r="2" spans="1:18" ht="80">
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2">
         <v>2019</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2">
         <v>50</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2">
         <v>24</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2">
         <v>26</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" t="s">
         <v>24</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="0" t="n">
+      <c r="P2">
         <v>2</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+    <row r="3" spans="1:18" ht="48">
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3">
         <v>2025</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3">
         <v>13</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="I3" s="1">
         <v>13</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" t="s">
         <v>33</v>
       </c>
       <c r="O3" s="1" t="s">
@@ -975,20 +949,20 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
+    <row r="4" spans="1:18" ht="16">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+    <row r="5" spans="1:18">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:18">
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="G7" s="1"/>
@@ -996,7 +970,7 @@
       <c r="I7" s="1"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:18">
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="G8" s="1"/>
@@ -1004,11 +978,11 @@
       <c r="I8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:18" ht="48">
       <c r="B9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9">
         <v>2025</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -1020,24 +994,24 @@
       <c r="F9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="1">
         <v>30</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="H9" s="1">
         <v>10</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="I9" s="1">
         <v>20</v>
       </c>
-      <c r="R9" s="4" t="s">
+      <c r="R9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:18" ht="48">
       <c r="B10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10">
         <v>2026</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -1049,103 +1023,103 @@
       <c r="F10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G10" s="1">
         <v>13</v>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="H10" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="I10" s="1">
         <v>8</v>
       </c>
       <c r="R10" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="82.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:18" ht="82.5" customHeight="1">
       <c r="B11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11">
         <v>2024</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" t="s">
         <v>49</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="G11" s="1">
         <v>30</v>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="H11" s="1">
         <v>14</v>
       </c>
-      <c r="I11" s="1" t="n">
+      <c r="I11" s="1">
         <v>16</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" t="s">
         <v>51</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="L11" s="6" t="s">
         <v>53</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:18" ht="51">
       <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12">
         <v>2023</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="1" t="n">
+      <c r="G12" s="1">
         <v>10</v>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="H12" s="1">
         <v>4</v>
       </c>
-      <c r="I12" s="1" t="n">
+      <c r="I12" s="1">
         <v>6</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="L12" s="8" t="s">
+      <c r="L12" s="7" t="s">
         <v>60</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="R12" s="5" t="s">
+      <c r="R12" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:18" ht="48">
       <c r="B13" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13">
         <v>2023</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -1157,25 +1131,25 @@
       <c r="F13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="G13" s="1">
         <v>7</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="H13" s="1">
         <v>4</v>
       </c>
-      <c r="I13" s="1" t="n">
+      <c r="I13" s="1">
         <v>3</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" t="s">
         <v>65</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" t="s">
         <v>66</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="L13" t="s">
         <v>67</v>
       </c>
-      <c r="O13" s="1" t="n">
+      <c r="O13" s="1">
         <v>96</v>
       </c>
       <c r="Q13" s="1" t="s">
@@ -1187,2727 +1161,3547 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="Q2" r:id="rId1" display="https://figshare.com/articles/dataset/A_multimodal_dataset_of_human_gait_at_different_walking_speeds/7734767"/>
-    <hyperlink ref="R3" r:id="rId2" display="https://www.nature.com/articles/s41597-025-05113-6"/>
-    <hyperlink ref="R9" r:id="rId3" display="https://arxiv.org/abs/2504.14602"/>
-    <hyperlink ref="R10" r:id="rId4" location="Bib1" display="https://www.nature.com/articles/s41597-025-06535-y#Bib1"/>
-    <hyperlink ref="R11" r:id="rId5" display="https://springernature.figshare.com/collections/3D_motion_analysis_dataset_of_healthy_young_adult_volunteers_walking_and_running_on_overground_and_treadmill/7056797?utm_source=chatgpt.com"/>
-    <hyperlink ref="R12" r:id="rId6" display="https://www.nature.com/articles/s41597-023-02077-3"/>
-    <hyperlink ref="Q13" r:id="rId7" display="https://csr.bu.edu/groundlink/"/>
-    <hyperlink ref="R13" r:id="rId8" display="https://dl.acm.org/doi/epdf/10.1145/3610548.3618247"/>
+    <hyperlink ref="Q2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="R3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="R9" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="R10" r:id="rId4" location="Bib1" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="R11" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="R12" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="Q13" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="R13" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
   </hyperlinks>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="5.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16.67"/>
+    <col min="1" max="1" width="10.1640625" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" customWidth="1"/>
+    <col min="16" max="16" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:16">
+      <c r="A1" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>77</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>78</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>79</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" t="s">
         <v>80</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0" t="n">
+    <row r="2" spans="1:16" ht="16">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>31</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" s="0" t="n">
+      <c r="C2" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2">
         <v>67</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2">
         <v>1.66</v>
       </c>
-      <c r="G2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="0" t="n">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
         <v>15</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" t="s">
         <v>83</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="L2">
         <v>8</v>
       </c>
-      <c r="P2" s="0" t="n">
+      <c r="P2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+    <row r="3" spans="1:16" ht="16">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3">
         <v>48</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="0" t="n">
-        <v>65.4</v>
-      </c>
-      <c r="E3" s="0" t="n">
+      <c r="D3">
+        <v>65.400000000000006</v>
+      </c>
+      <c r="E3">
         <v>1.64</v>
       </c>
-      <c r="G3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="0" t="n">
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
         <v>11</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" t="s">
         <v>83</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3">
         <v>4</v>
       </c>
-      <c r="P3" s="0" t="n">
+      <c r="P3">
         <v>9</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+    <row r="4" spans="1:16" ht="16">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4">
         <v>28</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4">
         <v>50</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4">
         <v>1.56</v>
       </c>
-      <c r="G4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="0" t="n">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>13</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" t="s">
         <v>83</v>
       </c>
-      <c r="L4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" s="0" t="n">
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="P4">
         <v>9</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+    <row r="5" spans="1:16" ht="16">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5">
         <v>23</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" s="0" t="n">
+      <c r="C5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5">
         <v>72.5</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5">
         <v>1.77</v>
       </c>
-      <c r="G5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="0" t="n">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
         <v>14</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" t="s">
         <v>83</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5">
         <v>6</v>
       </c>
-      <c r="P5" s="0" t="n">
+      <c r="P5">
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+    <row r="6" spans="1:16" ht="16">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6">
         <v>25</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="0" t="n">
+      <c r="C6" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6">
         <v>73.5</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6">
         <v>1.83</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6">
         <v>15</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" t="s">
         <v>83</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6">
         <v>6</v>
       </c>
-      <c r="P6" s="0" t="n">
+      <c r="P6">
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+    <row r="7" spans="1:16" ht="16">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7">
         <v>23</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" s="0" t="n">
+      <c r="C7" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7">
         <v>73</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7">
         <v>1.76</v>
       </c>
-      <c r="G7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="0" t="n">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
         <v>13</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" t="s">
         <v>83</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7">
         <v>8</v>
       </c>
-      <c r="P7" s="0" t="n">
+      <c r="P7">
         <v>9</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+    <row r="8" spans="1:16" ht="16">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8">
         <v>44</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8">
         <v>65</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8">
         <v>1.69</v>
       </c>
-      <c r="G8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="0" t="n">
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
         <v>14</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" t="s">
         <v>83</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="L8">
         <v>4</v>
       </c>
-      <c r="P8" s="0" t="n">
+      <c r="P8">
         <v>9</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+    <row r="9" spans="1:16" ht="16">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9">
         <v>30</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9">
         <v>57.1</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9">
         <v>1.66</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9">
         <v>0</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9">
         <v>15</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" t="s">
         <v>83</v>
       </c>
-      <c r="L9" s="0" t="n">
+      <c r="L9">
         <v>9</v>
       </c>
-      <c r="P9" s="0" t="n">
+      <c r="P9">
         <v>10</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+    <row r="10" spans="1:16" ht="16">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10">
         <v>57</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" s="0" t="n">
+      <c r="C10" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10">
         <v>86</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10">
         <v>1.88</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10">
         <v>0</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10">
         <v>15</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" t="s">
         <v>83</v>
       </c>
-      <c r="L10" s="0" t="n">
+      <c r="L10">
         <v>9</v>
       </c>
-      <c r="P10" s="0" t="n">
+      <c r="P10">
         <v>10</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+    <row r="11" spans="1:16" ht="16">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11">
         <v>59</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" s="0" t="n">
+      <c r="C11" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11">
         <v>63.4</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11">
         <v>1.8</v>
       </c>
-      <c r="G11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="0" t="n">
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
         <v>13</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" t="s">
         <v>83</v>
       </c>
-      <c r="L11" s="0" t="n">
+      <c r="L11">
         <v>4</v>
       </c>
-      <c r="P11" s="0" t="n">
+      <c r="P11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+    <row r="12" spans="1:16" ht="16">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12">
         <v>26</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12">
         <v>61.3</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12">
         <v>1.7</v>
       </c>
-      <c r="G12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="0" t="n">
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
         <v>13</v>
       </c>
-      <c r="P12" s="0" t="n">
+      <c r="P12">
         <v>9</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+    <row r="13" spans="1:16" ht="16">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13">
         <v>29</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" s="0" t="n">
+      <c r="C13" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13">
         <v>92</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13">
         <v>1.8</v>
       </c>
-      <c r="G13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="0" t="n">
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
         <v>14</v>
       </c>
-      <c r="P13" s="0" t="n">
+      <c r="P13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+    <row r="14" spans="1:16" ht="16">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14">
         <v>22</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D14" s="0" t="n">
+      <c r="D14">
         <v>67</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14">
         <v>1.58</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="G14">
         <v>0</v>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="H14">
         <v>15</v>
       </c>
-      <c r="P14" s="0" t="n">
+      <c r="P14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+    <row r="15" spans="1:16" ht="16">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15">
         <v>26</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15">
         <v>73.8</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15">
         <v>1.76</v>
       </c>
-      <c r="G15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="0" t="n">
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
         <v>12</v>
       </c>
-      <c r="P15" s="0" t="n">
+      <c r="P15">
         <v>8</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+    <row r="16" spans="1:16" ht="16">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16">
         <v>48</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16">
         <v>59.8</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16">
         <v>1.71</v>
       </c>
-      <c r="G16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="0" t="n">
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
         <v>15</v>
       </c>
-      <c r="P16" s="0" t="n">
+      <c r="P16">
         <v>10</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+    <row r="17" spans="1:16" ht="16">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17">
         <v>33</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="0" t="n">
+      <c r="C17" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17">
         <v>87.5</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17">
         <v>1.92</v>
       </c>
-      <c r="G17" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="0" t="n">
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
         <v>14</v>
       </c>
-      <c r="P17" s="0" t="n">
+      <c r="P17">
         <v>8</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+    <row r="18" spans="1:16" ht="16">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18">
         <v>31</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="0" t="n">
+      <c r="D18">
         <v>80.5</v>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18">
         <v>1.66</v>
       </c>
-      <c r="G18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="0" t="n">
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
         <v>15</v>
       </c>
-      <c r="P18" s="0" t="n">
+      <c r="P18">
         <v>10</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+    <row r="19" spans="1:16" ht="16">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19">
         <v>38</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="0" t="n">
+      <c r="C19" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19">
         <v>89.9</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19">
         <v>1.89</v>
       </c>
-      <c r="G19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="0" t="n">
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
         <v>15</v>
       </c>
-      <c r="P19" s="0" t="n">
+      <c r="P19">
         <v>8</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+    <row r="20" spans="1:16" ht="16">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20">
         <v>62</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="0" t="n">
+      <c r="D20">
         <v>60.7</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E20">
         <v>1.7</v>
       </c>
-      <c r="G20" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="0" t="n">
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
         <v>15</v>
       </c>
-      <c r="P20" s="0" t="n">
+      <c r="P20">
         <v>10</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+    <row r="21" spans="1:16" ht="16">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21">
         <v>21</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" s="0" t="n">
+      <c r="C21" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21">
         <v>67.2</v>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="E21">
         <v>1.77</v>
       </c>
-      <c r="G21" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="0" t="n">
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
         <v>13</v>
       </c>
-      <c r="P21" s="0" t="n">
+      <c r="P21">
         <v>10</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+    <row r="22" spans="1:16" ht="16">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22">
         <v>24</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="0" t="n">
+      <c r="D22">
         <v>63.5</v>
       </c>
-      <c r="E22" s="0" t="n">
+      <c r="E22">
         <v>1.6</v>
       </c>
-      <c r="G22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="0" t="n">
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
         <v>13</v>
       </c>
-      <c r="P22" s="0" t="n">
+      <c r="P22">
         <v>10</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+    <row r="23" spans="1:16" ht="16">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23">
         <v>21</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" s="0" t="n">
+      <c r="C23" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23">
         <v>89.6</v>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="E23">
         <v>1.84</v>
       </c>
-      <c r="G23" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="0" t="n">
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
         <v>11</v>
       </c>
-      <c r="P23" s="0" t="n">
+      <c r="P23">
         <v>9</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+    <row r="24" spans="1:16" ht="16">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24">
         <v>19</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="0" t="n">
+      <c r="D24">
         <v>56.5</v>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="E24">
         <v>1.55</v>
       </c>
-      <c r="G24" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="0" t="n">
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
         <v>13</v>
       </c>
-      <c r="P24" s="0" t="n">
+      <c r="P24">
         <v>8</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+    <row r="25" spans="1:16" ht="16">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25">
         <v>40</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="0" t="n">
+      <c r="D25">
         <v>61.8</v>
       </c>
-      <c r="E25" s="0" t="n">
+      <c r="E25">
         <v>1.65</v>
       </c>
-      <c r="G25" s="0" t="n">
+      <c r="G25">
         <v>0</v>
       </c>
-      <c r="H25" s="0" t="n">
+      <c r="H25">
         <v>15</v>
       </c>
-      <c r="P25" s="0" t="n">
+      <c r="P25">
         <v>10</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+    <row r="26" spans="1:16" ht="16">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26">
         <v>40</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="0" t="n">
+      <c r="D26">
         <v>61.5</v>
       </c>
-      <c r="E26" s="0" t="n">
+      <c r="E26">
         <v>1.64</v>
       </c>
-      <c r="G26" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="0" t="n">
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
         <v>14</v>
       </c>
-      <c r="P26" s="0" t="n">
+      <c r="P26">
         <v>9</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+    <row r="27" spans="1:16" ht="16">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27">
         <v>32</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D27" s="0" t="n">
+      <c r="C27" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27">
         <v>72.2</v>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="E27">
         <v>1.74</v>
       </c>
-      <c r="G27" s="0" t="n">
+      <c r="G27">
         <v>0</v>
       </c>
-      <c r="H27" s="0" t="n">
+      <c r="H27">
         <v>15</v>
       </c>
-      <c r="P27" s="0" t="n">
+      <c r="P27">
         <v>10</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+    <row r="28" spans="1:16" ht="16">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28">
         <v>28</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D28" s="0" t="n">
+      <c r="D28">
         <v>61.9</v>
       </c>
-      <c r="E28" s="0" t="n">
+      <c r="E28">
         <v>1.64</v>
       </c>
-      <c r="G28" s="0" t="n">
+      <c r="G28">
         <v>0</v>
       </c>
-      <c r="H28" s="0" t="n">
+      <c r="H28">
         <v>15</v>
       </c>
-      <c r="P28" s="0" t="n">
+      <c r="P28">
         <v>10</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
+    <row r="29" spans="1:16" ht="16">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29">
         <v>25</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29" s="0" t="n">
+      <c r="C29" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29">
         <v>88</v>
       </c>
-      <c r="E29" s="0" t="n">
+      <c r="E29">
         <v>1.91</v>
       </c>
-      <c r="G29" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="0" t="n">
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
         <v>15</v>
       </c>
-      <c r="P29" s="0" t="n">
+      <c r="P29">
         <v>10</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
+    <row r="30" spans="1:16" ht="16">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30">
         <v>25</v>
       </c>
-      <c r="C30" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D30" s="0" t="n">
+      <c r="C30" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30">
         <v>79.5</v>
       </c>
-      <c r="E30" s="0" t="n">
+      <c r="E30">
         <v>1.82</v>
       </c>
-      <c r="G30" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="0" t="n">
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
         <v>13</v>
       </c>
-      <c r="P30" s="0" t="n">
+      <c r="P30">
         <v>9</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="n">
+    <row r="31" spans="1:16" ht="16">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31">
         <v>21</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D31" s="0" t="n">
+      <c r="D31">
         <v>62.8</v>
       </c>
-      <c r="E31" s="0" t="n">
+      <c r="E31">
         <v>1.72</v>
       </c>
-      <c r="G31" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="0" t="n">
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
         <v>11</v>
       </c>
-      <c r="P31" s="0" t="n">
+      <c r="P31">
         <v>7</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="n">
+    <row r="32" spans="1:16" ht="16">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32">
         <v>39</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D32" s="0" t="n">
+      <c r="C32" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32">
         <v>74</v>
       </c>
-      <c r="E32" s="0" t="n">
+      <c r="E32">
         <v>1.74</v>
       </c>
-      <c r="G32" s="0" t="n">
+      <c r="G32">
         <v>0</v>
       </c>
-      <c r="H32" s="0" t="n">
+      <c r="H32">
         <v>15</v>
       </c>
-      <c r="P32" s="0" t="n">
+      <c r="P32">
         <v>10</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="n">
+    <row r="33" spans="1:16" ht="16">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33">
         <v>52</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D33" s="0" t="n">
+      <c r="C33" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33">
         <v>87.2</v>
       </c>
-      <c r="E33" s="0" t="n">
+      <c r="E33">
         <v>1.77</v>
       </c>
-      <c r="G33" s="0" t="n">
+      <c r="G33">
         <v>0</v>
       </c>
-      <c r="H33" s="0" t="n">
+      <c r="H33">
         <v>15</v>
       </c>
-      <c r="P33" s="0" t="n">
+      <c r="P33">
         <v>10</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="n">
+    <row r="34" spans="1:16" ht="16">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34">
         <v>35</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D34" s="0" t="n">
+      <c r="D34">
         <v>62</v>
       </c>
-      <c r="E34" s="0" t="n">
+      <c r="E34">
         <v>1.7</v>
       </c>
-      <c r="G34" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="0" t="n">
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
         <v>15</v>
       </c>
-      <c r="P34" s="0" t="n">
+      <c r="P34">
         <v>10</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="n">
+    <row r="35" spans="1:16" ht="16">
+      <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="0" t="n">
+      <c r="B35">
         <v>48</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D35" s="0" t="n">
+      <c r="C35" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D35">
         <v>89.4</v>
       </c>
-      <c r="E35" s="0" t="n">
+      <c r="E35">
         <v>1.9</v>
       </c>
-      <c r="G35" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="0" t="n">
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
         <v>15</v>
       </c>
-      <c r="P35" s="0" t="n">
+      <c r="P35">
         <v>10</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="n">
+    <row r="36" spans="1:16" ht="16">
+      <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36">
         <v>63</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="0" t="n">
+      <c r="D36">
         <v>60.2</v>
       </c>
-      <c r="E36" s="0" t="n">
+      <c r="E36">
         <v>1.66</v>
       </c>
-      <c r="G36" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="0" t="n">
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
         <v>15</v>
       </c>
-      <c r="P36" s="0" t="n">
+      <c r="P36">
         <v>10</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="n">
+    <row r="37" spans="1:16" ht="16">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="0" t="n">
+      <c r="B37">
         <v>58</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D37" s="0" t="n">
+      <c r="D37">
         <v>73</v>
       </c>
-      <c r="E37" s="0" t="n">
+      <c r="E37">
         <v>1.69</v>
       </c>
-      <c r="G37" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="0" t="n">
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
         <v>14</v>
       </c>
-      <c r="P37" s="0" t="n">
+      <c r="P37">
         <v>8</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="n">
+    <row r="38" spans="1:16" ht="16">
+      <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="0" t="n">
+      <c r="B38">
         <v>50</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D38" s="0" t="n">
+      <c r="D38">
         <v>68</v>
       </c>
-      <c r="E38" s="0" t="n">
+      <c r="E38">
         <v>1.73</v>
       </c>
-      <c r="G38" s="0" t="n">
+      <c r="G38">
         <v>0</v>
       </c>
-      <c r="H38" s="0" t="n">
+      <c r="H38">
         <v>15</v>
       </c>
-      <c r="P38" s="0" t="n">
+      <c r="P38">
         <v>10</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="n">
+    <row r="39" spans="1:16" ht="16">
+      <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="0" t="n">
+      <c r="B39">
         <v>46</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D39" s="0" t="n">
+      <c r="D39">
         <v>76</v>
       </c>
-      <c r="E39" s="0" t="n">
+      <c r="E39">
         <v>1.69</v>
       </c>
-      <c r="G39" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="0" t="n">
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
         <v>12</v>
       </c>
-      <c r="P39" s="0" t="n">
+      <c r="P39">
         <v>10</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="n">
+    <row r="40" spans="1:16" ht="16">
+      <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="0" t="n">
+      <c r="B40">
         <v>41</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D40" s="0" t="n">
+      <c r="D40">
         <v>60.5</v>
       </c>
-      <c r="E40" s="0" t="n">
+      <c r="E40">
         <v>1.67</v>
       </c>
-      <c r="G40" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="0" t="n">
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40">
         <v>15</v>
       </c>
-      <c r="P40" s="0" t="n">
+      <c r="P40">
         <v>10</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="n">
+    <row r="41" spans="1:16" ht="16">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="0" t="n">
+      <c r="B41">
         <v>43</v>
       </c>
-      <c r="C41" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" s="0" t="n">
+      <c r="C41" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41">
         <v>95</v>
       </c>
-      <c r="E41" s="0" t="n">
+      <c r="E41">
         <v>1.79</v>
       </c>
-      <c r="G41" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="0" t="n">
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
         <v>15</v>
       </c>
-      <c r="P41" s="0" t="n">
+      <c r="P41">
         <v>10</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="n">
+    <row r="42" spans="1:16" ht="16">
+      <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="0" t="n">
+      <c r="B42">
         <v>30</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D42" s="0" t="n">
+      <c r="D42">
         <v>58</v>
       </c>
-      <c r="E42" s="0" t="n">
+      <c r="E42">
         <v>1.69</v>
       </c>
-      <c r="G42" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="0" t="n">
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
         <v>14</v>
       </c>
-      <c r="P42" s="0" t="n">
+      <c r="P42">
         <v>9</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="n">
+    <row r="43" spans="1:16" ht="16">
+      <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43">
         <v>64</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D43" s="0" t="n">
+      <c r="D43">
         <v>51.5</v>
       </c>
-      <c r="E43" s="0" t="n">
+      <c r="E43">
         <v>1.71</v>
       </c>
-      <c r="G43" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="0" t="n">
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
         <v>13</v>
       </c>
-      <c r="P43" s="0" t="n">
+      <c r="P43">
         <v>7</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="n">
+    <row r="44" spans="1:16" ht="16">
+      <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" s="0" t="n">
+      <c r="B44">
         <v>51</v>
       </c>
-      <c r="C44" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D44" s="0" t="n">
+      <c r="C44" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D44">
         <v>65.5</v>
       </c>
-      <c r="E44" s="0" t="n">
+      <c r="E44">
         <v>1.72</v>
       </c>
-      <c r="G44" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="0" t="n">
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
         <v>14</v>
       </c>
-      <c r="P44" s="0" t="n">
+      <c r="P44">
         <v>8</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="n">
+    <row r="45" spans="1:16" ht="16">
+      <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="0" t="n">
+      <c r="B45">
         <v>24</v>
       </c>
-      <c r="C45" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D45" s="0" t="n">
+      <c r="C45" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D45">
         <v>86</v>
       </c>
-      <c r="E45" s="0" t="n">
+      <c r="E45">
         <v>1.87</v>
       </c>
-      <c r="G45" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" s="0" t="n">
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
         <v>13</v>
       </c>
-      <c r="P45" s="0" t="n">
+      <c r="P45">
         <v>8</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="n">
+    <row r="46" spans="1:16" ht="16">
+      <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" s="0" t="n">
+      <c r="B46">
         <v>26</v>
       </c>
-      <c r="C46" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D46" s="0" t="n">
+      <c r="C46" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D46">
         <v>50.8</v>
       </c>
-      <c r="E46" s="0" t="n">
+      <c r="E46">
         <v>1.72</v>
       </c>
-      <c r="G46" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="0" t="n">
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46">
         <v>13</v>
       </c>
-      <c r="P46" s="0" t="n">
+      <c r="P46">
         <v>8</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="n">
+    <row r="47" spans="1:16" ht="16">
+      <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" s="0" t="n">
+      <c r="B47">
         <v>38</v>
       </c>
-      <c r="C47" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D47" s="0" t="n">
+      <c r="C47" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D47">
         <v>81.5</v>
       </c>
-      <c r="E47" s="0" t="n">
+      <c r="E47">
         <v>1.77</v>
       </c>
-      <c r="G47" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" s="0" t="n">
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47">
         <v>14</v>
       </c>
-      <c r="P47" s="0" t="n">
+      <c r="P47">
         <v>8</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="n">
+    <row r="48" spans="1:16" ht="16">
+      <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" s="0" t="n">
+      <c r="B48">
         <v>42</v>
       </c>
-      <c r="C48" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D48" s="0" t="n">
-        <v>66.1</v>
-      </c>
-      <c r="E48" s="0" t="n">
+      <c r="C48" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D48">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="E48">
         <v>1.76</v>
       </c>
-      <c r="G48" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="0" t="n">
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48">
         <v>13</v>
       </c>
-      <c r="P48" s="0" t="n">
+      <c r="P48">
         <v>7</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="n">
+    <row r="49" spans="1:16" ht="16">
+      <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="0" t="n">
+      <c r="B49">
         <v>31</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D49" s="0" t="n">
+      <c r="C49" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D49">
         <v>74.8</v>
       </c>
-      <c r="E49" s="0" t="n">
+      <c r="E49">
         <v>1.88</v>
       </c>
-      <c r="G49" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="0" t="n">
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
         <v>13</v>
       </c>
-      <c r="P49" s="0" t="n">
+      <c r="P49">
         <v>8</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="n">
+    <row r="50" spans="1:16" ht="16">
+      <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" s="0" t="n">
+      <c r="B50">
         <v>67</v>
       </c>
-      <c r="C50" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D50" s="0" t="n">
+      <c r="C50" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D50">
         <v>98</v>
       </c>
-      <c r="E50" s="0" t="n">
+      <c r="E50">
         <v>1.83</v>
       </c>
-      <c r="G50" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" s="0" t="n">
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
         <v>14</v>
       </c>
-      <c r="P50" s="0" t="n">
+      <c r="P50">
         <v>9</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="n">
+    <row r="51" spans="1:16" ht="16">
+      <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" s="0" t="n">
+      <c r="B51">
         <v>21</v>
       </c>
-      <c r="C51" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D51" s="0" t="n">
+      <c r="C51" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D51">
         <v>74</v>
       </c>
-      <c r="E51" s="0" t="n">
+      <c r="E51">
         <v>1.78</v>
       </c>
-      <c r="G51" s="0" t="n">
+      <c r="G51">
         <v>0</v>
       </c>
-      <c r="H51" s="0" t="n">
+      <c r="H51">
         <v>15</v>
       </c>
-      <c r="P51" s="0" t="n">
+      <c r="P51">
         <v>10</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H52" s="10" t="n">
-        <f aca="false">SUM(H2:H51)</f>
+    <row r="52" spans="1:16">
+      <c r="H52" s="9">
+        <f>SUM(H2:H51)</f>
         <v>696</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="33.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="36.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="15.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="14.11"/>
+    <col min="8" max="8" width="10.5" customWidth="1"/>
+    <col min="9" max="9" width="30.6640625" customWidth="1"/>
+    <col min="10" max="10" width="33.1640625" customWidth="1"/>
+    <col min="11" max="11" width="36.6640625" customWidth="1"/>
+    <col min="12" max="12" width="15.5" customWidth="1"/>
+    <col min="14" max="14" width="14.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>85</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>77</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>78</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>79</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0" t="n">
+    <row r="2" spans="1:12">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>24</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" s="0" t="n">
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2">
         <v>74</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2">
         <v>175</v>
       </c>
-      <c r="G2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="0" t="n">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
         <v>21</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" t="s">
         <v>86</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="L2">
         <v>17</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+    <row r="3" spans="1:12">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3">
         <v>24</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="C3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3">
         <v>72</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3">
         <v>172</v>
       </c>
-      <c r="G3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="0" t="n">
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
         <v>23</v>
       </c>
-      <c r="J3" s="0" t="n">
+      <c r="J3">
         <v>0</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3">
         <v>23</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+    <row r="4" spans="1:12">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4">
         <v>23</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="C4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4">
         <v>80</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4">
         <v>178</v>
       </c>
-      <c r="G4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="0" t="n">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>24</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4">
         <v>0</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4">
         <v>24</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+    <row r="5" spans="1:12">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5">
         <v>23</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" s="0" t="n">
+      <c r="C5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5">
         <v>60</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5">
         <v>170</v>
       </c>
-      <c r="G5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="0" t="n">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
         <v>17</v>
       </c>
-      <c r="J5" s="0" t="s">
+      <c r="J5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+    <row r="6" spans="1:12">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6">
         <v>21</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="0" t="n">
+      <c r="C6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6">
         <v>71</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6">
         <v>171</v>
       </c>
-      <c r="G6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="0" t="n">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
         <v>25</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+    <row r="7" spans="1:12">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7">
         <v>20</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" s="0" t="n">
+      <c r="C7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7">
         <v>65</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7">
         <v>168</v>
       </c>
-      <c r="G7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="0" t="n">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
         <v>24</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+    <row r="8" spans="1:12">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8">
         <v>25</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="0" t="n">
+      <c r="C8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8">
         <v>72</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8">
         <v>176</v>
       </c>
-      <c r="G8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="0" t="n">
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
         <v>19</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+    <row r="9" spans="1:12">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9">
         <v>23</v>
       </c>
-      <c r="C9" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" s="0" t="n">
+      <c r="C9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9">
         <v>85</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9">
         <v>181</v>
       </c>
-      <c r="G9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="0" t="n">
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
         <v>21</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+    <row r="10" spans="1:12">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10">
         <v>24</v>
       </c>
-      <c r="C10" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" s="0" t="n">
+      <c r="C10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10">
         <v>76</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10">
         <v>183</v>
       </c>
-      <c r="G10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="0" t="n">
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
         <v>23</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+    <row r="11" spans="1:12">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11">
         <v>20</v>
       </c>
-      <c r="C11" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" s="0" t="n">
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11">
         <v>80</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11">
         <v>182</v>
       </c>
-      <c r="G11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="0" t="n">
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
         <v>23</v>
       </c>
-      <c r="J11" s="0" t="n">
+      <c r="J11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+    <row r="12" spans="1:12">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12">
         <v>23</v>
       </c>
-      <c r="C12" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" s="0" t="n">
+      <c r="C12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12">
         <v>75</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12">
         <v>175</v>
       </c>
-      <c r="G12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="0" t="n">
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
         <v>27</v>
       </c>
-      <c r="J12" s="0" t="s">
+      <c r="J12" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+    <row r="13" spans="1:12">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13">
         <v>24</v>
       </c>
-      <c r="C13" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" s="0" t="n">
+      <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13">
         <v>80</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13">
         <v>177</v>
       </c>
-      <c r="G13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="0" t="n">
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
         <v>28</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+    <row r="14" spans="1:12">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14">
         <v>21</v>
       </c>
-      <c r="C14" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="0" t="n">
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14">
         <v>58</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14">
         <v>170</v>
       </c>
-      <c r="G14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="0" t="n">
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
         <v>27</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H15" s="10" t="n">
-        <f aca="false">SUM(H1:H14)</f>
+    <row r="15" spans="1:12">
+      <c r="H15" s="9">
+        <f>SUM(H1:H14)</f>
         <v>302</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:16">
+      <c r="A1" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>77</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>78</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>79</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" t="s">
         <v>80</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+    <row r="4" spans="1:16">
+      <c r="A4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+    <row r="5" spans="1:16">
+      <c r="A5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+    <row r="6" spans="1:16">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6">
         <v>29</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="0" t="n">
+      <c r="C6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6">
         <v>61</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6">
         <v>167</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6">
         <v>2</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6">
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+    <row r="7" spans="1:16">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7">
         <v>42</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" s="0" t="n">
+      <c r="C7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7">
         <v>71.8</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7">
         <v>174</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7">
         <v>2</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7">
         <v>10</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+    <row r="8" spans="1:16">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8">
         <v>38</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="0" t="n">
+      <c r="C8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8">
         <v>100.5</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8">
         <v>182</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8">
         <v>2</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8">
         <v>12</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+    <row r="9" spans="1:16">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9">
         <v>42</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9">
         <v>60.7</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9">
         <v>165</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9">
         <v>2</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9">
         <v>10</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+    <row r="10" spans="1:16">
+      <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+    <row r="11" spans="1:16">
+      <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+    <row r="12" spans="1:16">
+      <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+    <row r="13" spans="1:16">
+      <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+    <row r="14" spans="1:16">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14">
         <v>56</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" t="s">
         <v>89</v>
       </c>
-      <c r="D14" s="0" t="n">
-        <v>67.9</v>
-      </c>
-      <c r="E14" s="0" t="n">
+      <c r="D14">
+        <v>67.900000000000006</v>
+      </c>
+      <c r="E14">
         <v>166</v>
       </c>
-      <c r="L14" s="0" t="n">
+      <c r="L14">
         <v>11</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+    <row r="15" spans="1:16">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15">
         <v>38</v>
       </c>
-      <c r="C15" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="0" t="n">
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15">
         <v>98</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15">
         <v>178</v>
       </c>
-      <c r="L15" s="0" t="n">
+      <c r="L15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+    <row r="16" spans="1:16">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16">
         <v>21</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" t="s">
         <v>89</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16">
         <v>61.9</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16">
         <v>158</v>
       </c>
-      <c r="L16" s="0" t="n">
+      <c r="L16">
         <v>13</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+    <row r="17" spans="1:12">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17">
         <v>35</v>
       </c>
-      <c r="C17" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="0" t="n">
+      <c r="C17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17">
         <v>64.7</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17">
         <v>170</v>
       </c>
-      <c r="L17" s="0" t="n">
+      <c r="L17">
         <v>10</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+    <row r="18" spans="1:12">
+      <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+    <row r="19" spans="1:12">
+      <c r="A19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+    <row r="20" spans="1:12">
+      <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+    <row r="21" spans="1:12">
+      <c r="A21">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:P52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="0" t="s">
+    <row r="1" spans="1:16">
+      <c r="A1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="0" t="s">
+      <c r="D1" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>77</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>78</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>79</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" t="s">
         <v>80</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" t="s">
         <v>81</v>
       </c>
     </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2">
+        <v>75.527861547542898</v>
+      </c>
+      <c r="E2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3">
+        <v>75.216410190148395</v>
+      </c>
+      <c r="E3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4">
+        <v>90.178596065609895</v>
+      </c>
+      <c r="E4">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5">
+        <v>68.752980738810905</v>
+      </c>
+      <c r="E5">
+        <v>183.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6">
+        <v>95.030180507290396</v>
+      </c>
+      <c r="E6">
+        <v>182.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7">
+        <v>70.554727693756206</v>
+      </c>
+      <c r="E7">
+        <v>167.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8">
+        <v>90.784376337728006</v>
+      </c>
+      <c r="E8">
+        <v>185.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9">
+        <v>75.6063604141372</v>
+      </c>
+      <c r="E9">
+        <v>171.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10">
+        <v>76.357363880860305</v>
+      </c>
+      <c r="E10">
+        <v>188.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11">
+        <v>57.273416314576401</v>
+      </c>
+      <c r="E11">
+        <v>170.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12">
+        <v>68.838643739611896</v>
+      </c>
+      <c r="E12">
+        <v>170.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13">
+        <v>89.765031280522606</v>
+      </c>
+      <c r="E13">
+        <v>185.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14">
+        <v>73.154918953797207</v>
+      </c>
+      <c r="E14">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15">
+        <v>94.315477454296001</v>
+      </c>
+      <c r="E15">
+        <v>176.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16">
+        <v>62.864201055909199</v>
+      </c>
+      <c r="E16">
+        <v>166.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17">
+        <v>70.474324955046299</v>
+      </c>
+      <c r="E17">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18">
+        <v>81.187589890170202</v>
+      </c>
+      <c r="E18">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19">
+        <v>73.292966162861603</v>
+      </c>
+      <c r="E19">
+        <v>173.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>25</v>
+      </c>
+      <c r="C20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20">
+        <v>63.2347601966772</v>
+      </c>
+      <c r="E20">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>29</v>
+      </c>
+      <c r="C21" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21">
+        <v>73.268840066888799</v>
+      </c>
+      <c r="E21">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>25</v>
+      </c>
+      <c r="C22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22">
+        <v>58.029067769687003</v>
+      </c>
+      <c r="E22">
+        <v>172.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>21</v>
+      </c>
+      <c r="C23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23">
+        <v>85.818703009347004</v>
+      </c>
+      <c r="E23">
+        <v>184.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>25</v>
+      </c>
+      <c r="C24" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24">
+        <v>76.065091739440305</v>
+      </c>
+      <c r="E24">
+        <v>172.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>27</v>
+      </c>
+      <c r="C25" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25">
+        <v>84.500624785972605</v>
+      </c>
+      <c r="E25">
+        <v>173.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26">
+        <v>80.189139537331101</v>
+      </c>
+      <c r="E26">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>37</v>
+      </c>
+      <c r="C27" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27">
+        <v>81.482945334893799</v>
+      </c>
+      <c r="E27">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>42</v>
+      </c>
+      <c r="C28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28">
+        <v>62.231371023998598</v>
+      </c>
+      <c r="E28">
+        <v>166.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>27</v>
+      </c>
+      <c r="C29" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29">
+        <v>103.593135418738</v>
+      </c>
+      <c r="E29">
+        <v>172.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30">
+        <v>89.521141517738698</v>
+      </c>
+      <c r="E30">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>27</v>
+      </c>
+      <c r="C31" t="s">
+        <v>82</v>
+      </c>
+      <c r="D31">
+        <v>68.862616007902801</v>
+      </c>
+      <c r="E31">
+        <v>174.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>31</v>
+      </c>
+      <c r="C32" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32">
+        <v>80.579689644200002</v>
+      </c>
+      <c r="E32">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33">
+        <v>68.146280219349904</v>
+      </c>
+      <c r="E33">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>28</v>
+      </c>
+      <c r="C34" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34">
+        <v>76.350187907485605</v>
+      </c>
+      <c r="E34">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>31</v>
+      </c>
+      <c r="C35" t="s">
+        <v>82</v>
+      </c>
+      <c r="D35">
+        <v>75.240691431495094</v>
+      </c>
+      <c r="E35">
+        <v>171.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>33</v>
+      </c>
+      <c r="C36" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36">
+        <v>84.462231629890397</v>
+      </c>
+      <c r="E36">
+        <v>175.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>23</v>
+      </c>
+      <c r="C37" t="s">
+        <v>82</v>
+      </c>
+      <c r="D37">
+        <v>54.140492711229903</v>
+      </c>
+      <c r="E37">
+        <v>169.6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>28</v>
+      </c>
+      <c r="C38" t="s">
+        <v>82</v>
+      </c>
+      <c r="D38">
+        <v>90.3777449015748</v>
+      </c>
+      <c r="E38">
+        <v>186.6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>26</v>
+      </c>
+      <c r="C39" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39">
+        <v>76.818976821680806</v>
+      </c>
+      <c r="E39">
+        <v>180.7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>21</v>
+      </c>
+      <c r="C40" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40">
+        <v>63.023042292533198</v>
+      </c>
+      <c r="E40">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>28</v>
+      </c>
+      <c r="C41" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41">
+        <v>136.13657014312699</v>
+      </c>
+      <c r="E41">
+        <v>183.6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>28</v>
+      </c>
+      <c r="C42" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42">
+        <v>85.778406001692602</v>
+      </c>
+      <c r="E42">
+        <v>185.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>20</v>
+      </c>
+      <c r="C43" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43">
+        <v>79.409803278182807</v>
+      </c>
+      <c r="E43">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>37</v>
+      </c>
+      <c r="C44" t="s">
+        <v>82</v>
+      </c>
+      <c r="D44">
+        <v>61.022674401557197</v>
+      </c>
+      <c r="E44">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>21</v>
+      </c>
+      <c r="C45" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45">
+        <v>61.324277567479101</v>
+      </c>
+      <c r="E45">
+        <v>164.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>26</v>
+      </c>
+      <c r="C46" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46">
+        <v>79.018618686461394</v>
+      </c>
+      <c r="E46">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>28</v>
+      </c>
+      <c r="C47" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47">
+        <v>64.610276323420507</v>
+      </c>
+      <c r="E47">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>30</v>
+      </c>
+      <c r="C48" t="s">
+        <v>89</v>
+      </c>
+      <c r="D48">
+        <v>61.061758542644803</v>
+      </c>
+      <c r="E48">
+        <v>165.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>36</v>
+      </c>
+      <c r="C49" t="s">
+        <v>82</v>
+      </c>
+      <c r="D49">
+        <v>68.4202597262979</v>
+      </c>
+      <c r="E49">
+        <v>171.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>68</v>
+      </c>
+      <c r="C50" t="s">
+        <v>82</v>
+      </c>
+      <c r="D50">
+        <v>80.633207153808499</v>
+      </c>
+      <c r="E50">
+        <v>174.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>34</v>
+      </c>
+      <c r="C51" t="s">
+        <v>82</v>
+      </c>
+      <c r="D51">
+        <v>96.299047509172397</v>
+      </c>
+      <c r="E51">
+        <v>174.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>25</v>
+      </c>
+      <c r="C52" t="s">
+        <v>89</v>
+      </c>
+      <c r="D52">
+        <v>65.733442413113394</v>
+      </c>
+      <c r="E52">
+        <v>169.5</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="28.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="33.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="36.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13.44"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="28.83203125" customWidth="1"/>
+    <col min="10" max="10" width="33.1640625" customWidth="1"/>
+    <col min="11" max="11" width="36.6640625" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>85</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>77</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>78</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>79</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0" t="s">
+    <row r="2" spans="1:12">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>90</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" t="s">
         <v>90</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2">
         <v>18</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+    <row r="3" spans="1:12">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" t="s">
         <v>90</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" t="s">
         <v>90</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3">
         <v>0</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3">
         <v>16</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+    <row r="4" spans="1:12">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>90</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" t="s">
         <v>90</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4">
         <v>12</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+    <row r="5" spans="1:12">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" t="s">
         <v>90</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5">
         <v>0</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5">
         <v>19</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+    <row r="6" spans="1:12">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" t="s">
         <v>90</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" t="s">
         <v>90</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6">
         <v>19</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+    <row r="7" spans="1:12">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7">
         <v>0</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7">
         <v>17</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+    <row r="8" spans="1:12">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" t="s">
         <v>90</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8">
         <v>0</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8">
         <v>15</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="L8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+    <row r="9" spans="1:12">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>90</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" t="s">
         <v>90</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9">
         <v>0</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9">
         <v>15</v>
       </c>
-      <c r="L9" s="0" t="n">
+      <c r="L9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+    <row r="10" spans="1:12">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" t="s">
         <v>90</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10">
         <v>0</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10">
         <v>19</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+    <row r="11" spans="1:12">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" t="s">
         <v>90</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" t="s">
         <v>90</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11">
         <v>0</v>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11">
         <v>17</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H12" s="10" t="n">
-        <f aca="false">SUM(H2:H11)</f>
+    <row r="12" spans="1:12">
+      <c r="H12" s="9">
+        <f>SUM(H2:H11)</f>
         <v>167</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H13" s="10"/>
+    <row r="13" spans="1:12">
+      <c r="H13" s="9"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="29.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="36.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13"/>
+    <col min="8" max="8" width="11.5" customWidth="1"/>
+    <col min="9" max="9" width="29.83203125" customWidth="1"/>
+    <col min="10" max="10" width="34" customWidth="1"/>
+    <col min="11" max="11" width="36.83203125" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>85</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>77</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>78</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>79</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0" t="s">
+    <row r="2" spans="1:12">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2">
         <v>69.86</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2">
         <v>1.68</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2">
         <v>3</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" t="s">
         <v>92</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="L2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+    <row r="3" spans="1:12">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>66.68</v>
-      </c>
-      <c r="E3" s="0" t="n">
+      <c r="C3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3">
+        <v>66.680000000000007</v>
+      </c>
+      <c r="E3">
         <v>1.7</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3">
         <v>4</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" t="s">
         <v>93</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3">
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+    <row r="4" spans="1:12">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>91</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4">
         <v>53.07</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4">
         <v>1.59</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4">
         <v>3</v>
       </c>
-      <c r="I4" s="0" t="s">
+      <c r="I4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+    <row r="5" spans="1:12">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>91</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" s="0" t="n">
+      <c r="C5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5">
         <v>71.67</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5">
         <v>1.82</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+    <row r="6" spans="1:12">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="0" t="n">
+      <c r="C6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6">
         <v>90.7</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6">
         <v>1.95</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+    <row r="7" spans="1:12">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7">
         <v>48.99</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7">
         <v>1.53</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+    <row r="8" spans="1:12">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" t="s">
         <v>89</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8">
         <v>63.96</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8">
         <v>1.75</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H9" s="10" t="n">
-        <f aca="false">SUM(H1:H8)</f>
+    <row r="9" spans="1:12">
+      <c r="H9" s="9">
+        <f>SUM(H1:H8)</f>
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shahzaibali/Desktop/TeamProject/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEB6682-670E-1D46-BC25-19AC66065210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E3A1DD3-767B-A546-8683-3A7E1AF4D8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20140" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="DB1" sheetId="2" r:id="rId2"/>
     <sheet name="DB2" sheetId="3" r:id="rId3"/>
     <sheet name="DB3" sheetId="4" r:id="rId4"/>
-    <sheet name="DB4" sheetId="5" r:id="rId5"/>
+    <sheet name="DB5" sheetId="5" r:id="rId5"/>
     <sheet name="DB Grouvel" sheetId="6" r:id="rId6"/>
     <sheet name="DB Han" sheetId="7" r:id="rId7"/>
   </sheets>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shahzaibali/Desktop/TeamProject/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E3A1DD3-767B-A546-8683-3A7E1AF4D8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6622946B-2715-4995-A2ED-0BADD7D94E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20140" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="14016" windowHeight="12696" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="DB1" sheetId="2" r:id="rId2"/>
     <sheet name="DB2" sheetId="3" r:id="rId3"/>
     <sheet name="DB3" sheetId="4" r:id="rId4"/>
-    <sheet name="DB5" sheetId="5" r:id="rId5"/>
-    <sheet name="DB Grouvel" sheetId="6" r:id="rId6"/>
-    <sheet name="DB Han" sheetId="7" r:id="rId7"/>
+    <sheet name="DB4" sheetId="8" r:id="rId5"/>
+    <sheet name="DB5" sheetId="5" r:id="rId6"/>
+    <sheet name="DB Grouvel" sheetId="6" r:id="rId7"/>
+    <sheet name="DB Han" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="97">
   <si>
     <t>Database No.</t>
   </si>
@@ -778,28 +779,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.1640625" customWidth="1"/>
-    <col min="4" max="4" width="33.83203125" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="4" max="4" width="33.77734375" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="23.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="14.33203125" customWidth="1"/>
     <col min="12" max="12" width="12.6640625" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="28.5" customWidth="1"/>
-    <col min="15" max="15" width="24.5" customWidth="1"/>
+    <col min="14" max="14" width="28.44140625" customWidth="1"/>
+    <col min="15" max="15" width="24.44140625" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="40.83203125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="29.83203125" customWidth="1"/>
+    <col min="17" max="17" width="40.77734375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="29.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" ht="17">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="15.6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -852,7 +853,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="80">
+    <row r="2" spans="1:18" ht="72">
       <c r="A2">
         <v>1</v>
       </c>
@@ -905,7 +906,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="48">
+    <row r="3" spans="1:18" ht="43.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -949,7 +950,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="16">
+    <row r="4" spans="1:18">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -978,7 +979,7 @@
       <c r="I8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="48">
+    <row r="9" spans="1:18" ht="57.6">
       <c r="B9" s="1" t="s">
         <v>37</v>
       </c>
@@ -1007,7 +1008,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="48">
+    <row r="10" spans="1:18" ht="43.2">
       <c r="B10" s="1" t="s">
         <v>42</v>
       </c>
@@ -1074,7 +1075,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="51">
+    <row r="12" spans="1:18" ht="46.8">
       <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
@@ -1115,7 +1116,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="48">
+    <row r="13" spans="1:18" ht="43.2">
       <c r="B13" s="1" t="s">
         <v>63</v>
       </c>
@@ -1178,18 +1179,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" customWidth="1"/>
     <col min="8" max="8" width="16.6640625" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.77734375" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="9.33203125" customWidth="1"/>
     <col min="16" max="16" width="16.6640625" customWidth="1"/>
@@ -1233,7 +1234,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="16">
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1265,7 +1266,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="16">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1297,7 +1298,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="16">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1329,7 +1330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="16">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1361,7 +1362,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="16">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1393,7 +1394,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="16">
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1425,7 +1426,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="16">
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1457,7 +1458,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="16">
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1489,7 +1490,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="16">
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1521,7 +1522,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="16">
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1553,7 +1554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="16">
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1579,7 +1580,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="16">
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1605,7 +1606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="16">
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1631,7 +1632,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="16">
+    <row r="15" spans="1:16">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1657,7 +1658,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="16">
+    <row r="16" spans="1:16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1683,7 +1684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="16">
+    <row r="17" spans="1:16">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1709,7 +1710,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="16">
+    <row r="18" spans="1:16">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1735,7 +1736,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="16">
+    <row r="19" spans="1:16">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1761,7 +1762,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="16">
+    <row r="20" spans="1:16">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1787,7 +1788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="16">
+    <row r="21" spans="1:16">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1813,7 +1814,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="16">
+    <row r="22" spans="1:16">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1839,7 +1840,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="16">
+    <row r="23" spans="1:16">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1865,7 +1866,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="16">
+    <row r="24" spans="1:16">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1891,7 +1892,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="16">
+    <row r="25" spans="1:16">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1917,7 +1918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="16">
+    <row r="26" spans="1:16">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1943,7 +1944,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="16">
+    <row r="27" spans="1:16">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1969,7 +1970,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="16">
+    <row r="28" spans="1:16">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1995,7 +1996,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="16">
+    <row r="29" spans="1:16">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2021,7 +2022,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="16">
+    <row r="30" spans="1:16">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2047,7 +2048,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="16">
+    <row r="31" spans="1:16">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2073,7 +2074,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="16">
+    <row r="32" spans="1:16">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2099,7 +2100,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="16">
+    <row r="33" spans="1:16">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2125,7 +2126,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="16">
+    <row r="34" spans="1:16">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2151,7 +2152,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="16">
+    <row r="35" spans="1:16">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2177,7 +2178,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="16">
+    <row r="36" spans="1:16">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2203,7 +2204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="16">
+    <row r="37" spans="1:16">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2229,7 +2230,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="16">
+    <row r="38" spans="1:16">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2255,7 +2256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="16">
+    <row r="39" spans="1:16">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2281,7 +2282,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="16">
+    <row r="40" spans="1:16">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2307,7 +2308,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="16">
+    <row r="41" spans="1:16">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2333,7 +2334,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="16">
+    <row r="42" spans="1:16">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2359,7 +2360,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="16">
+    <row r="43" spans="1:16">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2385,7 +2386,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="16">
+    <row r="44" spans="1:16">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2411,7 +2412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="16">
+    <row r="45" spans="1:16">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2437,7 +2438,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="16">
+    <row r="46" spans="1:16">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2463,7 +2464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="16">
+    <row r="47" spans="1:16">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2489,7 +2490,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="16">
+    <row r="48" spans="1:16">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2515,7 +2516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="16">
+    <row r="49" spans="1:16">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2541,7 +2542,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="16">
+    <row r="50" spans="1:16">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2567,7 +2568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="16">
+    <row r="51" spans="1:16">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2608,14 +2609,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="8" max="8" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" customWidth="1"/>
     <col min="9" max="9" width="30.6640625" customWidth="1"/>
-    <col min="10" max="10" width="33.1640625" customWidth="1"/>
+    <col min="10" max="10" width="33.109375" customWidth="1"/>
     <col min="11" max="11" width="36.6640625" customWidth="1"/>
-    <col min="12" max="12" width="15.5" customWidth="1"/>
-    <col min="14" max="14" width="14.1640625" customWidth="1"/>
+    <col min="12" max="12" width="15.44140625" customWidth="1"/>
+    <col min="14" max="14" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2994,7 +2995,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
@@ -3076,6 +3077,9 @@
       <c r="H6">
         <v>10</v>
       </c>
+      <c r="L6">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7">
@@ -3099,6 +3103,9 @@
       <c r="H7">
         <v>10</v>
       </c>
+      <c r="L7">
+        <v>10</v>
+      </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8">
@@ -3122,6 +3129,9 @@
       <c r="H8">
         <v>12</v>
       </c>
+      <c r="L8">
+        <v>12</v>
+      </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9">
@@ -3143,6 +3153,9 @@
         <v>2</v>
       </c>
       <c r="H9">
+        <v>10</v>
+      </c>
+      <c r="L9">
         <v>10</v>
       </c>
     </row>
@@ -3273,14 +3286,770 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D22FEE7-983F-4E6D-B518-6357D6EFC8AC}">
+  <dimension ref="A1:P58"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L1" t="s">
+        <v>80</v>
+      </c>
+      <c r="P1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2">
+        <v>68.900000000000006</v>
+      </c>
+      <c r="E2">
+        <v>1.75</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="E3">
+        <v>1.81</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>18</v>
+      </c>
+      <c r="L3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4">
+        <v>80.8</v>
+      </c>
+      <c r="E4">
+        <v>1.84</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>21</v>
+      </c>
+      <c r="L4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5">
+        <v>82.7</v>
+      </c>
+      <c r="E5">
+        <v>1.82</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6">
+        <v>54.9</v>
+      </c>
+      <c r="E6">
+        <v>1.63</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7">
+        <v>77.3</v>
+      </c>
+      <c r="E7">
+        <v>1.79</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8">
+        <v>94.2</v>
+      </c>
+      <c r="E8">
+        <v>1.91</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9">
+        <v>69.5</v>
+      </c>
+      <c r="E9">
+        <v>1.88</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10">
+        <v>72</v>
+      </c>
+      <c r="E10">
+        <v>1.84</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11">
+        <v>52.3</v>
+      </c>
+      <c r="E11">
+        <v>1.58</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12">
+        <v>60.4</v>
+      </c>
+      <c r="E12">
+        <v>1.68</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13">
+        <v>55</v>
+      </c>
+      <c r="E13">
+        <v>1.64</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25">
+        <v>62.1</v>
+      </c>
+      <c r="E25">
+        <v>1.62</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26">
+        <v>80.7</v>
+      </c>
+      <c r="E26">
+        <v>1.74</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>21</v>
+      </c>
+      <c r="C27" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27">
+        <v>91.2</v>
+      </c>
+      <c r="E27">
+        <v>1.99</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>21</v>
+      </c>
+      <c r="C28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28">
+        <v>69.5</v>
+      </c>
+      <c r="E28">
+        <v>1.78</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29">
+        <v>67.5</v>
+      </c>
+      <c r="E29">
+        <v>1.83</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>22</v>
+      </c>
+      <c r="C30" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30">
+        <v>62.1</v>
+      </c>
+      <c r="E30">
+        <v>1.81</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>28</v>
+      </c>
+      <c r="C31" t="s">
+        <v>82</v>
+      </c>
+      <c r="D31">
+        <v>81.349999999999994</v>
+      </c>
+      <c r="E31">
+        <v>1.81</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>21</v>
+      </c>
+      <c r="C32" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32">
+        <v>58.1</v>
+      </c>
+      <c r="E32">
+        <v>1.65</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>23</v>
+      </c>
+      <c r="C33" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33">
+        <v>80.900000000000006</v>
+      </c>
+      <c r="E33">
+        <v>1.78</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>27</v>
+      </c>
+      <c r="C34" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="E34">
+        <v>1.68</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>23</v>
+      </c>
+      <c r="C35" t="s">
+        <v>82</v>
+      </c>
+      <c r="D35">
+        <v>82</v>
+      </c>
+      <c r="E35">
+        <v>1.78</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125"/>
+    <col min="1" max="1" width="9.77734375" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375"/>
     <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -4187,304 +4956,6 @@
       <c r="E52">
         <v>169.5</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:L13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="28.83203125" customWidth="1"/>
-    <col min="10" max="10" width="33.1640625" customWidth="1"/>
-    <col min="11" max="11" width="36.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J1" t="s">
-        <v>78</v>
-      </c>
-      <c r="K1" t="s">
-        <v>79</v>
-      </c>
-      <c r="L1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>15</v>
-      </c>
-      <c r="L8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E9" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>15</v>
-      </c>
-      <c r="L9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E10" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="H12" s="9">
-        <f>SUM(H2:H11)</f>
-        <v>167</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="H13" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4493,14 +4964,312 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="8" max="8" width="10.77734375" customWidth="1"/>
+    <col min="9" max="9" width="28.77734375" customWidth="1"/>
+    <col min="10" max="10" width="33.109375" customWidth="1"/>
+    <col min="11" max="11" width="36.6640625" customWidth="1"/>
+    <col min="12" max="12" width="13.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>15</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>15</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E10" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="H12" s="9">
+        <f>SUM(H2:H11)</f>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="H13" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="8" max="8" width="11.5" customWidth="1"/>
-    <col min="9" max="9" width="29.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="9" width="29.77734375" customWidth="1"/>
     <col min="10" max="10" width="34" customWidth="1"/>
-    <col min="11" max="11" width="36.83203125" customWidth="1"/>
+    <col min="11" max="11" width="36.77734375" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6622946B-2715-4995-A2ED-0BADD7D94E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A16DE9-C835-1A4A-AA7F-200DF90A663F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="14016" windowHeight="12696" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29560" yWindow="-3260" windowWidth="38080" windowHeight="20780" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="97">
   <si>
     <t>Database No.</t>
   </si>
@@ -386,7 +386,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -466,6 +466,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -495,7 +501,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -515,6 +521,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -779,28 +786,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.109375" customWidth="1"/>
-    <col min="4" max="4" width="33.77734375" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" customWidth="1"/>
+    <col min="4" max="4" width="33.83203125" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="23.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.5" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="14.33203125" customWidth="1"/>
     <col min="12" max="12" width="12.6640625" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="28.44140625" customWidth="1"/>
-    <col min="15" max="15" width="24.44140625" customWidth="1"/>
+    <col min="14" max="14" width="28.5" customWidth="1"/>
+    <col min="15" max="15" width="24.5" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="40.77734375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="29.77734375" customWidth="1"/>
+    <col min="17" max="17" width="40.83203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="29.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" ht="15.6">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -853,7 +860,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="72">
+    <row r="2" spans="1:18" ht="80">
       <c r="A2">
         <v>1</v>
       </c>
@@ -906,7 +913,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="43.2">
+    <row r="3" spans="1:18" ht="48">
       <c r="A3">
         <v>2</v>
       </c>
@@ -950,7 +957,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" ht="16">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -979,7 +986,7 @@
       <c r="I8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="57.6">
+    <row r="9" spans="1:18" ht="48">
       <c r="B9" s="1" t="s">
         <v>37</v>
       </c>
@@ -1008,7 +1015,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="43.2">
+    <row r="10" spans="1:18" ht="48">
       <c r="B10" s="1" t="s">
         <v>42</v>
       </c>
@@ -1075,7 +1082,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="46.8">
+    <row r="12" spans="1:18" ht="51">
       <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
@@ -1116,7 +1123,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="43.2">
+    <row r="13" spans="1:18" ht="48">
       <c r="B13" s="1" t="s">
         <v>63</v>
       </c>
@@ -1179,18 +1186,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.77734375" customWidth="1"/>
+    <col min="7" max="7" width="11.83203125" customWidth="1"/>
     <col min="8" max="8" width="16.6640625" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="16.77734375" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="9.33203125" customWidth="1"/>
     <col min="16" max="16" width="16.6640625" customWidth="1"/>
@@ -1234,7 +1241,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" ht="16">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1266,7 +1273,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" ht="16">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1298,7 +1305,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" ht="16">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1330,7 +1337,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" ht="16">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1362,7 +1369,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" ht="16">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1394,7 +1401,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" ht="16">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1426,7 +1433,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" ht="16">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1458,7 +1465,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" ht="16">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1490,7 +1497,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" ht="16">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1522,7 +1529,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" ht="16">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1554,7 +1561,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" ht="16">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1580,7 +1587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" ht="16">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1606,7 +1613,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" ht="16">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1632,7 +1639,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" ht="16">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1658,7 +1665,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" ht="16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1684,7 +1691,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" ht="16">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1710,7 +1717,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" ht="16">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1736,7 +1743,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" ht="16">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1762,7 +1769,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" ht="16">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1788,7 +1795,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" ht="16">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1814,7 +1821,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" ht="16">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1840,7 +1847,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" ht="16">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1866,7 +1873,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" ht="16">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1892,7 +1899,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" ht="16">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1918,7 +1925,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" ht="16">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1944,7 +1951,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" ht="16">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1970,7 +1977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" ht="16">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1996,7 +2003,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" ht="16">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2022,7 +2029,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" ht="16">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2048,7 +2055,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" ht="16">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2074,7 +2081,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" ht="16">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2100,7 +2107,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" ht="16">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2126,7 +2133,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" ht="16">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2152,7 +2159,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" ht="16">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2178,7 +2185,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" ht="16">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2204,7 +2211,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" ht="16">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2230,7 +2237,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" ht="16">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2256,7 +2263,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" ht="16">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2282,7 +2289,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" ht="16">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2308,7 +2315,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" ht="16">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2334,7 +2341,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" ht="16">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2360,7 +2367,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" ht="16">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2386,7 +2393,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" ht="16">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2412,7 +2419,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" ht="16">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2438,7 +2445,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" ht="16">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2464,7 +2471,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" ht="16">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2490,7 +2497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" ht="16">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2516,7 +2523,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" ht="16">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2542,7 +2549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" ht="16">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2568,7 +2575,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" ht="16">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2609,14 +2616,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="8" max="8" width="10.44140625" customWidth="1"/>
+    <col min="8" max="8" width="10.5" customWidth="1"/>
     <col min="9" max="9" width="30.6640625" customWidth="1"/>
-    <col min="10" max="10" width="33.109375" customWidth="1"/>
+    <col min="10" max="10" width="33.1640625" customWidth="1"/>
     <col min="11" max="11" width="36.6640625" customWidth="1"/>
-    <col min="12" max="12" width="15.44140625" customWidth="1"/>
-    <col min="14" max="14" width="14.109375" customWidth="1"/>
+    <col min="12" max="12" width="15.5" customWidth="1"/>
+    <col min="14" max="14" width="14.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2995,7 +3002,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
@@ -3288,7 +3295,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D22FEE7-983F-4E6D-B518-6357D6EFC8AC}">
   <dimension ref="A1:P58"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col min="8" max="8" width="46.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
@@ -3617,58 +3627,278 @@
       <c r="A14">
         <v>13</v>
       </c>
+      <c r="B14" s="11">
+        <v>25</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="11">
+        <v>79.95</v>
+      </c>
+      <c r="E14" s="11">
+        <v>1.83</v>
+      </c>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11">
+        <v>1</v>
+      </c>
+      <c r="H14" s="11">
+        <v>22</v>
+      </c>
+      <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:16">
       <c r="A15">
         <v>14</v>
       </c>
+      <c r="B15" s="11">
+        <v>23</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="11">
+        <v>54.8</v>
+      </c>
+      <c r="E15" s="11">
+        <v>1.64</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11">
+        <v>1</v>
+      </c>
+      <c r="H15" s="11">
+        <v>21</v>
+      </c>
+      <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:16">
       <c r="A16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="B16" s="11">
+        <v>21</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="11">
+        <v>76.5</v>
+      </c>
+      <c r="E16" s="11">
+        <v>1.82</v>
+      </c>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11">
+        <v>1</v>
+      </c>
+      <c r="H16" s="11">
+        <v>21</v>
+      </c>
+      <c r="I16" s="11"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="B17" s="11">
+        <v>22</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="11">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="E17" s="11">
+        <v>1.82</v>
+      </c>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11">
+        <v>1</v>
+      </c>
+      <c r="H17" s="11">
+        <v>21</v>
+      </c>
+      <c r="I17" s="11"/>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="B18" s="11">
+        <v>20</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="11">
+        <v>56.45</v>
+      </c>
+      <c r="E18" s="11">
+        <v>1.65</v>
+      </c>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11">
+        <v>1</v>
+      </c>
+      <c r="H18" s="11">
+        <v>20</v>
+      </c>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="B19" s="11">
+        <v>22</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="11">
+        <v>78.3</v>
+      </c>
+      <c r="E19" s="11">
+        <v>1.88</v>
+      </c>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11">
+        <v>1</v>
+      </c>
+      <c r="H19" s="11">
+        <v>21</v>
+      </c>
+      <c r="I19" s="11"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="B20" s="11">
+        <v>22</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="11">
+        <v>90.8</v>
+      </c>
+      <c r="E20" s="11">
+        <v>1.92</v>
+      </c>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11">
+        <v>1</v>
+      </c>
+      <c r="H20" s="11">
+        <v>20</v>
+      </c>
+      <c r="I20" s="11"/>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="B21" s="11">
+        <v>24</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="11">
+        <v>72.2</v>
+      </c>
+      <c r="E21" s="11">
+        <v>1.86</v>
+      </c>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11">
+        <v>1</v>
+      </c>
+      <c r="H21" s="11">
+        <v>20</v>
+      </c>
+      <c r="I21" s="11"/>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="B22" s="11">
+        <v>22</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="11">
+        <v>81.8</v>
+      </c>
+      <c r="E22" s="11">
+        <v>1.87</v>
+      </c>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11">
+        <v>1</v>
+      </c>
+      <c r="H22" s="11">
+        <v>21</v>
+      </c>
+      <c r="I22" s="11"/>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="B23" s="11">
+        <v>21</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="11">
+        <v>61.8</v>
+      </c>
+      <c r="E23" s="11">
+        <v>1.67</v>
+      </c>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11">
+        <v>1</v>
+      </c>
+      <c r="H23" s="11">
+        <v>21</v>
+      </c>
+      <c r="I23" s="11"/>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="B24" s="11">
+        <v>30</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" s="11">
+        <v>55.75</v>
+      </c>
+      <c r="E24" s="11">
+        <v>1.61</v>
+      </c>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11">
+        <v>1</v>
+      </c>
+      <c r="H24" s="11">
+        <v>20</v>
+      </c>
+      <c r="I24" s="11"/>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3691,7 +3921,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:9">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3714,7 +3944,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:9">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3737,7 +3967,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:9">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3760,7 +3990,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:9">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3783,7 +4013,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:9">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3806,7 +4036,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:9">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3829,7 +4059,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:9">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4044,12 +4274,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375"/>
+    <col min="1" max="1" width="9.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125"/>
     <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -4966,13 +5196,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="8" max="8" width="10.77734375" customWidth="1"/>
-    <col min="9" max="9" width="28.77734375" customWidth="1"/>
-    <col min="10" max="10" width="33.109375" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="28.83203125" customWidth="1"/>
+    <col min="10" max="10" width="33.1640625" customWidth="1"/>
     <col min="11" max="11" width="36.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.44140625" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -5264,12 +5494,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="8" max="8" width="11.44140625" customWidth="1"/>
-    <col min="9" max="9" width="29.77734375" customWidth="1"/>
+    <col min="8" max="8" width="11.5" customWidth="1"/>
+    <col min="9" max="9" width="29.83203125" customWidth="1"/>
     <col min="10" max="10" width="34" customWidth="1"/>
-    <col min="11" max="11" width="36.77734375" customWidth="1"/>
+    <col min="11" max="11" width="36.83203125" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A16DE9-C835-1A4A-AA7F-200DF90A663F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7EF1EE6-401A-4E3E-AF97-F321F71DE426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29560" yWindow="-3260" windowWidth="38080" windowHeight="20780" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="14016" windowHeight="12336" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="98">
   <si>
     <t>Database No.</t>
   </si>
@@ -380,6 +380,9 @@
   </si>
   <si>
     <t>Height</t>
+  </si>
+  <si>
+    <t>Walk trials (files)</t>
   </si>
 </sst>
 </file>
@@ -786,28 +789,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.1640625" customWidth="1"/>
-    <col min="4" max="4" width="33.83203125" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="4" max="4" width="33.77734375" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="23.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="14.33203125" customWidth="1"/>
     <col min="12" max="12" width="12.6640625" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="28.5" customWidth="1"/>
-    <col min="15" max="15" width="24.5" customWidth="1"/>
+    <col min="14" max="14" width="28.44140625" customWidth="1"/>
+    <col min="15" max="15" width="24.44140625" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="40.83203125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="29.83203125" customWidth="1"/>
+    <col min="17" max="17" width="40.77734375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="29.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" ht="17">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="15.6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -860,7 +863,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="80">
+    <row r="2" spans="1:18" ht="72">
       <c r="A2">
         <v>1</v>
       </c>
@@ -913,7 +916,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="48">
+    <row r="3" spans="1:18" ht="43.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -957,7 +960,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="16">
+    <row r="4" spans="1:18">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -986,7 +989,7 @@
       <c r="I8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="48">
+    <row r="9" spans="1:18" ht="57.6">
       <c r="B9" s="1" t="s">
         <v>37</v>
       </c>
@@ -1015,7 +1018,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="48">
+    <row r="10" spans="1:18" ht="43.2">
       <c r="B10" s="1" t="s">
         <v>42</v>
       </c>
@@ -1082,7 +1085,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="51">
+    <row r="12" spans="1:18" ht="46.8">
       <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
@@ -1123,7 +1126,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="48">
+    <row r="13" spans="1:18" ht="43.2">
       <c r="B13" s="1" t="s">
         <v>63</v>
       </c>
@@ -1186,18 +1189,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" customWidth="1"/>
     <col min="8" max="8" width="16.6640625" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.77734375" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="9.33203125" customWidth="1"/>
     <col min="16" max="16" width="16.6640625" customWidth="1"/>
@@ -1241,7 +1244,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="16">
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1273,7 +1276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="16">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1305,7 +1308,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="16">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1337,7 +1340,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="16">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1369,7 +1372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="16">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1401,7 +1404,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="16">
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1433,7 +1436,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="16">
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1465,7 +1468,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="16">
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1497,7 +1500,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="16">
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1529,7 +1532,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="16">
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1561,7 +1564,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="16">
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1587,7 +1590,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="16">
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1613,7 +1616,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="16">
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1639,7 +1642,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="16">
+    <row r="15" spans="1:16">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1665,7 +1668,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="16">
+    <row r="16" spans="1:16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1691,7 +1694,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="16">
+    <row r="17" spans="1:16">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1717,7 +1720,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="16">
+    <row r="18" spans="1:16">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1743,7 +1746,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="16">
+    <row r="19" spans="1:16">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1769,7 +1772,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="16">
+    <row r="20" spans="1:16">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1795,7 +1798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="16">
+    <row r="21" spans="1:16">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1821,7 +1824,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="16">
+    <row r="22" spans="1:16">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1847,7 +1850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="16">
+    <row r="23" spans="1:16">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1873,7 +1876,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="16">
+    <row r="24" spans="1:16">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1899,7 +1902,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="16">
+    <row r="25" spans="1:16">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1925,7 +1928,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="16">
+    <row r="26" spans="1:16">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1951,7 +1954,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="16">
+    <row r="27" spans="1:16">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1977,7 +1980,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="16">
+    <row r="28" spans="1:16">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2003,7 +2006,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="16">
+    <row r="29" spans="1:16">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2029,7 +2032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="16">
+    <row r="30" spans="1:16">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2055,7 +2058,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="16">
+    <row r="31" spans="1:16">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2081,7 +2084,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="16">
+    <row r="32" spans="1:16">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2107,7 +2110,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="16">
+    <row r="33" spans="1:16">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2133,7 +2136,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="16">
+    <row r="34" spans="1:16">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2159,7 +2162,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="16">
+    <row r="35" spans="1:16">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2185,7 +2188,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="16">
+    <row r="36" spans="1:16">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2211,7 +2214,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="16">
+    <row r="37" spans="1:16">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2237,7 +2240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="16">
+    <row r="38" spans="1:16">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2263,7 +2266,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="16">
+    <row r="39" spans="1:16">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2289,7 +2292,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="16">
+    <row r="40" spans="1:16">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2315,7 +2318,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="16">
+    <row r="41" spans="1:16">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2341,7 +2344,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="16">
+    <row r="42" spans="1:16">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2367,7 +2370,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="16">
+    <row r="43" spans="1:16">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2393,7 +2396,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="16">
+    <row r="44" spans="1:16">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2419,7 +2422,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="16">
+    <row r="45" spans="1:16">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2445,7 +2448,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="16">
+    <row r="46" spans="1:16">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2471,7 +2474,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="16">
+    <row r="47" spans="1:16">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2497,7 +2500,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="16">
+    <row r="48" spans="1:16">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2523,7 +2526,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="16">
+    <row r="49" spans="1:16">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2549,7 +2552,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="16">
+    <row r="50" spans="1:16">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2575,7 +2578,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="16">
+    <row r="51" spans="1:16">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2616,14 +2619,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="8" max="8" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" customWidth="1"/>
     <col min="9" max="9" width="30.6640625" customWidth="1"/>
-    <col min="10" max="10" width="33.1640625" customWidth="1"/>
+    <col min="10" max="10" width="33.109375" customWidth="1"/>
     <col min="11" max="11" width="36.6640625" customWidth="1"/>
-    <col min="12" max="12" width="15.5" customWidth="1"/>
-    <col min="14" max="14" width="14.1640625" customWidth="1"/>
+    <col min="12" max="12" width="15.44140625" customWidth="1"/>
+    <col min="14" max="14" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -3002,7 +3005,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
@@ -3295,7 +3298,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D22FEE7-983F-4E6D-B518-6357D6EFC8AC}">
   <dimension ref="A1:P58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="8" max="8" width="46.33203125" customWidth="1"/>
   </cols>
@@ -3320,7 +3323,7 @@
         <v>75</v>
       </c>
       <c r="H1" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="I1" t="s">
         <v>77</v>
@@ -3343,16 +3346,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
         <v>82</v>
       </c>
       <c r="D2">
-        <v>68.900000000000006</v>
+        <v>81.349999999999994</v>
       </c>
       <c r="E2">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -3375,10 +3378,10 @@
         <v>84</v>
       </c>
       <c r="D3">
-        <v>64.900000000000006</v>
+        <v>58.1</v>
       </c>
       <c r="E3">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -3395,16 +3398,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
         <v>82</v>
       </c>
       <c r="D4">
-        <v>80.8</v>
+        <v>80.900000000000006</v>
       </c>
       <c r="E4">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -3421,16 +3424,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D5">
-        <v>82.7</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="E5">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3444,16 +3447,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D6">
-        <v>54.9</v>
+        <v>82</v>
       </c>
       <c r="E6">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -3470,13 +3473,13 @@
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D7">
-        <v>77.3</v>
+        <v>58.8</v>
       </c>
       <c r="E7">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -3493,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D8">
-        <v>94.2</v>
+        <v>59</v>
       </c>
       <c r="E8">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -3516,13 +3519,13 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D9">
-        <v>69.5</v>
+        <v>56.1</v>
       </c>
       <c r="E9">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -3536,16 +3539,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D10">
-        <v>72</v>
+        <v>52.1</v>
       </c>
       <c r="E10">
-        <v>1.84</v>
+        <v>1.61</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -3559,16 +3562,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D11">
-        <v>52.3</v>
+        <v>71</v>
       </c>
       <c r="E11">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -3582,16 +3585,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
         <v>84</v>
       </c>
       <c r="D12">
-        <v>60.4</v>
+        <v>53.15</v>
       </c>
       <c r="E12">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -3605,16 +3608,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
         <v>84</v>
       </c>
       <c r="D13">
-        <v>55</v>
+        <v>65.150000000000006</v>
       </c>
       <c r="E13">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -3902,17 +3905,17 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25">
-        <v>22</v>
-      </c>
-      <c r="C25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25">
-        <v>62.1</v>
-      </c>
-      <c r="E25">
-        <v>1.62</v>
+      <c r="B25" s="11">
+        <v>20</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="11">
+        <v>69.75</v>
+      </c>
+      <c r="E25" s="11">
+        <v>1.71</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -3925,17 +3928,17 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26">
-        <v>30</v>
-      </c>
-      <c r="C26" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26">
-        <v>80.7</v>
-      </c>
-      <c r="E26">
-        <v>1.74</v>
+      <c r="B26" s="11">
+        <v>22</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="11">
+        <v>66.150000000000006</v>
+      </c>
+      <c r="E26" s="11">
+        <v>1.7</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -3948,17 +3951,17 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27">
-        <v>21</v>
-      </c>
-      <c r="C27" t="s">
-        <v>82</v>
-      </c>
-      <c r="D27">
-        <v>91.2</v>
-      </c>
-      <c r="E27">
-        <v>1.99</v>
+      <c r="B27" s="11">
+        <v>23</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" s="11">
+        <v>73.349999999999994</v>
+      </c>
+      <c r="E27" s="11">
+        <v>1.86</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -3971,17 +3974,17 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28">
-        <v>21</v>
-      </c>
-      <c r="C28" t="s">
-        <v>82</v>
-      </c>
-      <c r="D28">
-        <v>69.5</v>
-      </c>
-      <c r="E28">
-        <v>1.78</v>
+      <c r="B28" s="11">
+        <v>22</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="11">
+        <v>71.75</v>
+      </c>
+      <c r="E28" s="11">
+        <v>1.79</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -3994,17 +3997,17 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29">
-        <v>24</v>
-      </c>
-      <c r="C29" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29">
-        <v>67.5</v>
-      </c>
-      <c r="E29">
-        <v>1.83</v>
+      <c r="B29" s="11">
+        <v>19</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="11">
+        <v>77.75</v>
+      </c>
+      <c r="E29" s="11">
+        <v>1.85</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -4017,17 +4020,17 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30">
-        <v>22</v>
-      </c>
-      <c r="C30" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30">
-        <v>62.1</v>
-      </c>
-      <c r="E30">
-        <v>1.81</v>
+      <c r="B30" s="11">
+        <v>29</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" s="11">
+        <v>68.900000000000006</v>
+      </c>
+      <c r="E30" s="11">
+        <v>1.75</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -4040,16 +4043,16 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31">
-        <v>28</v>
-      </c>
-      <c r="C31" t="s">
-        <v>82</v>
-      </c>
-      <c r="D31">
-        <v>81.349999999999994</v>
-      </c>
-      <c r="E31">
+      <c r="B31" s="11">
+        <v>21</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" s="11">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="E31" s="11">
         <v>1.81</v>
       </c>
       <c r="G31">
@@ -4063,17 +4066,17 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="11">
         <v>21</v>
       </c>
-      <c r="C32" t="s">
-        <v>84</v>
-      </c>
-      <c r="D32">
-        <v>58.1</v>
-      </c>
-      <c r="E32">
-        <v>1.65</v>
+      <c r="C32" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="11">
+        <v>80.8</v>
+      </c>
+      <c r="E32" s="11">
+        <v>1.84</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -4086,17 +4089,17 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="11">
         <v>23</v>
       </c>
-      <c r="C33" t="s">
-        <v>82</v>
-      </c>
-      <c r="D33">
-        <v>80.900000000000006</v>
-      </c>
-      <c r="E33">
-        <v>1.78</v>
+      <c r="C33" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" s="11">
+        <v>82.7</v>
+      </c>
+      <c r="E33" s="11">
+        <v>1.82</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -4109,17 +4112,17 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34">
-        <v>27</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B34" s="11">
+        <v>26</v>
+      </c>
+      <c r="C34" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D34">
-        <v>67.599999999999994</v>
-      </c>
-      <c r="E34">
-        <v>1.68</v>
+      <c r="D34" s="11">
+        <v>54.9</v>
+      </c>
+      <c r="E34" s="11">
+        <v>1.63</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -4132,17 +4135,17 @@
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35">
-        <v>23</v>
-      </c>
-      <c r="C35" t="s">
-        <v>82</v>
-      </c>
-      <c r="D35">
-        <v>82</v>
-      </c>
-      <c r="E35">
-        <v>1.78</v>
+      <c r="B35" s="11">
+        <v>21</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D35" s="11">
+        <v>77.3</v>
+      </c>
+      <c r="E35" s="11">
+        <v>1.79</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -4274,12 +4277,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125"/>
+    <col min="1" max="1" width="9.77734375" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375"/>
     <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -5196,13 +5199,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="28.83203125" customWidth="1"/>
-    <col min="10" max="10" width="33.1640625" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" customWidth="1"/>
+    <col min="9" max="9" width="28.77734375" customWidth="1"/>
+    <col min="10" max="10" width="33.109375" customWidth="1"/>
     <col min="11" max="11" width="36.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -5494,12 +5497,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="8" max="8" width="11.5" customWidth="1"/>
-    <col min="9" max="9" width="29.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="9" width="29.77734375" customWidth="1"/>
     <col min="10" max="10" width="34" customWidth="1"/>
-    <col min="11" max="11" width="36.83203125" customWidth="1"/>
+    <col min="11" max="11" width="36.77734375" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7EF1EE6-401A-4E3E-AF97-F321F71DE426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="14016" windowHeight="12336" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7EF1EE6-401A-4E3E-AF97-F321F71DE426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9A62A1-EA7A-7A41-83EC-643873FE09D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="48700" yWindow="-3260" windowWidth="18980" windowHeight="20780" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="105">
   <si>
     <t>Database No.</t>
   </si>
@@ -383,6 +383,27 @@
   </si>
   <si>
     <t>Walk trials (files)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No ID (Force Status): T06, T10, T12, T22 </t>
+  </si>
+  <si>
+    <t>No ID (Force Status): T04, T10</t>
+  </si>
+  <si>
+    <t>No ID (Force Status) at all</t>
+  </si>
+  <si>
+    <t>No ID (force status): T08, T35, T38</t>
+  </si>
+  <si>
+    <t>No ID at all</t>
+  </si>
+  <si>
+    <t>No ID (force status): T19, T24, T32, T39, T40, T41</t>
+  </si>
+  <si>
+    <t>No ID (force status): T02, T25, T26, T33, T45, T46, T47</t>
   </si>
 </sst>
 </file>
@@ -789,28 +810,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.109375" customWidth="1"/>
-    <col min="4" max="4" width="33.77734375" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" customWidth="1"/>
+    <col min="4" max="4" width="33.83203125" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="23.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.5" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="14.33203125" customWidth="1"/>
     <col min="12" max="12" width="12.6640625" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="28.44140625" customWidth="1"/>
-    <col min="15" max="15" width="24.44140625" customWidth="1"/>
+    <col min="14" max="14" width="28.5" customWidth="1"/>
+    <col min="15" max="15" width="24.5" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="40.77734375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="29.77734375" customWidth="1"/>
+    <col min="17" max="17" width="40.83203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="29.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" ht="15.6">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -863,7 +884,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="72">
+    <row r="2" spans="1:18" ht="80">
       <c r="A2">
         <v>1</v>
       </c>
@@ -916,7 +937,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="43.2">
+    <row r="3" spans="1:18" ht="48">
       <c r="A3">
         <v>2</v>
       </c>
@@ -960,7 +981,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" ht="16">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -989,7 +1010,7 @@
       <c r="I8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="57.6">
+    <row r="9" spans="1:18" ht="48">
       <c r="B9" s="1" t="s">
         <v>37</v>
       </c>
@@ -1018,7 +1039,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="43.2">
+    <row r="10" spans="1:18" ht="48">
       <c r="B10" s="1" t="s">
         <v>42</v>
       </c>
@@ -1085,7 +1106,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="46.8">
+    <row r="12" spans="1:18" ht="51">
       <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1147,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="43.2">
+    <row r="13" spans="1:18" ht="48">
       <c r="B13" s="1" t="s">
         <v>63</v>
       </c>
@@ -1189,18 +1210,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.77734375" customWidth="1"/>
+    <col min="7" max="7" width="11.83203125" customWidth="1"/>
     <col min="8" max="8" width="16.6640625" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="16.77734375" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="9.33203125" customWidth="1"/>
     <col min="16" max="16" width="16.6640625" customWidth="1"/>
@@ -1244,7 +1265,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" ht="16">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1276,7 +1297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" ht="16">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1308,7 +1329,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" ht="16">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1340,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" ht="16">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1372,7 +1393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" ht="16">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1404,7 +1425,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" ht="16">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1436,7 +1457,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" ht="16">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1468,7 +1489,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" ht="16">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1500,7 +1521,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" ht="16">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1532,7 +1553,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" ht="16">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1564,7 +1585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" ht="16">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1590,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" ht="16">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1616,7 +1637,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" ht="16">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1642,7 +1663,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" ht="16">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1668,7 +1689,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" ht="16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1694,7 +1715,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" ht="16">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1720,7 +1741,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" ht="16">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1746,7 +1767,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" ht="16">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1772,7 +1793,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" ht="16">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1798,7 +1819,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" ht="16">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1824,7 +1845,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" ht="16">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1850,7 +1871,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" ht="16">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1876,7 +1897,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" ht="16">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1902,7 +1923,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" ht="16">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1928,7 +1949,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" ht="16">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1954,7 +1975,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" ht="16">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1980,7 +2001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" ht="16">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2006,7 +2027,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" ht="16">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2032,7 +2053,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" ht="16">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2058,7 +2079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" ht="16">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2084,7 +2105,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" ht="16">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2110,7 +2131,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" ht="16">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2136,7 +2157,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" ht="16">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2162,7 +2183,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" ht="16">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2188,7 +2209,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" ht="16">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2214,7 +2235,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" ht="16">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2240,7 +2261,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" ht="16">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2266,7 +2287,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" ht="16">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2292,7 +2313,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" ht="16">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2318,7 +2339,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" ht="16">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2344,7 +2365,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" ht="16">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2370,7 +2391,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" ht="16">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2396,7 +2417,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" ht="16">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2422,7 +2443,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" ht="16">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2448,7 +2469,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" ht="16">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2474,7 +2495,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" ht="16">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2500,7 +2521,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" ht="16">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2526,7 +2547,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" ht="16">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2552,7 +2573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" ht="16">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2578,7 +2599,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" ht="16">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2619,14 +2640,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="8" max="8" width="10.44140625" customWidth="1"/>
+    <col min="8" max="8" width="10.5" customWidth="1"/>
     <col min="9" max="9" width="30.6640625" customWidth="1"/>
-    <col min="10" max="10" width="33.109375" customWidth="1"/>
+    <col min="10" max="10" width="33.1640625" customWidth="1"/>
     <col min="11" max="11" width="36.6640625" customWidth="1"/>
-    <col min="12" max="12" width="15.44140625" customWidth="1"/>
-    <col min="14" max="14" width="14.109375" customWidth="1"/>
+    <col min="12" max="12" width="15.5" customWidth="1"/>
+    <col min="14" max="14" width="14.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -3005,7 +3026,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
@@ -3298,9 +3319,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D22FEE7-983F-4E6D-B518-6357D6EFC8AC}">
   <dimension ref="A1:P58"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="8" max="8" width="46.33203125" customWidth="1"/>
+    <col min="6" max="6" width="0.83203125" customWidth="1"/>
+    <col min="7" max="7" width="6.6640625" customWidth="1"/>
+    <col min="8" max="8" width="7.1640625" customWidth="1"/>
+    <col min="9" max="9" width="30.83203125" customWidth="1"/>
+    <col min="10" max="10" width="48.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -3649,7 +3674,9 @@
       <c r="H14" s="11">
         <v>22</v>
       </c>
-      <c r="I14" s="11"/>
+      <c r="I14" s="11" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15">
@@ -3724,7 +3751,9 @@
       <c r="H17" s="11">
         <v>21</v>
       </c>
-      <c r="I17" s="11"/>
+      <c r="I17" s="11" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18">
@@ -3774,7 +3803,9 @@
       <c r="H19" s="11">
         <v>21</v>
       </c>
-      <c r="I19" s="11"/>
+      <c r="I19" s="11" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20">
@@ -4277,12 +4308,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375"/>
+    <col min="1" max="1" width="9.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125"/>
     <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -4578,7 +4610,7 @@
         <v>166.7</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4595,7 +4627,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4612,7 +4644,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4629,7 +4661,7 @@
         <v>173.7</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4646,7 +4678,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:8">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4663,7 +4695,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4680,7 +4712,7 @@
         <v>172.5</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4697,7 +4729,7 @@
         <v>184.5</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4714,7 +4746,7 @@
         <v>172.5</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4731,7 +4763,7 @@
         <v>173.5</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4748,7 +4780,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4765,7 +4797,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:8">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4782,7 +4814,7 @@
         <v>166.2</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4799,7 +4831,7 @@
         <v>172.5</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4816,7 +4848,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:8">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4833,7 +4865,7 @@
         <v>174.5</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:8">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4849,8 +4881,11 @@
       <c r="E32">
         <v>183</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="H32" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4866,8 +4901,11 @@
       <c r="E33">
         <v>169</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="H33" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4883,8 +4921,11 @@
       <c r="E34">
         <v>161</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="H34" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4900,8 +4941,11 @@
       <c r="E35">
         <v>171.5</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="H35" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36">
         <v>35</v>
       </c>
@@ -4917,8 +4961,11 @@
       <c r="E36">
         <v>175.5</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="H36" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4934,8 +4981,11 @@
       <c r="E37">
         <v>169.6</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="H37" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4951,8 +5001,11 @@
       <c r="E38">
         <v>186.6</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="H38" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4968,8 +5021,11 @@
       <c r="E39">
         <v>180.7</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="H39" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4985,8 +5041,11 @@
       <c r="E40">
         <v>170</v>
       </c>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="H40" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5002,8 +5061,11 @@
       <c r="E41">
         <v>183.6</v>
       </c>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="H41" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5020,7 +5082,7 @@
         <v>185.5</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:8">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5037,7 +5099,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:8">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5054,7 +5116,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:8">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5071,7 +5133,7 @@
         <v>164.5</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:8">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5088,7 +5150,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:8">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5105,7 +5167,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:8">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5199,13 +5261,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="8" max="8" width="10.77734375" customWidth="1"/>
-    <col min="9" max="9" width="28.77734375" customWidth="1"/>
-    <col min="10" max="10" width="33.109375" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="28.83203125" customWidth="1"/>
+    <col min="10" max="10" width="33.1640625" customWidth="1"/>
     <col min="11" max="11" width="36.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.44140625" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -5497,12 +5559,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="8" max="8" width="11.44140625" customWidth="1"/>
-    <col min="9" max="9" width="29.77734375" customWidth="1"/>
+    <col min="8" max="8" width="11.5" customWidth="1"/>
+    <col min="9" max="9" width="29.83203125" customWidth="1"/>
     <col min="10" max="10" width="34" customWidth="1"/>
-    <col min="11" max="11" width="36.77734375" customWidth="1"/>
+    <col min="11" max="11" width="36.83203125" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9A62A1-EA7A-7A41-83EC-643873FE09D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="48700" yWindow="-3260" windowWidth="18980" windowHeight="20780" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="48700" yWindow="-3260" windowWidth="18980" windowHeight="20780" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9A62A1-EA7A-7A41-83EC-643873FE09D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3024802E-79F7-43EF-B2B7-4BBC2CBDB3DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="48700" yWindow="-3260" windowWidth="18980" windowHeight="20780" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -810,28 +810,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.1640625" customWidth="1"/>
-    <col min="4" max="4" width="33.83203125" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="4" max="4" width="33.77734375" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="23.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="14.33203125" customWidth="1"/>
     <col min="12" max="12" width="12.6640625" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="28.5" customWidth="1"/>
-    <col min="15" max="15" width="24.5" customWidth="1"/>
+    <col min="14" max="14" width="28.44140625" customWidth="1"/>
+    <col min="15" max="15" width="24.44140625" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="40.83203125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="29.83203125" customWidth="1"/>
+    <col min="17" max="17" width="40.77734375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="29.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" ht="17">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="15.6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -884,7 +884,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="80">
+    <row r="2" spans="1:18" ht="72">
       <c r="A2">
         <v>1</v>
       </c>
@@ -937,7 +937,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="48">
+    <row r="3" spans="1:18" ht="43.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -981,7 +981,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="16">
+    <row r="4" spans="1:18">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1010,7 +1010,7 @@
       <c r="I8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="48">
+    <row r="9" spans="1:18" ht="57.6">
       <c r="B9" s="1" t="s">
         <v>37</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="48">
+    <row r="10" spans="1:18" ht="43.2">
       <c r="B10" s="1" t="s">
         <v>42</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="51">
+    <row r="12" spans="1:18" ht="46.8">
       <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="48">
+    <row r="13" spans="1:18" ht="43.2">
       <c r="B13" s="1" t="s">
         <v>63</v>
       </c>
@@ -1210,18 +1210,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" customWidth="1"/>
     <col min="8" max="8" width="16.6640625" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.77734375" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="9.33203125" customWidth="1"/>
     <col min="16" max="16" width="16.6640625" customWidth="1"/>
@@ -1265,7 +1265,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="16">
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="16">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="16">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="16">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="16">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="16">
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="16">
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="16">
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="16">
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="16">
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="16">
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="16">
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="16">
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="16">
+    <row r="15" spans="1:16">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="16">
+    <row r="16" spans="1:16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1715,7 +1715,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="16">
+    <row r="17" spans="1:16">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="16">
+    <row r="18" spans="1:16">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="16">
+    <row r="19" spans="1:16">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="16">
+    <row r="20" spans="1:16">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="16">
+    <row r="21" spans="1:16">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="16">
+    <row r="22" spans="1:16">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="16">
+    <row r="23" spans="1:16">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="16">
+    <row r="24" spans="1:16">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="16">
+    <row r="25" spans="1:16">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="16">
+    <row r="26" spans="1:16">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="16">
+    <row r="27" spans="1:16">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="16">
+    <row r="28" spans="1:16">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="16">
+    <row r="29" spans="1:16">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="16">
+    <row r="30" spans="1:16">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="16">
+    <row r="31" spans="1:16">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="16">
+    <row r="32" spans="1:16">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="16">
+    <row r="33" spans="1:16">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="16">
+    <row r="34" spans="1:16">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="16">
+    <row r="35" spans="1:16">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="16">
+    <row r="36" spans="1:16">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="16">
+    <row r="37" spans="1:16">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="16">
+    <row r="38" spans="1:16">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="16">
+    <row r="39" spans="1:16">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="16">
+    <row r="40" spans="1:16">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="16">
+    <row r="41" spans="1:16">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="16">
+    <row r="42" spans="1:16">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="16">
+    <row r="43" spans="1:16">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2417,7 +2417,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="16">
+    <row r="44" spans="1:16">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="16">
+    <row r="45" spans="1:16">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="16">
+    <row r="46" spans="1:16">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="16">
+    <row r="47" spans="1:16">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="16">
+    <row r="48" spans="1:16">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="16">
+    <row r="49" spans="1:16">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="16">
+    <row r="50" spans="1:16">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="16">
+    <row r="51" spans="1:16">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2640,14 +2640,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="8" max="8" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" customWidth="1"/>
     <col min="9" max="9" width="30.6640625" customWidth="1"/>
-    <col min="10" max="10" width="33.1640625" customWidth="1"/>
+    <col min="10" max="10" width="33.109375" customWidth="1"/>
     <col min="11" max="11" width="36.6640625" customWidth="1"/>
-    <col min="12" max="12" width="15.5" customWidth="1"/>
-    <col min="14" max="14" width="14.1640625" customWidth="1"/>
+    <col min="12" max="12" width="15.44140625" customWidth="1"/>
+    <col min="14" max="14" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2699,7 +2699,7 @@
         <v>74</v>
       </c>
       <c r="E2">
-        <v>175</v>
+        <v>1.75</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -2728,7 +2728,7 @@
         <v>72</v>
       </c>
       <c r="E3">
-        <v>172</v>
+        <v>1.72</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -2757,7 +2757,7 @@
         <v>80</v>
       </c>
       <c r="E4">
-        <v>178</v>
+        <v>1.78</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -2786,7 +2786,7 @@
         <v>60</v>
       </c>
       <c r="E5">
-        <v>170</v>
+        <v>1.7</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -2812,7 +2812,7 @@
         <v>71</v>
       </c>
       <c r="E6">
-        <v>171</v>
+        <v>1.71</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -2835,7 +2835,7 @@
         <v>65</v>
       </c>
       <c r="E7">
-        <v>168</v>
+        <v>1.68</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -2858,7 +2858,7 @@
         <v>72</v>
       </c>
       <c r="E8">
-        <v>176</v>
+        <v>1.76</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -2881,7 +2881,7 @@
         <v>85</v>
       </c>
       <c r="E9">
-        <v>181</v>
+        <v>1.81</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -2904,7 +2904,7 @@
         <v>76</v>
       </c>
       <c r="E10">
-        <v>183</v>
+        <v>1.83</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -2927,7 +2927,7 @@
         <v>80</v>
       </c>
       <c r="E11">
-        <v>182</v>
+        <v>1.82</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -2953,7 +2953,7 @@
         <v>75</v>
       </c>
       <c r="E12">
-        <v>175</v>
+        <v>1.75</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -2979,7 +2979,7 @@
         <v>80</v>
       </c>
       <c r="E13">
-        <v>177</v>
+        <v>1.77</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -3002,7 +3002,7 @@
         <v>58</v>
       </c>
       <c r="E14">
-        <v>170</v>
+        <v>1.7</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -3026,7 +3026,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
@@ -3319,13 +3319,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D22FEE7-983F-4E6D-B518-6357D6EFC8AC}">
   <dimension ref="A1:P58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="6" max="6" width="0.83203125" customWidth="1"/>
+    <col min="6" max="6" width="0.77734375" customWidth="1"/>
     <col min="7" max="7" width="6.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.1640625" customWidth="1"/>
-    <col min="9" max="9" width="30.83203125" customWidth="1"/>
-    <col min="10" max="10" width="48.5" customWidth="1"/>
+    <col min="8" max="8" width="7.109375" customWidth="1"/>
+    <col min="9" max="9" width="30.77734375" customWidth="1"/>
+    <col min="10" max="10" width="48.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -4308,12 +4308,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125"/>
+    <col min="1" max="1" width="9.77734375" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375"/>
     <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" customWidth="1"/>
     <col min="8" max="8" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5261,13 +5261,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="28.83203125" customWidth="1"/>
-    <col min="10" max="10" width="33.1640625" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" customWidth="1"/>
+    <col min="9" max="9" width="28.77734375" customWidth="1"/>
+    <col min="10" max="10" width="33.109375" customWidth="1"/>
     <col min="11" max="11" width="36.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -5559,12 +5559,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="8" max="8" width="11.5" customWidth="1"/>
-    <col min="9" max="9" width="29.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="9" width="29.77734375" customWidth="1"/>
     <col min="10" max="10" width="34" customWidth="1"/>
-    <col min="11" max="11" width="36.83203125" customWidth="1"/>
+    <col min="11" max="11" width="36.77734375" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9A62A1-EA7A-7A41-83EC-643873FE09D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543A890A-ADE4-0144-8342-295F1AAC9F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="48700" yWindow="-3260" windowWidth="18980" windowHeight="20780" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="140" yWindow="840" windowWidth="12560" windowHeight="15660" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="113">
   <si>
     <t>Database No.</t>
   </si>
@@ -404,6 +404,30 @@
   </si>
   <si>
     <t>No ID (force status): T02, T25, T26, T33, T45, T46, T47</t>
+  </si>
+  <si>
+    <t>GaitRec-VR: 3D Gait Analysis for Walking Overground with and without a Head-Mounted-Display in Virtual Reality</t>
+  </si>
+  <si>
+    <t>self-selected speeds</t>
+  </si>
+  <si>
+    <t>21–56</t>
+  </si>
+  <si>
+    <t>170.3 ± 6.6 cm</t>
+  </si>
+  <si>
+    <t>73.9 ± 15.7 kg</t>
+  </si>
+  <si>
+    <t>55 spherical markers</t>
+  </si>
+  <si>
+    <t>https://phaidra.ustp.at/o:5587</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41597-024-03939-0</t>
   </si>
 </sst>
 </file>
@@ -525,7 +549,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -546,6 +570,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -981,12 +1006,54 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="16">
-      <c r="A4" s="5">
+    <row r="4" spans="1:18" ht="48">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>36</v>
+      </c>
+      <c r="C4">
+        <v>2024</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4">
+        <v>20</v>
+      </c>
+      <c r="H4">
+        <v>11</v>
+      </c>
+      <c r="I4">
+        <v>9</v>
+      </c>
+      <c r="J4" t="s">
+        <v>107</v>
+      </c>
+      <c r="K4" t="s">
+        <v>108</v>
+      </c>
+      <c r="L4" t="s">
+        <v>109</v>
+      </c>
+      <c r="O4" t="s">
+        <v>110</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="R4" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -3027,6 +3094,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <cols>
+    <col min="7" max="7" width="8.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
@@ -3070,21 +3140,69 @@
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2">
+        <v>57.5</v>
+      </c>
+      <c r="E2">
+        <v>1.69</v>
+      </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3">
+        <v>66.5</v>
+      </c>
+      <c r="E3">
+        <v>1.67</v>
+      </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>42</v>
+      </c>
+      <c r="C4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4">
+        <v>108.7</v>
+      </c>
+      <c r="E4">
+        <v>1.76</v>
+      </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5">
         <v>4</v>
       </c>
+      <c r="B5">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5">
+        <v>62.8</v>
+      </c>
+      <c r="E5">
+        <v>1.67</v>
+      </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6">
@@ -3100,7 +3218,7 @@
         <v>61</v>
       </c>
       <c r="E6">
-        <v>167</v>
+        <v>1.67</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -3126,7 +3244,7 @@
         <v>71.8</v>
       </c>
       <c r="E7">
-        <v>174</v>
+        <v>1.74</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -3152,7 +3270,7 @@
         <v>100.5</v>
       </c>
       <c r="E8">
-        <v>182</v>
+        <v>1.82</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -3178,7 +3296,7 @@
         <v>60.7</v>
       </c>
       <c r="E9">
-        <v>165</v>
+        <v>1.65</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -3194,21 +3312,69 @@
       <c r="A10">
         <v>9</v>
       </c>
+      <c r="B10">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10">
+        <v>71</v>
+      </c>
+      <c r="E10">
+        <v>1.67</v>
+      </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11">
         <v>10</v>
       </c>
+      <c r="B11">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11">
+        <v>67.5</v>
+      </c>
+      <c r="E11">
+        <v>1.62</v>
+      </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12">
         <v>11</v>
       </c>
+      <c r="B12">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12">
+        <v>94</v>
+      </c>
+      <c r="E12">
+        <v>1.86</v>
+      </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13">
         <v>12</v>
       </c>
+      <c r="B13">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13">
+        <v>54</v>
+      </c>
+      <c r="E13">
+        <v>1.66</v>
+      </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14">
@@ -3218,13 +3384,13 @@
         <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D14">
         <v>67.900000000000006</v>
       </c>
       <c r="E14">
-        <v>166</v>
+        <v>1.66</v>
       </c>
       <c r="L14">
         <v>11</v>
@@ -3244,7 +3410,7 @@
         <v>98</v>
       </c>
       <c r="E15">
-        <v>178</v>
+        <v>1.78</v>
       </c>
       <c r="L15">
         <v>14</v>
@@ -3258,13 +3424,13 @@
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D16">
         <v>61.9</v>
       </c>
       <c r="E16">
-        <v>158</v>
+        <v>1.58</v>
       </c>
       <c r="L16">
         <v>13</v>
@@ -3284,7 +3450,7 @@
         <v>64.7</v>
       </c>
       <c r="E17">
-        <v>170</v>
+        <v>1.7</v>
       </c>
       <c r="L17">
         <v>10</v>
@@ -3294,20 +3460,68 @@
       <c r="A18">
         <v>17</v>
       </c>
+      <c r="B18">
+        <v>46</v>
+      </c>
+      <c r="C18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18">
+        <v>85.5</v>
+      </c>
+      <c r="E18">
+        <v>1.72</v>
+      </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19">
         <v>18</v>
       </c>
+      <c r="B19">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19">
+        <v>67</v>
+      </c>
+      <c r="E19">
+        <v>1.69</v>
+      </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20">
         <v>19</v>
       </c>
+      <c r="B20">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="E20">
+        <v>1.73</v>
+      </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21">
         <v>20</v>
+      </c>
+      <c r="B21">
+        <v>30</v>
+      </c>
+      <c r="C21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21">
+        <v>82.1</v>
+      </c>
+      <c r="E21">
+        <v>1.72</v>
       </c>
     </row>
   </sheetData>
@@ -4369,7 +4583,7 @@
         <v>75.527861547542898</v>
       </c>
       <c r="E2">
-        <v>175</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -4386,7 +4600,7 @@
         <v>75.216410190148395</v>
       </c>
       <c r="E3">
-        <v>165</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -4403,7 +4617,7 @@
         <v>90.178596065609895</v>
       </c>
       <c r="E4">
-        <v>180</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -4420,7 +4634,7 @@
         <v>68.752980738810905</v>
       </c>
       <c r="E5">
-        <v>183.5</v>
+        <v>1.835</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -4437,7 +4651,7 @@
         <v>95.030180507290396</v>
       </c>
       <c r="E6">
-        <v>182.6</v>
+        <v>1.8260000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -4454,7 +4668,7 @@
         <v>70.554727693756206</v>
       </c>
       <c r="E7">
-        <v>167.5</v>
+        <v>1.675</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -4471,7 +4685,7 @@
         <v>90.784376337728006</v>
       </c>
       <c r="E8">
-        <v>185.4</v>
+        <v>1.8540000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -4488,7 +4702,7 @@
         <v>75.6063604141372</v>
       </c>
       <c r="E9">
-        <v>171.6</v>
+        <v>1.716</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -4505,7 +4719,7 @@
         <v>76.357363880860305</v>
       </c>
       <c r="E10">
-        <v>188.8</v>
+        <v>1.8879999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -4522,7 +4736,7 @@
         <v>57.273416314576401</v>
       </c>
       <c r="E11">
-        <v>170.5</v>
+        <v>1.7050000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -4539,7 +4753,7 @@
         <v>68.838643739611896</v>
       </c>
       <c r="E12">
-        <v>170.1</v>
+        <v>1.7010000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -4556,7 +4770,7 @@
         <v>89.765031280522606</v>
       </c>
       <c r="E13">
-        <v>185.6</v>
+        <v>1.8560000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -4573,7 +4787,7 @@
         <v>73.154918953797207</v>
       </c>
       <c r="E14">
-        <v>178</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -4590,7 +4804,7 @@
         <v>94.315477454296001</v>
       </c>
       <c r="E15">
-        <v>176.5</v>
+        <v>1.7649999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -4607,7 +4821,7 @@
         <v>62.864201055909199</v>
       </c>
       <c r="E16">
-        <v>166.7</v>
+        <v>1.667</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -4624,7 +4838,7 @@
         <v>70.474324955046299</v>
       </c>
       <c r="E17">
-        <v>174</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -4641,7 +4855,7 @@
         <v>81.187589890170202</v>
       </c>
       <c r="E18">
-        <v>185</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -4658,7 +4872,7 @@
         <v>73.292966162861603</v>
       </c>
       <c r="E19">
-        <v>173.7</v>
+        <v>1.7370000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -4675,7 +4889,7 @@
         <v>63.2347601966772</v>
       </c>
       <c r="E20">
-        <v>169</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -4692,7 +4906,7 @@
         <v>73.268840066888799</v>
       </c>
       <c r="E21">
-        <v>177</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -4709,7 +4923,7 @@
         <v>58.029067769687003</v>
       </c>
       <c r="E22">
-        <v>172.5</v>
+        <v>1.7250000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -4726,7 +4940,7 @@
         <v>85.818703009347004</v>
       </c>
       <c r="E23">
-        <v>184.5</v>
+        <v>1.845</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -4743,7 +4957,7 @@
         <v>76.065091739440305</v>
       </c>
       <c r="E24">
-        <v>172.5</v>
+        <v>1.7250000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -4760,7 +4974,7 @@
         <v>84.500624785972605</v>
       </c>
       <c r="E25">
-        <v>173.5</v>
+        <v>1.7350000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -4777,7 +4991,7 @@
         <v>80.189139537331101</v>
       </c>
       <c r="E26">
-        <v>178</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -4794,7 +5008,7 @@
         <v>81.482945334893799</v>
       </c>
       <c r="E27">
-        <v>175</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4811,7 +5025,7 @@
         <v>62.231371023998598</v>
       </c>
       <c r="E28">
-        <v>166.2</v>
+        <v>1.6619999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -4828,7 +5042,7 @@
         <v>103.593135418738</v>
       </c>
       <c r="E29">
-        <v>172.5</v>
+        <v>1.7250000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -4845,7 +5059,7 @@
         <v>89.521141517738698</v>
       </c>
       <c r="E30">
-        <v>170</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -4862,7 +5076,7 @@
         <v>68.862616007902801</v>
       </c>
       <c r="E31">
-        <v>174.5</v>
+        <v>1.7450000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -4879,7 +5093,7 @@
         <v>80.579689644200002</v>
       </c>
       <c r="E32">
-        <v>183</v>
+        <v>1.83</v>
       </c>
       <c r="H32" t="s">
         <v>102</v>
@@ -4899,7 +5113,7 @@
         <v>68.146280219349904</v>
       </c>
       <c r="E33">
-        <v>169</v>
+        <v>1.69</v>
       </c>
       <c r="H33" t="s">
         <v>101</v>
@@ -4919,7 +5133,7 @@
         <v>76.350187907485605</v>
       </c>
       <c r="E34">
-        <v>161</v>
+        <v>1.61</v>
       </c>
       <c r="H34" t="s">
         <v>102</v>
@@ -4939,7 +5153,7 @@
         <v>75.240691431495094</v>
       </c>
       <c r="E35">
-        <v>171.5</v>
+        <v>1.7150000000000001</v>
       </c>
       <c r="H35" t="s">
         <v>102</v>
@@ -4959,7 +5173,7 @@
         <v>84.462231629890397</v>
       </c>
       <c r="E36">
-        <v>175.5</v>
+        <v>1.7549999999999999</v>
       </c>
       <c r="H36" t="s">
         <v>102</v>
@@ -4979,7 +5193,7 @@
         <v>54.140492711229903</v>
       </c>
       <c r="E37">
-        <v>169.6</v>
+        <v>1.696</v>
       </c>
       <c r="H37" t="s">
         <v>102</v>
@@ -4999,7 +5213,7 @@
         <v>90.3777449015748</v>
       </c>
       <c r="E38">
-        <v>186.6</v>
+        <v>1.8660000000000001</v>
       </c>
       <c r="H38" t="s">
         <v>102</v>
@@ -5019,7 +5233,7 @@
         <v>76.818976821680806</v>
       </c>
       <c r="E39">
-        <v>180.7</v>
+        <v>1.8069999999999999</v>
       </c>
       <c r="H39" t="s">
         <v>103</v>
@@ -5039,7 +5253,7 @@
         <v>63.023042292533198</v>
       </c>
       <c r="E40">
-        <v>170</v>
+        <v>1.7</v>
       </c>
       <c r="H40" t="s">
         <v>104</v>
@@ -5059,7 +5273,7 @@
         <v>136.13657014312699</v>
       </c>
       <c r="E41">
-        <v>183.6</v>
+        <v>1.8360000000000001</v>
       </c>
       <c r="H41" t="s">
         <v>102</v>
@@ -5079,7 +5293,7 @@
         <v>85.778406001692602</v>
       </c>
       <c r="E42">
-        <v>185.5</v>
+        <v>1.855</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -5096,7 +5310,7 @@
         <v>79.409803278182807</v>
       </c>
       <c r="E43">
-        <v>178</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -5113,7 +5327,7 @@
         <v>61.022674401557197</v>
       </c>
       <c r="E44">
-        <v>179</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -5130,7 +5344,7 @@
         <v>61.324277567479101</v>
       </c>
       <c r="E45">
-        <v>164.5</v>
+        <v>1.645</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -5147,7 +5361,7 @@
         <v>79.018618686461394</v>
       </c>
       <c r="E46">
-        <v>163</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -5164,7 +5378,7 @@
         <v>64.610276323420507</v>
       </c>
       <c r="E47">
-        <v>165</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -5181,7 +5395,7 @@
         <v>61.061758542644803</v>
       </c>
       <c r="E48">
-        <v>165.8</v>
+        <v>1.6579999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -5198,7 +5412,7 @@
         <v>68.4202597262979</v>
       </c>
       <c r="E49">
-        <v>171.5</v>
+        <v>1.7150000000000001</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -5215,7 +5429,7 @@
         <v>80.633207153808499</v>
       </c>
       <c r="E50">
-        <v>174.5</v>
+        <v>1.7450000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -5232,7 +5446,7 @@
         <v>96.299047509172397</v>
       </c>
       <c r="E51">
-        <v>174.2</v>
+        <v>1.742</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -5249,7 +5463,7 @@
         <v>65.733442413113394</v>
       </c>
       <c r="E52">
-        <v>169.5</v>
+        <v>1.6950000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -549,7 +549,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -570,7 +570,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1007,7 +1006,7 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="48">
-      <c r="A4" s="12">
+      <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543A890A-ADE4-0144-8342-295F1AAC9F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2FAFB5B-05D2-4FE9-ACB0-BFD4FCA9B7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="840" windowWidth="12560" windowHeight="15660" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -376,12 +376,6 @@
     <t>No ID</t>
   </si>
   <si>
-    <t>Mass</t>
-  </si>
-  <si>
-    <t>Height</t>
-  </si>
-  <si>
     <t>Walk trials (files)</t>
   </si>
   <si>
@@ -428,6 +422,12 @@
   </si>
   <si>
     <t>https://www.nature.com/articles/s41597-024-03939-0</t>
+  </si>
+  <si>
+    <t>Mass (kg)</t>
+  </si>
+  <si>
+    <t>Participant</t>
   </si>
 </sst>
 </file>
@@ -834,28 +834,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.1640625" customWidth="1"/>
-    <col min="4" max="4" width="33.83203125" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="4" max="4" width="33.77734375" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="23.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="14.33203125" customWidth="1"/>
     <col min="12" max="12" width="12.6640625" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="28.5" customWidth="1"/>
-    <col min="15" max="15" width="24.5" customWidth="1"/>
+    <col min="14" max="14" width="28.44140625" customWidth="1"/>
+    <col min="15" max="15" width="24.44140625" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="40.83203125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="29.83203125" customWidth="1"/>
+    <col min="17" max="17" width="40.77734375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="29.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" ht="17">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="15.6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -908,7 +908,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="80">
+    <row r="2" spans="1:18" ht="72">
       <c r="A2">
         <v>1</v>
       </c>
@@ -961,7 +961,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="48">
+    <row r="3" spans="1:18" ht="43.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="48">
+    <row r="4" spans="1:18" ht="57.6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1016,13 +1016,13 @@
         <v>2024</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G4">
         <v>20</v>
@@ -1034,25 +1034,25 @@
         <v>9</v>
       </c>
       <c r="J4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L4" t="s">
         <v>107</v>
       </c>
-      <c r="K4" t="s">
+      <c r="O4" t="s">
         <v>108</v>
       </c>
-      <c r="L4" t="s">
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="O4" t="s">
+      <c r="R4" t="s">
         <v>110</v>
-      </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="R4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1076,7 +1076,7 @@
       <c r="I8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="48">
+    <row r="9" spans="1:18" ht="57.6">
       <c r="B9" s="1" t="s">
         <v>37</v>
       </c>
@@ -1105,7 +1105,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="48">
+    <row r="10" spans="1:18" ht="43.2">
       <c r="B10" s="1" t="s">
         <v>42</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="51">
+    <row r="12" spans="1:18" ht="46.8">
       <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
@@ -1213,7 +1213,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="48">
+    <row r="13" spans="1:18" ht="43.2">
       <c r="B13" s="1" t="s">
         <v>63</v>
       </c>
@@ -1276,18 +1276,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" customWidth="1"/>
     <col min="8" max="8" width="16.6640625" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.77734375" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="9.33203125" customWidth="1"/>
     <col min="16" max="16" width="16.6640625" customWidth="1"/>
@@ -1304,7 +1304,7 @@
         <v>72</v>
       </c>
       <c r="D1" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="E1" t="s">
         <v>74</v>
@@ -1331,7 +1331,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="16">
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="16">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="16">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="16">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="16">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="16">
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="16">
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="16">
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="16">
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1619,7 +1619,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="16">
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="16">
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="16">
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="16">
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="16">
+    <row r="15" spans="1:16">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="16">
+    <row r="16" spans="1:16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="16">
+    <row r="17" spans="1:16">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="16">
+    <row r="18" spans="1:16">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="16">
+    <row r="19" spans="1:16">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="16">
+    <row r="20" spans="1:16">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="16">
+    <row r="21" spans="1:16">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="16">
+    <row r="22" spans="1:16">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="16">
+    <row r="23" spans="1:16">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="16">
+    <row r="24" spans="1:16">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="16">
+    <row r="25" spans="1:16">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="16">
+    <row r="26" spans="1:16">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="16">
+    <row r="27" spans="1:16">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="16">
+    <row r="28" spans="1:16">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="16">
+    <row r="29" spans="1:16">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="16">
+    <row r="30" spans="1:16">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="16">
+    <row r="31" spans="1:16">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="16">
+    <row r="32" spans="1:16">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="16">
+    <row r="33" spans="1:16">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="16">
+    <row r="34" spans="1:16">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="16">
+    <row r="35" spans="1:16">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="16">
+    <row r="36" spans="1:16">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="16">
+    <row r="37" spans="1:16">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="16">
+    <row r="38" spans="1:16">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="16">
+    <row r="39" spans="1:16">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="16">
+    <row r="40" spans="1:16">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2405,7 +2405,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="16">
+    <row r="41" spans="1:16">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="16">
+    <row r="42" spans="1:16">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="16">
+    <row r="43" spans="1:16">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="16">
+    <row r="44" spans="1:16">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="16">
+    <row r="45" spans="1:16">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="16">
+    <row r="46" spans="1:16">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="16">
+    <row r="47" spans="1:16">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="16">
+    <row r="48" spans="1:16">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="16">
+    <row r="49" spans="1:16">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="16">
+    <row r="50" spans="1:16">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="16">
+    <row r="51" spans="1:16">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2706,14 +2706,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="8" max="8" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" customWidth="1"/>
     <col min="9" max="9" width="30.6640625" customWidth="1"/>
-    <col min="10" max="10" width="33.1640625" customWidth="1"/>
+    <col min="10" max="10" width="33.109375" customWidth="1"/>
     <col min="11" max="11" width="36.6640625" customWidth="1"/>
-    <col min="12" max="12" width="15.5" customWidth="1"/>
-    <col min="14" max="14" width="14.1640625" customWidth="1"/>
+    <col min="12" max="12" width="15.44140625" customWidth="1"/>
+    <col min="14" max="14" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2727,7 +2727,7 @@
         <v>72</v>
       </c>
       <c r="D1" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="E1" t="s">
         <v>74</v>
@@ -3092,9 +3092,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="7" max="7" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -3108,7 +3108,7 @@
         <v>72</v>
       </c>
       <c r="D1" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="E1" t="s">
         <v>74</v>
@@ -3532,13 +3532,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D22FEE7-983F-4E6D-B518-6357D6EFC8AC}">
   <dimension ref="A1:P58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="6" max="6" width="0.83203125" customWidth="1"/>
+    <col min="6" max="6" width="0.77734375" customWidth="1"/>
     <col min="7" max="7" width="6.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.1640625" customWidth="1"/>
-    <col min="9" max="9" width="30.83203125" customWidth="1"/>
-    <col min="10" max="10" width="48.5" customWidth="1"/>
+    <col min="8" max="8" width="7.109375" customWidth="1"/>
+    <col min="9" max="9" width="30.77734375" customWidth="1"/>
+    <col min="10" max="10" width="48.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -3552,7 +3552,7 @@
         <v>72</v>
       </c>
       <c r="D1" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="E1" t="s">
         <v>74</v>
@@ -3561,7 +3561,7 @@
         <v>75</v>
       </c>
       <c r="H1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I1" t="s">
         <v>77</v>
@@ -3888,7 +3888,7 @@
         <v>22</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -3965,7 +3965,7 @@
         <v>21</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -4017,7 +4017,7 @@
         <v>21</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -4521,18 +4521,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125"/>
+    <col min="1" max="1" width="9.77734375" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375"/>
     <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" customWidth="1"/>
     <col min="8" max="8" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="10" t="s">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>71</v>
@@ -4540,11 +4540,11 @@
       <c r="C1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>96</v>
+      <c r="D1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" t="s">
+        <v>74</v>
       </c>
       <c r="G1" t="s">
         <v>75</v>
@@ -5095,7 +5095,7 @@
         <v>1.83</v>
       </c>
       <c r="H32" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -5115,7 +5115,7 @@
         <v>1.69</v>
       </c>
       <c r="H33" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -5135,7 +5135,7 @@
         <v>1.61</v>
       </c>
       <c r="H34" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -5155,7 +5155,7 @@
         <v>1.7150000000000001</v>
       </c>
       <c r="H35" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -5175,7 +5175,7 @@
         <v>1.7549999999999999</v>
       </c>
       <c r="H36" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -5195,7 +5195,7 @@
         <v>1.696</v>
       </c>
       <c r="H37" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -5215,7 +5215,7 @@
         <v>1.8660000000000001</v>
       </c>
       <c r="H38" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -5235,7 +5235,7 @@
         <v>1.8069999999999999</v>
       </c>
       <c r="H39" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -5255,7 +5255,7 @@
         <v>1.7</v>
       </c>
       <c r="H40" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -5275,7 +5275,7 @@
         <v>1.8360000000000001</v>
       </c>
       <c r="H41" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -5474,13 +5474,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="28.83203125" customWidth="1"/>
-    <col min="10" max="10" width="33.1640625" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" customWidth="1"/>
+    <col min="9" max="9" width="28.77734375" customWidth="1"/>
+    <col min="10" max="10" width="33.109375" customWidth="1"/>
     <col min="11" max="11" width="36.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -5772,12 +5772,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="8" max="8" width="11.5" customWidth="1"/>
-    <col min="9" max="9" width="29.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="9" width="29.77734375" customWidth="1"/>
     <col min="10" max="10" width="34" customWidth="1"/>
-    <col min="11" max="11" width="36.83203125" customWidth="1"/>
+    <col min="11" max="11" width="36.77734375" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543A890A-ADE4-0144-8342-295F1AAC9F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160AA16A-6098-8648-A331-1419E8B71809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="840" windowWidth="12560" windowHeight="15660" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="160" yWindow="820" windowWidth="25280" windowHeight="15660" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -40,6 +40,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -549,7 +571,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -570,6 +592,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3095,6 +3119,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
+    <col min="10" max="10" width="39.6640625" customWidth="1"/>
+    <col min="11" max="11" width="46" customWidth="1"/>
+    <col min="12" max="12" width="65.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -3151,6 +3179,9 @@
       <c r="E2">
         <v>1.69</v>
       </c>
+      <c r="H2" s="13"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
     </row>
     <row r="3" spans="1:16">
       <c r="A3">
@@ -3168,6 +3199,9 @@
       <c r="E3">
         <v>1.67</v>
       </c>
+      <c r="H3" s="13"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
     </row>
     <row r="4" spans="1:16">
       <c r="A4">
@@ -3185,6 +3219,9 @@
       <c r="E4">
         <v>1.76</v>
       </c>
+      <c r="H4" s="13"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
     </row>
     <row r="5" spans="1:16">
       <c r="A5">
@@ -3202,6 +3239,9 @@
       <c r="E5">
         <v>1.67</v>
       </c>
+      <c r="H5" s="13"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6">
@@ -3222,12 +3262,11 @@
       <c r="G6">
         <v>2</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="13">
         <v>10</v>
       </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7">
@@ -3248,12 +3287,11 @@
       <c r="G7">
         <v>2</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="13">
         <v>10</v>
       </c>
-      <c r="L7">
-        <v>10</v>
-      </c>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8">
@@ -3274,12 +3312,11 @@
       <c r="G8">
         <v>2</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="13">
         <v>12</v>
       </c>
-      <c r="L8">
-        <v>12</v>
-      </c>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9">
@@ -3300,12 +3337,11 @@
       <c r="G9">
         <v>2</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="13">
         <v>10</v>
       </c>
-      <c r="L9">
-        <v>10</v>
-      </c>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
     </row>
     <row r="10" spans="1:16">
       <c r="A10">
@@ -3323,6 +3359,9 @@
       <c r="E10">
         <v>1.67</v>
       </c>
+      <c r="H10" s="13"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
     </row>
     <row r="11" spans="1:16">
       <c r="A11">
@@ -3340,6 +3379,9 @@
       <c r="E11">
         <v>1.62</v>
       </c>
+      <c r="H11" s="13"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
     </row>
     <row r="12" spans="1:16">
       <c r="A12">
@@ -3357,6 +3399,9 @@
       <c r="E12">
         <v>1.86</v>
       </c>
+      <c r="H12" s="13"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
     </row>
     <row r="13" spans="1:16">
       <c r="A13">
@@ -3374,6 +3419,9 @@
       <c r="E13">
         <v>1.66</v>
       </c>
+      <c r="H13" s="13"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
     </row>
     <row r="14" spans="1:16">
       <c r="A14">
@@ -3391,9 +3439,9 @@
       <c r="E14">
         <v>1.66</v>
       </c>
-      <c r="L14">
-        <v>11</v>
-      </c>
+      <c r="H14" s="13"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
     </row>
     <row r="15" spans="1:16">
       <c r="A15">
@@ -3411,9 +3459,9 @@
       <c r="E15">
         <v>1.78</v>
       </c>
-      <c r="L15">
-        <v>14</v>
-      </c>
+      <c r="H15" s="13"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
     </row>
     <row r="16" spans="1:16">
       <c r="A16">
@@ -3431,9 +3479,9 @@
       <c r="E16">
         <v>1.58</v>
       </c>
-      <c r="L16">
-        <v>13</v>
-      </c>
+      <c r="H16" s="13"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
     </row>
     <row r="17" spans="1:12">
       <c r="A17">
@@ -3451,9 +3499,9 @@
       <c r="E17">
         <v>1.7</v>
       </c>
-      <c r="L17">
-        <v>10</v>
-      </c>
+      <c r="H17" s="13"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18">
@@ -3471,6 +3519,9 @@
       <c r="E18">
         <v>1.72</v>
       </c>
+      <c r="H18" s="13"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
     </row>
     <row r="19" spans="1:12">
       <c r="A19">
@@ -3488,6 +3539,9 @@
       <c r="E19">
         <v>1.69</v>
       </c>
+      <c r="H19" s="13"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
     </row>
     <row r="20" spans="1:12">
       <c r="A20">
@@ -3505,6 +3559,9 @@
       <c r="E20">
         <v>1.73</v>
       </c>
+      <c r="H20" s="13"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
     </row>
     <row r="21" spans="1:12">
       <c r="A21">
@@ -3522,6 +3579,9 @@
       <c r="E21">
         <v>1.72</v>
       </c>
+      <c r="H21" s="13"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3539,6 +3599,7 @@
     <col min="8" max="8" width="7.1640625" customWidth="1"/>
     <col min="9" max="9" width="30.83203125" customWidth="1"/>
     <col min="10" max="10" width="48.5" customWidth="1"/>
+    <col min="11" max="11" width="38.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -3602,6 +3663,7 @@
         <v>20</v>
       </c>
       <c r="L2">
+        <f t="shared" ref="L2:L13" si="0">H2-K2</f>
         <v>20</v>
       </c>
     </row>
@@ -3628,6 +3690,7 @@
         <v>18</v>
       </c>
       <c r="L3">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
     </row>
@@ -3654,6 +3717,7 @@
         <v>21</v>
       </c>
       <c r="L4">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
     </row>
@@ -3679,6 +3743,10 @@
       <c r="H5">
         <v>20</v>
       </c>
+      <c r="L5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6">
@@ -3702,6 +3770,10 @@
       <c r="H6">
         <v>21</v>
       </c>
+      <c r="L6">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7">
@@ -3725,6 +3797,10 @@
       <c r="H7">
         <v>21</v>
       </c>
+      <c r="L7">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8">
@@ -3748,6 +3824,10 @@
       <c r="H8">
         <v>21</v>
       </c>
+      <c r="L8">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9">
@@ -3771,6 +3851,10 @@
       <c r="H9">
         <v>21</v>
       </c>
+      <c r="L9">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10">
@@ -3794,6 +3878,10 @@
       <c r="H10">
         <v>21</v>
       </c>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11">
@@ -3817,6 +3905,10 @@
       <c r="H11">
         <v>21</v>
       </c>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12">
@@ -3840,6 +3932,10 @@
       <c r="H12">
         <v>20</v>
       </c>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13">
@@ -3863,6 +3959,10 @@
       <c r="H13">
         <v>22</v>
       </c>
+      <c r="L13">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14">
@@ -3890,6 +3990,13 @@
       <c r="I14" s="11" t="s">
         <v>98</v>
       </c>
+      <c r="K14">
+        <v>4</v>
+      </c>
+      <c r="L14">
+        <f>H14-K14</f>
+        <v>18</v>
+      </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15">
@@ -3915,6 +4022,10 @@
         <v>21</v>
       </c>
       <c r="I15" s="11"/>
+      <c r="L15">
+        <f t="shared" ref="L15:L35" si="1">H15-K15</f>
+        <v>21</v>
+      </c>
     </row>
     <row r="16" spans="1:16">
       <c r="A16">
@@ -3940,8 +4051,12 @@
         <v>21</v>
       </c>
       <c r="I16" s="11"/>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="L16">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3967,8 +4082,15 @@
       <c r="I17" s="11" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="K17">
+        <v>2</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3992,8 +4114,12 @@
         <v>20</v>
       </c>
       <c r="I18" s="11"/>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="L18">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4019,8 +4145,15 @@
       <c r="I19" s="11" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="K19">
+        <v>21</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4044,8 +4177,12 @@
         <v>20</v>
       </c>
       <c r="I20" s="11"/>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="L20">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4069,8 +4206,12 @@
         <v>20</v>
       </c>
       <c r="I21" s="11"/>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="L21">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4094,8 +4235,12 @@
         <v>21</v>
       </c>
       <c r="I22" s="11"/>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="L22">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4119,8 +4264,12 @@
         <v>21</v>
       </c>
       <c r="I23" s="11"/>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="L23">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4144,8 +4293,12 @@
         <v>20</v>
       </c>
       <c r="I24" s="11"/>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="L24">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4167,8 +4320,12 @@
       <c r="H25">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="1:9">
+      <c r="L25">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4190,8 +4347,12 @@
       <c r="H26">
         <v>23</v>
       </c>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="L26">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4213,8 +4374,12 @@
       <c r="H27">
         <v>22</v>
       </c>
-    </row>
-    <row r="28" spans="1:9">
+      <c r="L27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4236,8 +4401,12 @@
       <c r="H28">
         <v>22</v>
       </c>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="L28">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4259,8 +4428,12 @@
       <c r="H29">
         <v>21</v>
       </c>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="L29">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4282,8 +4455,12 @@
       <c r="H30">
         <v>20</v>
       </c>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="L30">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4305,8 +4482,12 @@
       <c r="H31">
         <v>18</v>
       </c>
-    </row>
-    <row r="32" spans="1:9">
+      <c r="L31">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4328,8 +4509,12 @@
       <c r="H32">
         <v>20</v>
       </c>
-    </row>
-    <row r="33" spans="1:8">
+      <c r="L32">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4351,8 +4536,12 @@
       <c r="H33">
         <v>20</v>
       </c>
-    </row>
-    <row r="34" spans="1:8">
+      <c r="L33">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4374,8 +4563,12 @@
       <c r="H34">
         <v>24</v>
       </c>
-    </row>
-    <row r="35" spans="1:8">
+      <c r="L34">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4397,68 +4590,72 @@
       <c r="H35">
         <v>22</v>
       </c>
-    </row>
-    <row r="36" spans="1:8">
+      <c r="L35">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:12">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:12">
       <c r="A38">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:12">
       <c r="A39">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:12">
       <c r="A40">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:12">
       <c r="A41">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:12">
       <c r="A42">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:12">
       <c r="A43">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:12">
       <c r="A44">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:12">
       <c r="A45">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:12">
       <c r="A46">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:12">
       <c r="A47">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:12">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4528,6 +4725,9 @@
     <col min="4" max="4" width="13.6640625" customWidth="1"/>
     <col min="5" max="5" width="12.5" customWidth="1"/>
     <col min="8" max="8" width="21.33203125" customWidth="1"/>
+    <col min="9" max="9" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="39.5" customWidth="1"/>
+    <col min="11" max="11" width="34.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -4584,6 +4784,10 @@
       <c r="E2">
         <v>1.75</v>
       </c>
+      <c r="L2" cm="1">
+        <f t="array" ref="L2:L52">H2:H52-K2:K52</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3">
@@ -4601,6 +4805,9 @@
       <c r="E3">
         <v>1.65</v>
       </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4">
@@ -4618,6 +4825,9 @@
       <c r="E4">
         <v>1.8</v>
       </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5">
@@ -4635,6 +4845,9 @@
       <c r="E5">
         <v>1.835</v>
       </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6">
@@ -4652,6 +4865,9 @@
       <c r="E6">
         <v>1.8260000000000001</v>
       </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7">
@@ -4669,6 +4885,9 @@
       <c r="E7">
         <v>1.675</v>
       </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8">
@@ -4686,6 +4905,9 @@
       <c r="E8">
         <v>1.8540000000000001</v>
       </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9">
@@ -4703,6 +4925,9 @@
       <c r="E9">
         <v>1.716</v>
       </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10">
@@ -4720,6 +4945,9 @@
       <c r="E10">
         <v>1.8879999999999999</v>
       </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11">
@@ -4737,6 +4965,9 @@
       <c r="E11">
         <v>1.7050000000000001</v>
       </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12">
@@ -4754,6 +4985,9 @@
       <c r="E12">
         <v>1.7010000000000001</v>
       </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13">
@@ -4771,6 +5005,9 @@
       <c r="E13">
         <v>1.8560000000000001</v>
       </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14">
@@ -4788,6 +5025,9 @@
       <c r="E14">
         <v>1.78</v>
       </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15">
@@ -4805,6 +5045,9 @@
       <c r="E15">
         <v>1.7649999999999999</v>
       </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:16">
       <c r="A16">
@@ -4822,8 +5065,11 @@
       <c r="E16">
         <v>1.667</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="L16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4839,8 +5085,11 @@
       <c r="E17">
         <v>1.74</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="L17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4856,8 +5105,11 @@
       <c r="E18">
         <v>1.85</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="L18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4873,8 +5125,11 @@
       <c r="E19">
         <v>1.7370000000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="L19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4890,8 +5145,11 @@
       <c r="E20">
         <v>1.69</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="L20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4907,8 +5165,11 @@
       <c r="E21">
         <v>1.77</v>
       </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="L21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4924,8 +5185,11 @@
       <c r="E22">
         <v>1.7250000000000001</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="L22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4941,8 +5205,11 @@
       <c r="E23">
         <v>1.845</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="L23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4958,8 +5225,11 @@
       <c r="E24">
         <v>1.7250000000000001</v>
       </c>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="L24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4975,8 +5245,11 @@
       <c r="E25">
         <v>1.7350000000000001</v>
       </c>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="L25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4992,8 +5265,11 @@
       <c r="E26">
         <v>1.78</v>
       </c>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="L26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5009,8 +5285,11 @@
       <c r="E27">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="L27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5026,8 +5305,11 @@
       <c r="E28">
         <v>1.6619999999999999</v>
       </c>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="L28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5043,8 +5325,11 @@
       <c r="E29">
         <v>1.7250000000000001</v>
       </c>
-    </row>
-    <row r="30" spans="1:8">
+      <c r="L29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5060,8 +5345,11 @@
       <c r="E30">
         <v>1.7</v>
       </c>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="L30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5077,8 +5365,11 @@
       <c r="E31">
         <v>1.7450000000000001</v>
       </c>
-    </row>
-    <row r="32" spans="1:8">
+      <c r="L31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5094,11 +5385,17 @@
       <c r="E32">
         <v>1.83</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32">
+        <v>40</v>
+      </c>
+      <c r="I32" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="33" spans="1:8">
+      <c r="L32">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5114,11 +5411,20 @@
       <c r="E33">
         <v>1.69</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33">
+        <v>44</v>
+      </c>
+      <c r="I33" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="34" spans="1:8">
+      <c r="K33">
+        <v>3</v>
+      </c>
+      <c r="L33">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5134,11 +5440,17 @@
       <c r="E34">
         <v>1.61</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34">
+        <v>41</v>
+      </c>
+      <c r="I34" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="35" spans="1:8">
+      <c r="L34">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5154,11 +5466,17 @@
       <c r="E35">
         <v>1.7150000000000001</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35">
+        <v>40</v>
+      </c>
+      <c r="I35" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="36" spans="1:8">
+      <c r="L35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5174,11 +5492,17 @@
       <c r="E36">
         <v>1.7549999999999999</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36">
+        <v>43</v>
+      </c>
+      <c r="I36" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="37" spans="1:8">
+      <c r="L36">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5194,11 +5518,17 @@
       <c r="E37">
         <v>1.696</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H37">
+        <v>40</v>
+      </c>
+      <c r="I37" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="38" spans="1:8">
+      <c r="L37">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5214,11 +5544,17 @@
       <c r="E38">
         <v>1.8660000000000001</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38">
+        <v>43</v>
+      </c>
+      <c r="I38" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="39" spans="1:8">
+      <c r="L38">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5234,11 +5570,20 @@
       <c r="E39">
         <v>1.8069999999999999</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39">
+        <v>40</v>
+      </c>
+      <c r="I39" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="40" spans="1:8">
+      <c r="K39">
+        <v>6</v>
+      </c>
+      <c r="L39">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5254,11 +5599,20 @@
       <c r="E40">
         <v>1.7</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H40">
+        <v>44</v>
+      </c>
+      <c r="I40" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="41" spans="1:8">
+      <c r="K40">
+        <v>7</v>
+      </c>
+      <c r="L40">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5274,11 +5628,17 @@
       <c r="E41">
         <v>1.8360000000000001</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H41">
+        <v>40</v>
+      </c>
+      <c r="I41" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="42" spans="1:8">
+      <c r="L41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5294,8 +5654,11 @@
       <c r="E42">
         <v>1.855</v>
       </c>
-    </row>
-    <row r="43" spans="1:8">
+      <c r="L42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5311,8 +5674,11 @@
       <c r="E43">
         <v>1.78</v>
       </c>
-    </row>
-    <row r="44" spans="1:8">
+      <c r="L43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5328,8 +5694,11 @@
       <c r="E44">
         <v>1.79</v>
       </c>
-    </row>
-    <row r="45" spans="1:8">
+      <c r="L44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5345,8 +5714,11 @@
       <c r="E45">
         <v>1.645</v>
       </c>
-    </row>
-    <row r="46" spans="1:8">
+      <c r="L45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5362,8 +5734,11 @@
       <c r="E46">
         <v>1.63</v>
       </c>
-    </row>
-    <row r="47" spans="1:8">
+      <c r="L46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5379,8 +5754,11 @@
       <c r="E47">
         <v>1.65</v>
       </c>
-    </row>
-    <row r="48" spans="1:8">
+      <c r="L47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5396,8 +5774,11 @@
       <c r="E48">
         <v>1.6579999999999999</v>
       </c>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="L48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5413,8 +5794,11 @@
       <c r="E49">
         <v>1.7150000000000001</v>
       </c>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="L49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5430,8 +5814,11 @@
       <c r="E50">
         <v>1.7450000000000001</v>
       </c>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="L50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5447,8 +5834,11 @@
       <c r="E51">
         <v>1.742</v>
       </c>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="L51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5463,6 +5853,9 @@
       </c>
       <c r="E52">
         <v>1.6950000000000001</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2FAFB5B-05D2-4FE9-ACB0-BFD4FCA9B7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A0DC64-AF30-FD44-84BC-E5730575DD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="160" yWindow="840" windowWidth="25280" windowHeight="15640" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -40,6 +40,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -834,28 +856,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.109375" customWidth="1"/>
-    <col min="4" max="4" width="33.77734375" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" customWidth="1"/>
+    <col min="4" max="4" width="33.83203125" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="23.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.5" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="14.33203125" customWidth="1"/>
     <col min="12" max="12" width="12.6640625" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="28.44140625" customWidth="1"/>
-    <col min="15" max="15" width="24.44140625" customWidth="1"/>
+    <col min="14" max="14" width="28.5" customWidth="1"/>
+    <col min="15" max="15" width="24.5" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="40.77734375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="29.77734375" customWidth="1"/>
+    <col min="17" max="17" width="40.83203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="29.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" ht="15.6">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -908,7 +930,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="72">
+    <row r="2" spans="1:18" ht="80">
       <c r="A2">
         <v>1</v>
       </c>
@@ -961,7 +983,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="43.2">
+    <row r="3" spans="1:18" ht="48">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1005,7 +1027,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="57.6">
+    <row r="4" spans="1:18" ht="48">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1076,7 +1098,7 @@
       <c r="I8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="57.6">
+    <row r="9" spans="1:18" ht="48">
       <c r="B9" s="1" t="s">
         <v>37</v>
       </c>
@@ -1105,7 +1127,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="43.2">
+    <row r="10" spans="1:18" ht="48">
       <c r="B10" s="1" t="s">
         <v>42</v>
       </c>
@@ -1172,7 +1194,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="46.8">
+    <row r="12" spans="1:18" ht="51">
       <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
@@ -1213,7 +1235,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="43.2">
+    <row r="13" spans="1:18" ht="48">
       <c r="B13" s="1" t="s">
         <v>63</v>
       </c>
@@ -1276,18 +1298,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.77734375" customWidth="1"/>
+    <col min="7" max="7" width="11.83203125" customWidth="1"/>
     <col min="8" max="8" width="16.6640625" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="16.77734375" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="9.33203125" customWidth="1"/>
     <col min="16" max="16" width="16.6640625" customWidth="1"/>
@@ -1331,7 +1353,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" ht="16">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1363,7 +1385,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" ht="16">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1395,7 +1417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" ht="16">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1427,7 +1449,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" ht="16">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1459,7 +1481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" ht="16">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1491,7 +1513,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" ht="16">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1523,7 +1545,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" ht="16">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1555,7 +1577,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" ht="16">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1587,7 +1609,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" ht="16">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1619,7 +1641,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" ht="16">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1651,7 +1673,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" ht="16">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1677,7 +1699,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" ht="16">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1703,7 +1725,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" ht="16">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1729,7 +1751,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" ht="16">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1755,7 +1777,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" ht="16">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1781,7 +1803,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" ht="16">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1807,7 +1829,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" ht="16">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1833,7 +1855,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" ht="16">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1859,7 +1881,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" ht="16">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1885,7 +1907,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" ht="16">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1911,7 +1933,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" ht="16">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1937,7 +1959,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" ht="16">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1963,7 +1985,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" ht="16">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1989,7 +2011,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" ht="16">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2015,7 +2037,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" ht="16">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2041,7 +2063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" ht="16">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2067,7 +2089,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" ht="16">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2093,7 +2115,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" ht="16">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2119,7 +2141,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" ht="16">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2145,7 +2167,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" ht="16">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2171,7 +2193,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" ht="16">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2197,7 +2219,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" ht="16">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2223,7 +2245,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" ht="16">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2249,7 +2271,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" ht="16">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2275,7 +2297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" ht="16">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2301,7 +2323,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" ht="16">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2327,7 +2349,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" ht="16">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2353,7 +2375,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" ht="16">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2379,7 +2401,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" ht="16">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2405,7 +2427,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" ht="16">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2431,7 +2453,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" ht="16">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2457,7 +2479,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" ht="16">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2483,7 +2505,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" ht="16">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2509,7 +2531,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" ht="16">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2535,7 +2557,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" ht="16">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2561,7 +2583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" ht="16">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2587,7 +2609,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" ht="16">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2613,7 +2635,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" ht="16">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2639,7 +2661,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" ht="16">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2665,7 +2687,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" ht="16">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2706,14 +2728,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="8" max="8" width="10.44140625" customWidth="1"/>
+    <col min="8" max="8" width="10.5" customWidth="1"/>
     <col min="9" max="9" width="30.6640625" customWidth="1"/>
-    <col min="10" max="10" width="33.109375" customWidth="1"/>
+    <col min="10" max="10" width="33.1640625" customWidth="1"/>
     <col min="11" max="11" width="36.6640625" customWidth="1"/>
-    <col min="12" max="12" width="15.44140625" customWidth="1"/>
-    <col min="14" max="14" width="14.109375" customWidth="1"/>
+    <col min="12" max="12" width="15.5" customWidth="1"/>
+    <col min="14" max="14" width="14.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -3092,9 +3114,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="7" max="7" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -3532,13 +3554,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D22FEE7-983F-4E6D-B518-6357D6EFC8AC}">
   <dimension ref="A1:P58"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="6" max="6" width="0.77734375" customWidth="1"/>
+    <col min="6" max="6" width="0.83203125" customWidth="1"/>
     <col min="7" max="7" width="6.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.109375" customWidth="1"/>
-    <col min="9" max="9" width="30.77734375" customWidth="1"/>
-    <col min="10" max="10" width="48.44140625" customWidth="1"/>
+    <col min="8" max="8" width="7.1640625" customWidth="1"/>
+    <col min="9" max="9" width="30.83203125" customWidth="1"/>
+    <col min="10" max="10" width="48.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -4521,13 +4543,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375"/>
+    <col min="1" max="1" width="9.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125"/>
     <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
     <col min="8" max="8" width="21.33203125" customWidth="1"/>
+    <col min="9" max="9" width="35.33203125" customWidth="1"/>
+    <col min="10" max="10" width="50.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -4584,6 +4608,10 @@
       <c r="E2">
         <v>1.75</v>
       </c>
+      <c r="L2" cm="1">
+        <f t="array" ref="L2:L52">H2:H52-K2:K52</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3">
@@ -4601,6 +4629,9 @@
       <c r="E3">
         <v>1.65</v>
       </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4">
@@ -4618,6 +4649,9 @@
       <c r="E4">
         <v>1.8</v>
       </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5">
@@ -4635,6 +4669,9 @@
       <c r="E5">
         <v>1.835</v>
       </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6">
@@ -4652,6 +4689,9 @@
       <c r="E6">
         <v>1.8260000000000001</v>
       </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7">
@@ -4669,6 +4709,9 @@
       <c r="E7">
         <v>1.675</v>
       </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8">
@@ -4686,6 +4729,9 @@
       <c r="E8">
         <v>1.8540000000000001</v>
       </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9">
@@ -4703,6 +4749,9 @@
       <c r="E9">
         <v>1.716</v>
       </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10">
@@ -4720,6 +4769,9 @@
       <c r="E10">
         <v>1.8879999999999999</v>
       </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11">
@@ -4737,6 +4789,9 @@
       <c r="E11">
         <v>1.7050000000000001</v>
       </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12">
@@ -4754,6 +4809,9 @@
       <c r="E12">
         <v>1.7010000000000001</v>
       </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13">
@@ -4771,6 +4829,9 @@
       <c r="E13">
         <v>1.8560000000000001</v>
       </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14">
@@ -4788,6 +4849,9 @@
       <c r="E14">
         <v>1.78</v>
       </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15">
@@ -4805,6 +4869,9 @@
       <c r="E15">
         <v>1.7649999999999999</v>
       </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:16">
       <c r="A16">
@@ -4822,8 +4889,11 @@
       <c r="E16">
         <v>1.667</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="L16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4839,8 +4909,11 @@
       <c r="E17">
         <v>1.74</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="L17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4856,8 +4929,11 @@
       <c r="E18">
         <v>1.85</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="L18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4873,8 +4949,11 @@
       <c r="E19">
         <v>1.7370000000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="L19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4890,8 +4969,11 @@
       <c r="E20">
         <v>1.69</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="L20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4907,8 +4989,11 @@
       <c r="E21">
         <v>1.77</v>
       </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="L21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4924,8 +5009,11 @@
       <c r="E22">
         <v>1.7250000000000001</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="L22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4941,8 +5029,11 @@
       <c r="E23">
         <v>1.845</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="L23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4958,8 +5049,11 @@
       <c r="E24">
         <v>1.7250000000000001</v>
       </c>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="L24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4975,8 +5069,11 @@
       <c r="E25">
         <v>1.7350000000000001</v>
       </c>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="L25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4992,8 +5089,11 @@
       <c r="E26">
         <v>1.78</v>
       </c>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="L26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5009,8 +5109,11 @@
       <c r="E27">
         <v>1.75</v>
       </c>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="L27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5026,8 +5129,11 @@
       <c r="E28">
         <v>1.6619999999999999</v>
       </c>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="L28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5043,8 +5149,11 @@
       <c r="E29">
         <v>1.7250000000000001</v>
       </c>
-    </row>
-    <row r="30" spans="1:8">
+      <c r="L29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5060,8 +5169,11 @@
       <c r="E30">
         <v>1.7</v>
       </c>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="L30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5077,8 +5189,11 @@
       <c r="E31">
         <v>1.7450000000000001</v>
       </c>
-    </row>
-    <row r="32" spans="1:8">
+      <c r="L31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5094,11 +5209,23 @@
       <c r="E32">
         <v>1.83</v>
       </c>
-      <c r="H32" t="s">
+      <c r="G32">
+        <v>3</v>
+      </c>
+      <c r="H32">
+        <v>40</v>
+      </c>
+      <c r="I32" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="33" spans="1:8">
+      <c r="K32">
+        <v>40</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5114,11 +5241,23 @@
       <c r="E33">
         <v>1.69</v>
       </c>
-      <c r="H33" t="s">
+      <c r="G33">
+        <v>3</v>
+      </c>
+      <c r="H33">
+        <v>44</v>
+      </c>
+      <c r="I33" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="34" spans="1:8">
+      <c r="K33">
+        <v>3</v>
+      </c>
+      <c r="L33">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5134,11 +5273,23 @@
       <c r="E34">
         <v>1.61</v>
       </c>
-      <c r="H34" t="s">
+      <c r="G34">
+        <v>3</v>
+      </c>
+      <c r="H34">
+        <v>41</v>
+      </c>
+      <c r="I34" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="35" spans="1:8">
+      <c r="K34">
+        <v>41</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5154,11 +5305,23 @@
       <c r="E35">
         <v>1.7150000000000001</v>
       </c>
-      <c r="H35" t="s">
+      <c r="G35">
+        <v>3</v>
+      </c>
+      <c r="H35">
+        <v>41</v>
+      </c>
+      <c r="I35" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="36" spans="1:8">
+      <c r="K35">
+        <v>41</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5174,11 +5337,23 @@
       <c r="E36">
         <v>1.7549999999999999</v>
       </c>
-      <c r="H36" t="s">
+      <c r="G36">
+        <v>3</v>
+      </c>
+      <c r="H36">
+        <v>40</v>
+      </c>
+      <c r="I36" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="1:8">
+      <c r="K36">
+        <v>40</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5194,11 +5369,23 @@
       <c r="E37">
         <v>1.696</v>
       </c>
-      <c r="H37" t="s">
+      <c r="G37">
+        <v>3</v>
+      </c>
+      <c r="H37">
+        <v>40</v>
+      </c>
+      <c r="I37" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="38" spans="1:8">
+      <c r="K37">
+        <v>40</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5214,11 +5401,23 @@
       <c r="E38">
         <v>1.8660000000000001</v>
       </c>
-      <c r="H38" t="s">
+      <c r="G38">
+        <v>3</v>
+      </c>
+      <c r="H38">
+        <v>43</v>
+      </c>
+      <c r="I38" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="39" spans="1:8">
+      <c r="K38">
+        <v>43</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5234,11 +5433,23 @@
       <c r="E39">
         <v>1.8069999999999999</v>
       </c>
-      <c r="H39" t="s">
+      <c r="G39">
+        <v>3</v>
+      </c>
+      <c r="H39">
+        <v>40</v>
+      </c>
+      <c r="I39" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="40" spans="1:8">
+      <c r="K39">
+        <v>6</v>
+      </c>
+      <c r="L39">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5254,11 +5465,23 @@
       <c r="E40">
         <v>1.7</v>
       </c>
-      <c r="H40" t="s">
+      <c r="G40">
+        <v>3</v>
+      </c>
+      <c r="H40">
+        <v>44</v>
+      </c>
+      <c r="I40" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="41" spans="1:8">
+      <c r="K40">
+        <v>7</v>
+      </c>
+      <c r="L40">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5274,11 +5497,23 @@
       <c r="E41">
         <v>1.8360000000000001</v>
       </c>
-      <c r="H41" t="s">
+      <c r="G41">
+        <v>3</v>
+      </c>
+      <c r="H41">
+        <v>40</v>
+      </c>
+      <c r="I41" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="42" spans="1:8">
+      <c r="K41">
+        <v>40</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5294,8 +5529,11 @@
       <c r="E42">
         <v>1.855</v>
       </c>
-    </row>
-    <row r="43" spans="1:8">
+      <c r="L42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5311,8 +5549,11 @@
       <c r="E43">
         <v>1.78</v>
       </c>
-    </row>
-    <row r="44" spans="1:8">
+      <c r="L43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5328,8 +5569,11 @@
       <c r="E44">
         <v>1.79</v>
       </c>
-    </row>
-    <row r="45" spans="1:8">
+      <c r="L44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5345,8 +5589,11 @@
       <c r="E45">
         <v>1.645</v>
       </c>
-    </row>
-    <row r="46" spans="1:8">
+      <c r="L45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5362,8 +5609,11 @@
       <c r="E46">
         <v>1.63</v>
       </c>
-    </row>
-    <row r="47" spans="1:8">
+      <c r="L46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5379,8 +5629,11 @@
       <c r="E47">
         <v>1.65</v>
       </c>
-    </row>
-    <row r="48" spans="1:8">
+      <c r="L47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5396,8 +5649,11 @@
       <c r="E48">
         <v>1.6579999999999999</v>
       </c>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="L48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5413,8 +5669,11 @@
       <c r="E49">
         <v>1.7150000000000001</v>
       </c>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="L49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5430,8 +5689,11 @@
       <c r="E50">
         <v>1.7450000000000001</v>
       </c>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="L50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5447,8 +5709,11 @@
       <c r="E51">
         <v>1.742</v>
       </c>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="L51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5463,6 +5728,9 @@
       </c>
       <c r="E52">
         <v>1.6950000000000001</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5474,13 +5742,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="8" max="8" width="10.77734375" customWidth="1"/>
-    <col min="9" max="9" width="28.77734375" customWidth="1"/>
-    <col min="10" max="10" width="33.109375" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="28.83203125" customWidth="1"/>
+    <col min="10" max="10" width="33.1640625" customWidth="1"/>
     <col min="11" max="11" width="36.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.44140625" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -5772,12 +6040,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="8" max="8" width="11.44140625" customWidth="1"/>
-    <col min="9" max="9" width="29.77734375" customWidth="1"/>
+    <col min="8" max="8" width="11.5" customWidth="1"/>
+    <col min="9" max="9" width="29.83203125" customWidth="1"/>
     <col min="10" max="10" width="34" customWidth="1"/>
-    <col min="11" max="11" width="36.77734375" customWidth="1"/>
+    <col min="11" max="11" width="36.83203125" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A0DC64-AF30-FD44-84BC-E5730575DD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF71292-6654-4E41-82F6-3A9644DFF615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="840" windowWidth="25280" windowHeight="15640" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="160" yWindow="840" windowWidth="25280" windowHeight="15640" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="114">
   <si>
     <t>Database No.</t>
   </si>
@@ -450,6 +450,9 @@
   </si>
   <si>
     <t>Participant</t>
+  </si>
+  <si>
+    <t>Error when processing in AddBiomechanics</t>
   </si>
 </sst>
 </file>
@@ -3912,6 +3915,12 @@
       <c r="I14" s="11" t="s">
         <v>96</v>
       </c>
+      <c r="K14">
+        <v>4</v>
+      </c>
+      <c r="L14" s="11">
+        <v>18</v>
+      </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15">
@@ -3937,6 +3946,9 @@
         <v>21</v>
       </c>
       <c r="I15" s="11"/>
+      <c r="L15">
+        <v>21</v>
+      </c>
     </row>
     <row r="16" spans="1:16">
       <c r="A16">
@@ -3962,8 +3974,11 @@
         <v>21</v>
       </c>
       <c r="I16" s="11"/>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="L16">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3989,8 +4004,14 @@
       <c r="I17" s="11" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="K17">
+        <v>2</v>
+      </c>
+      <c r="L17" s="11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4014,8 +4035,11 @@
         <v>20</v>
       </c>
       <c r="I18" s="11"/>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="L18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4041,8 +4065,14 @@
       <c r="I19" s="11" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="K19">
+        <v>21</v>
+      </c>
+      <c r="L19" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4066,8 +4096,11 @@
         <v>20</v>
       </c>
       <c r="I20" s="11"/>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="L20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4091,8 +4124,11 @@
         <v>20</v>
       </c>
       <c r="I21" s="11"/>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="L21" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4116,8 +4152,11 @@
         <v>21</v>
       </c>
       <c r="I22" s="11"/>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="L22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4141,8 +4180,11 @@
         <v>21</v>
       </c>
       <c r="I23" s="11"/>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="L23" s="11">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4165,9 +4207,17 @@
       <c r="H24" s="11">
         <v>20</v>
       </c>
-      <c r="I24" s="11"/>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="I24" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="K24">
+        <v>20</v>
+      </c>
+      <c r="L24" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4190,7 +4240,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:12">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4213,7 +4263,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:12">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4236,7 +4286,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:12">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4259,7 +4309,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:12">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4282,7 +4332,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:12">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4305,7 +4355,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:12">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4328,7 +4378,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:12">
       <c r="A32">
         <v>31</v>
       </c>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF71292-6654-4E41-82F6-3A9644DFF615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C35DB42-DFBE-1846-A038-A469151F962B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="840" windowWidth="25280" windowHeight="15640" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="160" yWindow="840" windowWidth="25280" windowHeight="15640" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -574,7 +574,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -595,6 +595,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1311,7 +1312,7 @@
     <col min="6" max="6" width="5.33203125" customWidth="1"/>
     <col min="7" max="7" width="11.83203125" customWidth="1"/>
     <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="9" max="9" width="27.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.83203125" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="9.33203125" customWidth="1"/>
@@ -1677,7 +1678,7 @@
       </c>
     </row>
     <row r="12" spans="1:16" ht="16">
-      <c r="A12">
+      <c r="A12" s="12">
         <v>11</v>
       </c>
       <c r="B12">
@@ -1698,12 +1699,19 @@
       <c r="H12">
         <v>13</v>
       </c>
+      <c r="I12">
+        <v>6</v>
+      </c>
+      <c r="L12" cm="1">
+        <f t="array" ref="L12:L21">P12:P21-I12:I21</f>
+        <v>16</v>
+      </c>
       <c r="P12">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="16">
-      <c r="A13">
+      <c r="A13" s="12">
         <v>12</v>
       </c>
       <c r="B13">
@@ -1724,12 +1732,18 @@
       <c r="H13">
         <v>14</v>
       </c>
+      <c r="I13">
+        <v>9</v>
+      </c>
+      <c r="L13">
+        <v>14</v>
+      </c>
       <c r="P13">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="16">
-      <c r="A14">
+      <c r="A14" s="12">
         <v>13</v>
       </c>
       <c r="B14">
@@ -1750,12 +1764,18 @@
       <c r="H14">
         <v>15</v>
       </c>
+      <c r="I14">
+        <v>7</v>
+      </c>
+      <c r="L14">
+        <v>18</v>
+      </c>
       <c r="P14">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="16">
-      <c r="A15">
+      <c r="A15" s="12">
         <v>14</v>
       </c>
       <c r="B15">
@@ -1776,12 +1796,18 @@
       <c r="H15">
         <v>12</v>
       </c>
+      <c r="I15">
+        <v>10</v>
+      </c>
+      <c r="L15">
+        <v>10</v>
+      </c>
       <c r="P15">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16">
-      <c r="A16">
+      <c r="A16" s="12">
         <v>15</v>
       </c>
       <c r="B16">
@@ -1802,12 +1828,18 @@
       <c r="H16">
         <v>15</v>
       </c>
+      <c r="I16">
+        <v>9</v>
+      </c>
+      <c r="L16">
+        <v>16</v>
+      </c>
       <c r="P16">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="16">
-      <c r="A17">
+      <c r="A17" s="12">
         <v>16</v>
       </c>
       <c r="B17">
@@ -1828,12 +1860,18 @@
       <c r="H17">
         <v>14</v>
       </c>
+      <c r="I17">
+        <v>12</v>
+      </c>
+      <c r="L17">
+        <v>10</v>
+      </c>
       <c r="P17">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="16">
-      <c r="A18">
+      <c r="A18" s="12">
         <v>17</v>
       </c>
       <c r="B18">
@@ -1854,12 +1892,18 @@
       <c r="H18">
         <v>15</v>
       </c>
+      <c r="I18">
+        <v>9</v>
+      </c>
+      <c r="L18">
+        <v>16</v>
+      </c>
       <c r="P18">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="16">
-      <c r="A19">
+      <c r="A19" s="12">
         <v>18</v>
       </c>
       <c r="B19">
@@ -1880,12 +1924,18 @@
       <c r="H19">
         <v>15</v>
       </c>
+      <c r="I19">
+        <v>11</v>
+      </c>
+      <c r="L19">
+        <v>12</v>
+      </c>
       <c r="P19">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="16">
-      <c r="A20">
+      <c r="A20" s="12">
         <v>19</v>
       </c>
       <c r="B20">
@@ -1906,12 +1956,18 @@
       <c r="H20">
         <v>15</v>
       </c>
+      <c r="I20">
+        <v>8</v>
+      </c>
+      <c r="L20">
+        <v>17</v>
+      </c>
       <c r="P20">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="16">
-      <c r="A21">
+      <c r="A21" s="12">
         <v>20</v>
       </c>
       <c r="B21">
@@ -1932,8 +1988,14 @@
       <c r="H21">
         <v>13</v>
       </c>
+      <c r="I21">
+        <v>10</v>
+      </c>
+      <c r="L21">
+        <v>13</v>
+      </c>
       <c r="P21">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="16">
@@ -2790,7 +2852,7 @@
         <v>74</v>
       </c>
       <c r="E2">
-        <v>175</v>
+        <v>1.75</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -2819,7 +2881,7 @@
         <v>72</v>
       </c>
       <c r="E3">
-        <v>172</v>
+        <v>1.72</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -2848,7 +2910,7 @@
         <v>80</v>
       </c>
       <c r="E4">
-        <v>178</v>
+        <v>1.78</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -2877,7 +2939,7 @@
         <v>60</v>
       </c>
       <c r="E5">
-        <v>170</v>
+        <v>1.7</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -2903,7 +2965,7 @@
         <v>71</v>
       </c>
       <c r="E6">
-        <v>171</v>
+        <v>1.71</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -2926,7 +2988,7 @@
         <v>65</v>
       </c>
       <c r="E7">
-        <v>168</v>
+        <v>1.68</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -2949,7 +3011,7 @@
         <v>72</v>
       </c>
       <c r="E8">
-        <v>176</v>
+        <v>1.76</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -2972,7 +3034,7 @@
         <v>85</v>
       </c>
       <c r="E9">
-        <v>181</v>
+        <v>1.81</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -2995,7 +3057,7 @@
         <v>76</v>
       </c>
       <c r="E10">
-        <v>183</v>
+        <v>1.83</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -3018,7 +3080,7 @@
         <v>80</v>
       </c>
       <c r="E11">
-        <v>182</v>
+        <v>1.82</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -3044,7 +3106,7 @@
         <v>75</v>
       </c>
       <c r="E12">
-        <v>175</v>
+        <v>1.75</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -3070,7 +3132,7 @@
         <v>80</v>
       </c>
       <c r="E13">
-        <v>177</v>
+        <v>1.77</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -3093,7 +3155,7 @@
         <v>58</v>
       </c>
       <c r="E14">
-        <v>170</v>
+        <v>1.7</v>
       </c>
       <c r="G14">
         <v>1</v>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C35DB42-DFBE-1846-A038-A469151F962B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="840" windowWidth="25280" windowHeight="15640" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -574,7 +574,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -595,7 +595,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -860,28 +859,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.1640625" customWidth="1"/>
-    <col min="4" max="4" width="33.83203125" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="4" max="4" width="33.77734375" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="23.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="14.33203125" customWidth="1"/>
     <col min="12" max="12" width="12.6640625" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="28.5" customWidth="1"/>
-    <col min="15" max="15" width="24.5" customWidth="1"/>
+    <col min="14" max="14" width="28.44140625" customWidth="1"/>
+    <col min="15" max="15" width="24.44140625" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="40.83203125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="29.83203125" customWidth="1"/>
+    <col min="17" max="17" width="40.77734375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="29.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" ht="17">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="15.6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -934,7 +933,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="80">
+    <row r="2" spans="1:18" ht="72">
       <c r="A2">
         <v>1</v>
       </c>
@@ -987,7 +986,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="48">
+    <row r="3" spans="1:18" ht="43.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1031,7 +1030,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="48">
+    <row r="4" spans="1:18" ht="57.6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1102,7 +1101,7 @@
       <c r="I8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="48">
+    <row r="9" spans="1:18" ht="57.6">
       <c r="B9" s="1" t="s">
         <v>37</v>
       </c>
@@ -1131,7 +1130,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="48">
+    <row r="10" spans="1:18" ht="43.2">
       <c r="B10" s="1" t="s">
         <v>42</v>
       </c>
@@ -1198,7 +1197,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="51">
+    <row r="12" spans="1:18" ht="46.8">
       <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
@@ -1239,7 +1238,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="48">
+    <row r="13" spans="1:18" ht="43.2">
       <c r="B13" s="1" t="s">
         <v>63</v>
       </c>
@@ -1302,18 +1301,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" customWidth="1"/>
     <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="9" max="9" width="27.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.77734375" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="9.33203125" customWidth="1"/>
     <col min="16" max="16" width="16.6640625" customWidth="1"/>
@@ -1357,7 +1356,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="16">
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1389,7 +1388,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="16">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1421,7 +1420,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="16">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1453,7 +1452,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="16">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1485,7 +1484,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="16">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1517,7 +1516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="16">
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1549,7 +1548,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="16">
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1581,7 +1580,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="16">
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1613,7 +1612,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="16">
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1645,7 +1644,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="16">
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1677,8 +1676,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="16">
-      <c r="A12" s="12">
+    <row r="12" spans="1:16">
+      <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
@@ -1710,8 +1709,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="16">
-      <c r="A13" s="12">
+    <row r="13" spans="1:16">
+      <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
@@ -1742,8 +1741,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="16">
-      <c r="A14" s="12">
+    <row r="14" spans="1:16">
+      <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
@@ -1774,8 +1773,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="16">
-      <c r="A15" s="12">
+    <row r="15" spans="1:16">
+      <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
@@ -1806,8 +1805,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="16">
-      <c r="A16" s="12">
+    <row r="16" spans="1:16">
+      <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
@@ -1838,8 +1837,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="16">
-      <c r="A17" s="12">
+    <row r="17" spans="1:16">
+      <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
@@ -1870,8 +1869,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="16">
-      <c r="A18" s="12">
+    <row r="18" spans="1:16">
+      <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
@@ -1902,8 +1901,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="16">
-      <c r="A19" s="12">
+    <row r="19" spans="1:16">
+      <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
@@ -1934,8 +1933,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="16">
-      <c r="A20" s="12">
+    <row r="20" spans="1:16">
+      <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
@@ -1966,8 +1965,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="16">
-      <c r="A21" s="12">
+    <row r="21" spans="1:16">
+      <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
@@ -1998,7 +1997,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="16">
+    <row r="22" spans="1:16">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2024,7 +2023,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="16">
+    <row r="23" spans="1:16">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2050,7 +2049,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="16">
+    <row r="24" spans="1:16">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2076,7 +2075,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="16">
+    <row r="25" spans="1:16">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2102,7 +2101,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="16">
+    <row r="26" spans="1:16">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2128,7 +2127,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="16">
+    <row r="27" spans="1:16">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2154,7 +2153,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="16">
+    <row r="28" spans="1:16">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2180,7 +2179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="16">
+    <row r="29" spans="1:16">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2206,7 +2205,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="16">
+    <row r="30" spans="1:16">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2232,7 +2231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="16">
+    <row r="31" spans="1:16">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2258,7 +2257,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="16">
+    <row r="32" spans="1:16">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2284,7 +2283,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="16">
+    <row r="33" spans="1:16">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2310,7 +2309,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="16">
+    <row r="34" spans="1:16">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2336,7 +2335,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="16">
+    <row r="35" spans="1:16">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2362,7 +2361,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="16">
+    <row r="36" spans="1:16">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2388,7 +2387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="16">
+    <row r="37" spans="1:16">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2414,7 +2413,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="16">
+    <row r="38" spans="1:16">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2440,7 +2439,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="16">
+    <row r="39" spans="1:16">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2466,7 +2465,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="16">
+    <row r="40" spans="1:16">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2492,7 +2491,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="16">
+    <row r="41" spans="1:16">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2518,7 +2517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="16">
+    <row r="42" spans="1:16">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2544,7 +2543,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="16">
+    <row r="43" spans="1:16">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2570,7 +2569,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="16">
+    <row r="44" spans="1:16">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2596,7 +2595,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="16">
+    <row r="45" spans="1:16">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2622,7 +2621,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="16">
+    <row r="46" spans="1:16">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2648,7 +2647,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="16">
+    <row r="47" spans="1:16">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2674,7 +2673,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="16">
+    <row r="48" spans="1:16">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2700,7 +2699,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="16">
+    <row r="49" spans="1:16">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2726,7 +2725,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="16">
+    <row r="50" spans="1:16">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2752,7 +2751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="16">
+    <row r="51" spans="1:16">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2793,14 +2792,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="8" max="8" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" customWidth="1"/>
     <col min="9" max="9" width="30.6640625" customWidth="1"/>
-    <col min="10" max="10" width="33.1640625" customWidth="1"/>
+    <col min="10" max="10" width="33.109375" customWidth="1"/>
     <col min="11" max="11" width="36.6640625" customWidth="1"/>
-    <col min="12" max="12" width="15.5" customWidth="1"/>
-    <col min="14" max="14" width="14.1640625" customWidth="1"/>
+    <col min="12" max="12" width="15.44140625" customWidth="1"/>
+    <col min="14" max="14" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -3179,9 +3178,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="7" max="7" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -3619,13 +3618,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D22FEE7-983F-4E6D-B518-6357D6EFC8AC}">
   <dimension ref="A1:P58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="6" max="6" width="0.83203125" customWidth="1"/>
+    <col min="6" max="6" width="0.77734375" customWidth="1"/>
     <col min="7" max="7" width="6.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.1640625" customWidth="1"/>
-    <col min="9" max="9" width="30.83203125" customWidth="1"/>
-    <col min="10" max="10" width="48.5" customWidth="1"/>
+    <col min="8" max="8" width="7.109375" customWidth="1"/>
+    <col min="9" max="9" width="30.77734375" customWidth="1"/>
+    <col min="10" max="10" width="48.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -4655,15 +4654,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125"/>
+    <col min="1" max="1" width="9.77734375" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375"/>
     <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" customWidth="1"/>
     <col min="8" max="8" width="21.33203125" customWidth="1"/>
     <col min="9" max="9" width="35.33203125" customWidth="1"/>
-    <col min="10" max="10" width="50.83203125" customWidth="1"/>
+    <col min="10" max="10" width="50.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -5854,13 +5853,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="28.83203125" customWidth="1"/>
-    <col min="10" max="10" width="33.1640625" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" customWidth="1"/>
+    <col min="9" max="9" width="28.77734375" customWidth="1"/>
+    <col min="10" max="10" width="33.109375" customWidth="1"/>
     <col min="11" max="11" width="36.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -6152,12 +6151,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="8" max="8" width="11.5" customWidth="1"/>
-    <col min="9" max="9" width="29.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="9" width="29.77734375" customWidth="1"/>
     <col min="10" max="10" width="34" customWidth="1"/>
-    <col min="11" max="11" width="36.83203125" customWidth="1"/>
+    <col min="11" max="11" width="36.77734375" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C35DB42-DFBE-1846-A038-A469151F962B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9980B15C-3823-4044-B77A-08BFB5975DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3765,6 +3765,9 @@
       <c r="H5">
         <v>20</v>
       </c>
+      <c r="L5">
+        <v>20</v>
+      </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6">
@@ -3788,6 +3791,9 @@
       <c r="H6">
         <v>21</v>
       </c>
+      <c r="L6">
+        <v>20</v>
+      </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7">
@@ -3811,6 +3817,9 @@
       <c r="H7">
         <v>21</v>
       </c>
+      <c r="L7">
+        <v>21</v>
+      </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8">
@@ -3834,6 +3843,9 @@
       <c r="H8">
         <v>21</v>
       </c>
+      <c r="L8">
+        <v>20</v>
+      </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9">
@@ -3857,6 +3869,9 @@
       <c r="H9">
         <v>21</v>
       </c>
+      <c r="L9">
+        <v>21</v>
+      </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10">
@@ -3880,6 +3895,9 @@
       <c r="H10">
         <v>21</v>
       </c>
+      <c r="L10">
+        <v>21</v>
+      </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11">
@@ -3903,6 +3921,9 @@
       <c r="H11">
         <v>21</v>
       </c>
+      <c r="L11">
+        <v>21</v>
+      </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12">
@@ -3926,6 +3947,9 @@
       <c r="H12">
         <v>20</v>
       </c>
+      <c r="L12">
+        <v>19</v>
+      </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13">
@@ -3948,6 +3972,9 @@
       </c>
       <c r="H13">
         <v>22</v>
+      </c>
+      <c r="L13">
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:16">

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0051rra\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C35DB42-DFBE-1846-A038-A469151F962B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE6372F-ACDE-4C6B-A760-E706BC3DFEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="840" windowWidth="25280" windowHeight="15640" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="DB Grouvel" sheetId="6" r:id="rId7"/>
     <sheet name="DB Han" sheetId="7" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="114">
   <si>
     <t>Database No.</t>
   </si>
@@ -574,7 +574,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -595,7 +595,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -860,28 +859,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.1640625" customWidth="1"/>
-    <col min="4" max="4" width="33.83203125" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="33.85546875" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
-    <col min="6" max="6" width="23.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" customWidth="1"/>
+    <col min="6" max="6" width="23.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="28.5" customWidth="1"/>
-    <col min="15" max="15" width="24.5" customWidth="1"/>
+    <col min="14" max="14" width="28.42578125" customWidth="1"/>
+    <col min="15" max="15" width="24.42578125" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="40.83203125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="29.83203125" customWidth="1"/>
+    <col min="17" max="17" width="40.85546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="29.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" ht="17">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="15.75">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -934,7 +933,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="80">
+    <row r="2" spans="1:18" ht="75">
       <c r="A2">
         <v>1</v>
       </c>
@@ -987,7 +986,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="48">
+    <row r="3" spans="1:18" ht="45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1031,7 +1030,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="48">
+    <row r="4" spans="1:18" ht="60">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1102,7 +1101,7 @@
       <c r="I8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="48">
+    <row r="9" spans="1:18" ht="60">
       <c r="B9" s="1" t="s">
         <v>37</v>
       </c>
@@ -1131,7 +1130,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="48">
+    <row r="10" spans="1:18" ht="45">
       <c r="B10" s="1" t="s">
         <v>42</v>
       </c>
@@ -1198,7 +1197,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="51">
+    <row r="12" spans="1:18" ht="60">
       <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
@@ -1239,7 +1238,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="48">
+    <row r="13" spans="1:18" ht="45">
       <c r="B13" s="1" t="s">
         <v>63</v>
       </c>
@@ -1302,21 +1301,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.5" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="9" max="9" width="27.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="5.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" customWidth="1"/>
+    <col min="9" max="9" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="9.33203125" customWidth="1"/>
-    <col min="16" max="16" width="16.6640625" customWidth="1"/>
+    <col min="12" max="12" width="9.28515625" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1357,7 +1356,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="16">
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1389,7 +1388,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="16">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1421,7 +1420,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="16">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1453,7 +1452,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="16">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1485,7 +1484,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="16">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1517,7 +1516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="16">
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1549,7 +1548,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="16">
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1581,7 +1580,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="16">
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1613,7 +1612,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="16">
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1645,7 +1644,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="16">
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1677,8 +1676,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="16">
-      <c r="A12" s="12">
+    <row r="12" spans="1:16">
+      <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
@@ -1710,8 +1709,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="16">
-      <c r="A13" s="12">
+    <row r="13" spans="1:16">
+      <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
@@ -1742,8 +1741,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="16">
-      <c r="A14" s="12">
+    <row r="14" spans="1:16">
+      <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
@@ -1774,8 +1773,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="16">
-      <c r="A15" s="12">
+    <row r="15" spans="1:16">
+      <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
@@ -1806,8 +1805,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="16">
-      <c r="A16" s="12">
+    <row r="16" spans="1:16">
+      <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
@@ -1838,8 +1837,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="16">
-      <c r="A17" s="12">
+    <row r="17" spans="1:16">
+      <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
@@ -1870,8 +1869,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="16">
-      <c r="A18" s="12">
+    <row r="18" spans="1:16">
+      <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
@@ -1902,8 +1901,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="16">
-      <c r="A19" s="12">
+    <row r="19" spans="1:16">
+      <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
@@ -1934,8 +1933,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="16">
-      <c r="A20" s="12">
+    <row r="20" spans="1:16">
+      <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
@@ -1966,8 +1965,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="16">
-      <c r="A21" s="12">
+    <row r="21" spans="1:16">
+      <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
@@ -1998,7 +1997,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="16">
+    <row r="22" spans="1:16">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2024,7 +2023,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="16">
+    <row r="23" spans="1:16">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2050,7 +2049,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="16">
+    <row r="24" spans="1:16">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2076,7 +2075,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="16">
+    <row r="25" spans="1:16">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2102,7 +2101,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="16">
+    <row r="26" spans="1:16">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2128,7 +2127,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="16">
+    <row r="27" spans="1:16">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2154,7 +2153,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="16">
+    <row r="28" spans="1:16">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2180,7 +2179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="16">
+    <row r="29" spans="1:16">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2206,7 +2205,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="16">
+    <row r="30" spans="1:16">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2232,7 +2231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="16">
+    <row r="31" spans="1:16">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2258,7 +2257,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="16">
+    <row r="32" spans="1:16">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2284,7 +2283,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="16">
+    <row r="33" spans="1:16">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2310,7 +2309,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="16">
+    <row r="34" spans="1:16">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2336,7 +2335,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="16">
+    <row r="35" spans="1:16">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2362,7 +2361,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="16">
+    <row r="36" spans="1:16">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2388,7 +2387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="16">
+    <row r="37" spans="1:16">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2414,7 +2413,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="16">
+    <row r="38" spans="1:16">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2440,7 +2439,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="16">
+    <row r="39" spans="1:16">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2466,7 +2465,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="16">
+    <row r="40" spans="1:16">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2492,7 +2491,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="16">
+    <row r="41" spans="1:16">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2518,7 +2517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="16">
+    <row r="42" spans="1:16">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2544,7 +2543,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="16">
+    <row r="43" spans="1:16">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2570,7 +2569,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="16">
+    <row r="44" spans="1:16">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2596,7 +2595,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="16">
+    <row r="45" spans="1:16">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2622,7 +2621,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="16">
+    <row r="46" spans="1:16">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2648,7 +2647,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="16">
+    <row r="47" spans="1:16">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2674,7 +2673,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="16">
+    <row r="48" spans="1:16">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2700,7 +2699,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="16">
+    <row r="49" spans="1:16">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2726,7 +2725,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="16">
+    <row r="50" spans="1:16">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2752,7 +2751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="16">
+    <row r="51" spans="1:16">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2793,14 +2792,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="8" max="8" width="10.5" customWidth="1"/>
-    <col min="9" max="9" width="30.6640625" customWidth="1"/>
-    <col min="10" max="10" width="33.1640625" customWidth="1"/>
-    <col min="11" max="11" width="36.6640625" customWidth="1"/>
-    <col min="12" max="12" width="15.5" customWidth="1"/>
-    <col min="14" max="14" width="14.1640625" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" customWidth="1"/>
+    <col min="9" max="9" width="30.7109375" customWidth="1"/>
+    <col min="10" max="10" width="33.140625" customWidth="1"/>
+    <col min="11" max="11" width="36.7109375" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -3179,9 +3178,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="7" max="7" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -3619,13 +3618,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D22FEE7-983F-4E6D-B518-6357D6EFC8AC}">
   <dimension ref="A1:P58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="6" max="6" width="0.83203125" customWidth="1"/>
-    <col min="7" max="7" width="6.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.1640625" customWidth="1"/>
-    <col min="9" max="9" width="30.83203125" customWidth="1"/>
-    <col min="10" max="10" width="48.5" customWidth="1"/>
+    <col min="6" max="6" width="0.85546875" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="30.85546875" customWidth="1"/>
+    <col min="10" max="10" width="48.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -4536,55 +4535,187 @@
       <c r="A36">
         <v>35</v>
       </c>
+      <c r="B36" s="11">
+        <v>24</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" s="11">
+        <v>94.2</v>
+      </c>
+      <c r="E36" s="11">
+        <v>1.91</v>
+      </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
         <v>36</v>
       </c>
+      <c r="B37" s="11">
+        <v>23</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D37" s="11">
+        <v>69.5</v>
+      </c>
+      <c r="E37" s="11">
+        <v>1.88</v>
+      </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
         <v>37</v>
       </c>
+      <c r="B38" s="11">
+        <v>26</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D38" s="11">
+        <v>72</v>
+      </c>
+      <c r="E38" s="11">
+        <v>1.84</v>
+      </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
         <v>38</v>
       </c>
+      <c r="B39" s="11">
+        <v>20</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D39" s="11">
+        <v>52.3</v>
+      </c>
+      <c r="E39" s="11">
+        <v>1.58</v>
+      </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
         <v>39</v>
       </c>
+      <c r="B40" s="11">
+        <v>25</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" s="11">
+        <v>60.4</v>
+      </c>
+      <c r="E40" s="11">
+        <v>1.68</v>
+      </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
         <v>40</v>
       </c>
+      <c r="B41" s="11">
+        <v>23</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D41" s="11">
+        <v>55</v>
+      </c>
+      <c r="E41" s="11">
+        <v>1.64</v>
+      </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
         <v>41</v>
       </c>
+      <c r="B42" s="11">
+        <v>21</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" s="11">
+        <v>69.7</v>
+      </c>
+      <c r="E42" s="11">
+        <v>1.69</v>
+      </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
         <v>42</v>
       </c>
+      <c r="B43" s="11">
+        <v>26</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="11">
+        <v>59.3</v>
+      </c>
+      <c r="E43" s="11">
+        <v>1.69</v>
+      </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
         <v>43</v>
       </c>
+      <c r="B44" s="11">
+        <v>25</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" s="11">
+        <v>54.5</v>
+      </c>
+      <c r="E44" s="11">
+        <v>1.67</v>
+      </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
         <v>44</v>
       </c>
+      <c r="B45" s="11">
+        <v>23</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" s="11">
+        <v>57.4</v>
+      </c>
+      <c r="E45" s="11">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46">
         <v>45</v>
+      </c>
+      <c r="B46" s="11">
+        <v>27</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46" s="11">
+        <v>47.3</v>
+      </c>
+      <c r="E46" s="11">
+        <v>1.6</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -4655,15 +4786,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.5" customWidth="1"/>
-    <col min="8" max="8" width="21.33203125" customWidth="1"/>
-    <col min="9" max="9" width="35.33203125" customWidth="1"/>
-    <col min="10" max="10" width="50.83203125" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="21.28515625" customWidth="1"/>
+    <col min="9" max="9" width="35.28515625" customWidth="1"/>
+    <col min="10" max="10" width="50.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -5854,13 +5985,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="28.83203125" customWidth="1"/>
-    <col min="10" max="10" width="33.1640625" customWidth="1"/>
-    <col min="11" max="11" width="36.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" customWidth="1"/>
+    <col min="10" max="10" width="33.140625" customWidth="1"/>
+    <col min="11" max="11" width="36.7109375" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -6152,12 +6283,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="8" max="8" width="11.5" customWidth="1"/>
-    <col min="9" max="9" width="29.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="9" max="9" width="29.85546875" customWidth="1"/>
     <col min="10" max="10" width="34" customWidth="1"/>
-    <col min="11" max="11" width="36.83203125" customWidth="1"/>
+    <col min="11" max="11" width="36.85546875" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6361,4 +6492,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{f867a8da-a586-4d74-a123-5474ccdeebfd}" enabled="1" method="Standard" siteId="{698c6ffb-74e3-4a84-be68-f22d8d3201a3}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{853ACEB3-83EA-42DF-9D3A-405FB1CE049E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21AEE1D-4466-4A9B-AB40-8E8220E4BAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
-    <sheet name="DB1" sheetId="2" r:id="rId2"/>
-    <sheet name="DB2" sheetId="3" r:id="rId3"/>
-    <sheet name="DB3" sheetId="4" r:id="rId4"/>
-    <sheet name="DB4" sheetId="5" r:id="rId5"/>
-    <sheet name="DB5" sheetId="6" r:id="rId6"/>
-    <sheet name="DB Grouvel" sheetId="7" r:id="rId7"/>
-    <sheet name="DB Han" sheetId="8" r:id="rId8"/>
+    <sheet name="OtherDBs" sheetId="9" r:id="rId2"/>
+    <sheet name="DB1" sheetId="2" r:id="rId3"/>
+    <sheet name="DB2" sheetId="3" r:id="rId4"/>
+    <sheet name="DB3" sheetId="4" r:id="rId5"/>
+    <sheet name="DB4" sheetId="5" r:id="rId6"/>
+    <sheet name="DB5" sheetId="6" r:id="rId7"/>
+    <sheet name="DB Grouvel" sheetId="7" r:id="rId8"/>
+    <sheet name="DB Han" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="137">
   <si>
     <t>Database No.</t>
   </si>
@@ -75,12 +76,6 @@
     <t>Age range</t>
   </si>
   <si>
-    <t>Height range</t>
-  </si>
-  <si>
-    <t>Weight range</t>
-  </si>
-  <si>
     <t>Geographical Region</t>
   </si>
   <si>
@@ -93,9 +88,6 @@
     <t>No. Force Plates</t>
   </si>
   <si>
-    <t>File Download Link</t>
-  </si>
-  <si>
     <t>Schreiber &amp; Moissenet</t>
   </si>
   <si>
@@ -108,42 +100,6 @@
     <t>0–0.4 m.s−1 (C1), 0.4–0.8 m.s−1 (C2), 0.8–1.2 m.s−1 (C3). Self-selected spontaneous (C4) and fast (C5)</t>
   </si>
   <si>
-    <t>19-67</t>
-  </si>
-  <si>
-    <t>1.74 ± 0.09 m</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">71.0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="EuclidSymbol"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">± </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="MinionPro"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12.3 kg </t>
-    </r>
-  </si>
-  <si>
     <t>Luxembourg</t>
   </si>
   <si>
@@ -165,15 +121,6 @@
     <t>Preferred &amp; step widths</t>
   </si>
   <si>
-    <t>20–25</t>
-  </si>
-  <si>
-    <t>165-185 cm</t>
-  </si>
-  <si>
-    <t>55-85 kg</t>
-  </si>
-  <si>
     <t xml:space="preserve">38 cutaneous reflective markers </t>
   </si>
   <si>
@@ -187,15 +134,6 @@
   </si>
   <si>
     <t>self-selected speeds</t>
-  </si>
-  <si>
-    <t>21–56</t>
-  </si>
-  <si>
-    <t>170.3 ± 6.6 cm</t>
-  </si>
-  <si>
-    <t>73.9 ± 15.7 kg</t>
   </si>
   <si>
     <t>55 spherical markers</t>
@@ -435,12 +373,134 @@
   <si>
     <t>PROCESSING</t>
   </si>
+  <si>
+    <t>Horst</t>
+  </si>
+  <si>
+    <t>Paper Link</t>
+  </si>
+  <si>
+    <t>Download Link</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41597-019-0124-4</t>
+  </si>
+  <si>
+    <t>A public dataset of overground walking kinetics and full-body kinematics in healthy adult individuals</t>
+  </si>
+  <si>
+    <t>20 trials</t>
+  </si>
+  <si>
+    <t>62 retro reflective markers</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41598-019-38748-8</t>
+  </si>
+  <si>
+    <t>https://data.mendeley.com/datasets/svx74xcrjr/3</t>
+  </si>
+  <si>
+    <t>Kuopio gait dataset: motion capture, inertial measurement and video-based sagittal-plane keypoint data from walking trials</t>
+  </si>
+  <si>
+    <t>Lavikainen</t>
+  </si>
+  <si>
+    <t>https://zenodo.org/records/10559504</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S2352340924008059#refdata001</t>
+  </si>
+  <si>
+    <t>77 ± 14.2</t>
+  </si>
+  <si>
+    <t>1.74 ± .07</t>
+  </si>
+  <si>
+    <t>Height range (m)</t>
+  </si>
+  <si>
+    <t>Weight range (kg)</t>
+  </si>
+  <si>
+    <t>1.74 ± 0.09</t>
+  </si>
+  <si>
+    <t>1.70 ± 0.06</t>
+  </si>
+  <si>
+    <t>1.74 ± 0.10</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">71.0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="EuclidSymbol"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">± </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="MinionPro"/>
+        <charset val="1"/>
+      </rPr>
+      <t>12.3</t>
+    </r>
+  </si>
+  <si>
+    <t>73.9 ± 15.7</t>
+  </si>
+  <si>
+    <t>67.9 ±  11.3</t>
+  </si>
+  <si>
+    <t>23.1 ±  2.7</t>
+  </si>
+  <si>
+    <t>21 – 56</t>
+  </si>
+  <si>
+    <t>29.7 ± 7.9</t>
+  </si>
+  <si>
+    <t>20 – 25</t>
+  </si>
+  <si>
+    <t>19 – 67</t>
+  </si>
+  <si>
+    <t>1.65 – 1.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55 – 85 </t>
+  </si>
+  <si>
+    <t>slow, comfortable, fast</t>
+  </si>
+  <si>
+    <t>60 trials</t>
+  </si>
+  <si>
+    <t>Overground, barefoot</t>
+  </si>
+  <si>
+    <t>42 reflective markers</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -519,19 +579,19 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -548,7 +608,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -562,12 +622,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -831,29 +896,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.88671875" customWidth="1"/>
     <col min="2" max="2" width="12.44140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.109375" customWidth="1"/>
-    <col min="4" max="4" width="33.88671875" customWidth="1"/>
+    <col min="4" max="4" width="29" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="23.6640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.44140625" customWidth="1"/>
     <col min="9" max="9" width="9.88671875" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" customWidth="1"/>
+    <col min="11" max="11" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
     <col min="14" max="14" width="28.44140625" customWidth="1"/>
     <col min="15" max="15" width="24.44140625" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="40.88671875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="29.88671875" customWidth="1"/>
+    <col min="17" max="17" width="34.88671875" customWidth="1"/>
+    <col min="18" max="18" width="40.88671875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="29.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" ht="15.6">
+    <row r="1" spans="1:19" s="2" customFormat="1" ht="15.6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -885,45 +951,48 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="72">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="72">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C2">
         <v>2019</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G2">
         <v>50</v>
@@ -935,48 +1004,51 @@
         <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="M2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="P2">
         <v>2</v>
       </c>
-      <c r="Q2" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="43.2">
+      <c r="Q2" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="43.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C3">
         <v>2025</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G3">
         <v>13</v>
@@ -988,39 +1060,42 @@
         <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="L3" t="s">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="57.6">
+        <v>25</v>
+      </c>
+      <c r="P3">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="57.6">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>2024</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G4">
         <v>20</v>
@@ -1032,239 +1107,162 @@
         <v>9</v>
       </c>
       <c r="J4" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="K4" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>124</v>
       </c>
       <c r="O4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="P4">
         <v>1</v>
       </c>
-      <c r="Q4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="R4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="5">
+      <c r="Q4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="57.6">
+      <c r="A5" s="10">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="B5" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5">
+        <v>2019</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5">
+        <v>57</v>
+      </c>
+      <c r="H5">
+        <v>29</v>
+      </c>
+      <c r="I5">
+        <v>28</v>
+      </c>
+      <c r="J5" t="s">
+        <v>126</v>
+      </c>
+      <c r="K5" t="s">
+        <v>122</v>
+      </c>
+      <c r="L5" t="s">
+        <v>125</v>
+      </c>
+      <c r="N5" t="s">
+        <v>108</v>
+      </c>
+      <c r="O5" t="s">
+        <v>109</v>
+      </c>
+      <c r="P5">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="57.6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6">
+        <v>2024</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G6">
+        <v>51</v>
+      </c>
+      <c r="H6">
+        <v>18</v>
+      </c>
+      <c r="I6">
+        <v>33</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="K6" t="s">
+        <v>117</v>
+      </c>
+      <c r="L6" t="s">
+        <v>116</v>
+      </c>
+      <c r="N6" t="s">
+        <v>134</v>
+      </c>
+      <c r="O6" t="s">
+        <v>136</v>
+      </c>
+      <c r="P6" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="R6" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="7" spans="1:19">
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="R7" s="1"/>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="S7" s="1"/>
+    </row>
+    <row r="8" spans="1:19">
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="R8" s="1"/>
-    </row>
-    <row r="9" spans="1:18" ht="57.6">
-      <c r="B9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9">
-        <v>2025</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="1">
-        <v>30</v>
-      </c>
-      <c r="H9" s="1">
-        <v>10</v>
-      </c>
-      <c r="I9" s="1">
-        <v>20</v>
-      </c>
-      <c r="R9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="43.2">
-      <c r="B10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="1">
-        <v>13</v>
-      </c>
-      <c r="H10" s="1">
-        <v>5</v>
-      </c>
-      <c r="I10" s="1">
-        <v>8</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="82.5" customHeight="1">
-      <c r="B11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11">
-        <v>2024</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11" s="1">
-        <v>30</v>
-      </c>
-      <c r="H11" s="1">
-        <v>14</v>
-      </c>
-      <c r="I11" s="1">
-        <v>16</v>
-      </c>
-      <c r="J11" t="s">
-        <v>59</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="46.8">
-      <c r="B12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12">
-        <v>2023</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>4</v>
-      </c>
-      <c r="I12" s="1">
-        <v>6</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="R12" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="43.2">
-      <c r="B13" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13">
-        <v>2023</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" s="1">
-        <v>7</v>
-      </c>
-      <c r="H13" s="1">
-        <v>4</v>
-      </c>
-      <c r="I13" s="1">
-        <v>3</v>
-      </c>
-      <c r="J13" t="s">
-        <v>73</v>
-      </c>
-      <c r="K13" t="s">
-        <v>74</v>
-      </c>
-      <c r="L13" t="s">
-        <v>75</v>
-      </c>
-      <c r="O13" s="1">
-        <v>96</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="11" spans="1:19" ht="82.5" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="Q2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="R3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="R9" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="R10" r:id="rId4" location="Bib1" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="R11" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="R12" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="Q13" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="R13" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="R2" r:id="rId1" xr:uid="{F307A5B7-186F-4624-80A3-54E8DFBFB6D0}"/>
+    <hyperlink ref="Q2" r:id="rId2" xr:uid="{ECB5A3CA-71AA-429E-AE8B-FC866B4DBE03}"/>
+    <hyperlink ref="Q3" r:id="rId3" xr:uid="{EBD71AC2-C4DD-46AC-B00B-166427480014}"/>
+    <hyperlink ref="R4" r:id="rId4" xr:uid="{75C91AE3-1F22-40E3-BBBD-E8CDBD56D498}"/>
+    <hyperlink ref="Q4" r:id="rId5" xr:uid="{5F3508AA-F1AA-470F-914C-42B32A5FD884}"/>
+    <hyperlink ref="Q5" r:id="rId6" xr:uid="{62A625B7-C3A0-4B20-90D7-ED2F76F4088A}"/>
+    <hyperlink ref="R5" r:id="rId7" xr:uid="{4BCB748A-1E5D-4370-8850-6D84A19A182D}"/>
+    <hyperlink ref="Q6" r:id="rId8" location="refdata001" xr:uid="{0908479C-E69E-42CF-9C79-7C4C12278427}"/>
+    <hyperlink ref="R6" r:id="rId9" xr:uid="{F31C4ED8-A6AD-4FE3-979E-D83CF4B6DFF1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1272,6 +1270,232 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A02F7DDF-461B-4D0B-BBA8-A327F5C71FB4}">
+  <dimension ref="B2:R9"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="17.88671875" customWidth="1"/>
+    <col min="4" max="4" width="26.33203125" customWidth="1"/>
+    <col min="5" max="5" width="21.88671875" customWidth="1"/>
+    <col min="6" max="6" width="26.77734375" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="18" max="18" width="35.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:18" ht="72">
+      <c r="B2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2">
+        <v>2025</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="1">
+        <v>30</v>
+      </c>
+      <c r="H2" s="1">
+        <v>10</v>
+      </c>
+      <c r="I2" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="1"/>
+      <c r="R2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="2:18" ht="57.6">
+      <c r="B3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="1">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1">
+        <v>5</v>
+      </c>
+      <c r="I3" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" ht="72">
+      <c r="B4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4">
+        <v>2024</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="1">
+        <v>30</v>
+      </c>
+      <c r="H4" s="1">
+        <v>14</v>
+      </c>
+      <c r="I4" s="1">
+        <v>16</v>
+      </c>
+      <c r="J4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" ht="61.2">
+      <c r="B5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5">
+        <v>2023</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="1">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1">
+        <v>4</v>
+      </c>
+      <c r="I5" s="1">
+        <v>6</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" ht="57.6">
+      <c r="B6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6">
+        <v>2023</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="1">
+        <v>7</v>
+      </c>
+      <c r="H6" s="1">
+        <v>4</v>
+      </c>
+      <c r="I6" s="1">
+        <v>3</v>
+      </c>
+      <c r="J6" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" t="s">
+        <v>62</v>
+      </c>
+      <c r="L6" t="s">
+        <v>63</v>
+      </c>
+      <c r="O6" s="1">
+        <v>96</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18">
+      <c r="B7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="Q7" s="1"/>
+    </row>
+    <row r="8" spans="2:18">
+      <c r="B8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="Q8" s="1"/>
+    </row>
+    <row r="9" spans="2:18">
+      <c r="B9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="Q9" s="1"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="R6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="Q6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="R5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="R4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="R3" r:id="rId5" location="Bib1" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="R2" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P52"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
@@ -1293,40 +1517,40 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E1" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="G1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="H1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="I1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="J1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="K1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="L1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="P1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -1336,8 +1560,8 @@
       <c r="B2">
         <v>31</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>90</v>
+      <c r="C2" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D2">
         <v>67</v>
@@ -1352,7 +1576,7 @@
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="L2">
         <v>8</v>
@@ -1368,8 +1592,8 @@
       <c r="B3">
         <v>48</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>92</v>
+      <c r="C3" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D3">
         <v>65.400000000000006</v>
@@ -1384,7 +1608,7 @@
         <v>11</v>
       </c>
       <c r="I3" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -1400,8 +1624,8 @@
       <c r="B4">
         <v>28</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>92</v>
+      <c r="C4" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D4">
         <v>50</v>
@@ -1416,7 +1640,7 @@
         <v>13</v>
       </c>
       <c r="I4" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -1432,8 +1656,8 @@
       <c r="B5">
         <v>23</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>90</v>
+      <c r="C5" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D5">
         <v>72.5</v>
@@ -1448,7 +1672,7 @@
         <v>14</v>
       </c>
       <c r="I5" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -1464,8 +1688,8 @@
       <c r="B6">
         <v>25</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>90</v>
+      <c r="C6" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D6">
         <v>73.5</v>
@@ -1480,7 +1704,7 @@
         <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="L6">
         <v>6</v>
@@ -1496,8 +1720,8 @@
       <c r="B7">
         <v>23</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>90</v>
+      <c r="C7" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D7">
         <v>73</v>
@@ -1512,7 +1736,7 @@
         <v>13</v>
       </c>
       <c r="I7" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="L7">
         <v>8</v>
@@ -1528,8 +1752,8 @@
       <c r="B8">
         <v>44</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>92</v>
+      <c r="C8" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D8">
         <v>65</v>
@@ -1544,7 +1768,7 @@
         <v>14</v>
       </c>
       <c r="I8" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="L8">
         <v>4</v>
@@ -1560,8 +1784,8 @@
       <c r="B9">
         <v>30</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>92</v>
+      <c r="C9" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D9">
         <v>57.1</v>
@@ -1576,7 +1800,7 @@
         <v>15</v>
       </c>
       <c r="I9" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="L9">
         <v>9</v>
@@ -1592,8 +1816,8 @@
       <c r="B10">
         <v>57</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>90</v>
+      <c r="C10" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D10">
         <v>86</v>
@@ -1608,7 +1832,7 @@
         <v>15</v>
       </c>
       <c r="I10" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="L10">
         <v>9</v>
@@ -1624,8 +1848,8 @@
       <c r="B11">
         <v>59</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>90</v>
+      <c r="C11" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D11">
         <v>63.4</v>
@@ -1640,7 +1864,7 @@
         <v>13</v>
       </c>
       <c r="I11" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="L11">
         <v>4</v>
@@ -1656,8 +1880,8 @@
       <c r="B12">
         <v>26</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>92</v>
+      <c r="C12" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D12">
         <v>61.3</v>
@@ -1689,8 +1913,8 @@
       <c r="B13">
         <v>29</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>90</v>
+      <c r="C13" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D13">
         <v>92</v>
@@ -1721,8 +1945,8 @@
       <c r="B14">
         <v>22</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>92</v>
+      <c r="C14" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D14">
         <v>67</v>
@@ -1753,8 +1977,8 @@
       <c r="B15">
         <v>26</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>92</v>
+      <c r="C15" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D15">
         <v>73.8</v>
@@ -1785,8 +2009,8 @@
       <c r="B16">
         <v>48</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>92</v>
+      <c r="C16" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D16">
         <v>59.8</v>
@@ -1817,8 +2041,8 @@
       <c r="B17">
         <v>33</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>90</v>
+      <c r="C17" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D17">
         <v>87.5</v>
@@ -1849,8 +2073,8 @@
       <c r="B18">
         <v>31</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>92</v>
+      <c r="C18" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D18">
         <v>80.5</v>
@@ -1881,8 +2105,8 @@
       <c r="B19">
         <v>38</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>90</v>
+      <c r="C19" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D19">
         <v>89.9</v>
@@ -1913,8 +2137,8 @@
       <c r="B20">
         <v>62</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>92</v>
+      <c r="C20" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D20">
         <v>60.7</v>
@@ -1945,8 +2169,8 @@
       <c r="B21">
         <v>21</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>90</v>
+      <c r="C21" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D21">
         <v>67.2</v>
@@ -1977,8 +2201,8 @@
       <c r="B22">
         <v>24</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>92</v>
+      <c r="C22" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D22">
         <v>63.5</v>
@@ -2003,8 +2227,8 @@
       <c r="B23">
         <v>21</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>90</v>
+      <c r="C23" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D23">
         <v>89.6</v>
@@ -2029,8 +2253,8 @@
       <c r="B24">
         <v>19</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>92</v>
+      <c r="C24" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D24">
         <v>56.5</v>
@@ -2055,8 +2279,8 @@
       <c r="B25">
         <v>40</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>92</v>
+      <c r="C25" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D25">
         <v>61.8</v>
@@ -2081,8 +2305,8 @@
       <c r="B26">
         <v>40</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>92</v>
+      <c r="C26" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D26">
         <v>61.5</v>
@@ -2107,8 +2331,8 @@
       <c r="B27">
         <v>32</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>90</v>
+      <c r="C27" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D27">
         <v>72.2</v>
@@ -2133,8 +2357,8 @@
       <c r="B28">
         <v>28</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>92</v>
+      <c r="C28" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D28">
         <v>61.9</v>
@@ -2159,8 +2383,8 @@
       <c r="B29">
         <v>25</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>90</v>
+      <c r="C29" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D29">
         <v>88</v>
@@ -2185,8 +2409,8 @@
       <c r="B30">
         <v>25</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>90</v>
+      <c r="C30" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D30">
         <v>79.5</v>
@@ -2211,8 +2435,8 @@
       <c r="B31">
         <v>21</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>92</v>
+      <c r="C31" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D31">
         <v>62.8</v>
@@ -2237,8 +2461,8 @@
       <c r="B32">
         <v>39</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>90</v>
+      <c r="C32" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D32">
         <v>74</v>
@@ -2263,8 +2487,8 @@
       <c r="B33">
         <v>52</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>90</v>
+      <c r="C33" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D33">
         <v>87.2</v>
@@ -2289,8 +2513,8 @@
       <c r="B34">
         <v>35</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>92</v>
+      <c r="C34" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D34">
         <v>62</v>
@@ -2315,8 +2539,8 @@
       <c r="B35">
         <v>48</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>90</v>
+      <c r="C35" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D35">
         <v>89.4</v>
@@ -2341,8 +2565,8 @@
       <c r="B36">
         <v>63</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>92</v>
+      <c r="C36" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D36">
         <v>60.2</v>
@@ -2367,8 +2591,8 @@
       <c r="B37">
         <v>58</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>92</v>
+      <c r="C37" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D37">
         <v>73</v>
@@ -2393,8 +2617,8 @@
       <c r="B38">
         <v>50</v>
       </c>
-      <c r="C38" s="8" t="s">
-        <v>92</v>
+      <c r="C38" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D38">
         <v>68</v>
@@ -2419,8 +2643,8 @@
       <c r="B39">
         <v>46</v>
       </c>
-      <c r="C39" s="8" t="s">
-        <v>92</v>
+      <c r="C39" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D39">
         <v>76</v>
@@ -2445,8 +2669,8 @@
       <c r="B40">
         <v>41</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>92</v>
+      <c r="C40" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D40">
         <v>60.5</v>
@@ -2471,8 +2695,8 @@
       <c r="B41">
         <v>43</v>
       </c>
-      <c r="C41" s="8" t="s">
-        <v>90</v>
+      <c r="C41" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D41">
         <v>95</v>
@@ -2497,8 +2721,8 @@
       <c r="B42">
         <v>30</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>92</v>
+      <c r="C42" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D42">
         <v>58</v>
@@ -2523,8 +2747,8 @@
       <c r="B43">
         <v>64</v>
       </c>
-      <c r="C43" s="8" t="s">
-        <v>92</v>
+      <c r="C43" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D43">
         <v>51.5</v>
@@ -2549,8 +2773,8 @@
       <c r="B44">
         <v>51</v>
       </c>
-      <c r="C44" s="8" t="s">
-        <v>90</v>
+      <c r="C44" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D44">
         <v>65.5</v>
@@ -2575,8 +2799,8 @@
       <c r="B45">
         <v>24</v>
       </c>
-      <c r="C45" s="8" t="s">
-        <v>90</v>
+      <c r="C45" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D45">
         <v>86</v>
@@ -2601,8 +2825,8 @@
       <c r="B46">
         <v>26</v>
       </c>
-      <c r="C46" s="8" t="s">
-        <v>90</v>
+      <c r="C46" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D46">
         <v>50.8</v>
@@ -2627,8 +2851,8 @@
       <c r="B47">
         <v>38</v>
       </c>
-      <c r="C47" s="8" t="s">
-        <v>90</v>
+      <c r="C47" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D47">
         <v>81.5</v>
@@ -2653,8 +2877,8 @@
       <c r="B48">
         <v>42</v>
       </c>
-      <c r="C48" s="8" t="s">
-        <v>90</v>
+      <c r="C48" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D48">
         <v>66.099999999999994</v>
@@ -2679,8 +2903,8 @@
       <c r="B49">
         <v>31</v>
       </c>
-      <c r="C49" s="8" t="s">
-        <v>90</v>
+      <c r="C49" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D49">
         <v>74.8</v>
@@ -2705,8 +2929,8 @@
       <c r="B50">
         <v>67</v>
       </c>
-      <c r="C50" s="8" t="s">
-        <v>90</v>
+      <c r="C50" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D50">
         <v>98</v>
@@ -2731,8 +2955,8 @@
       <c r="B51">
         <v>21</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>90</v>
+      <c r="C51" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="D51">
         <v>74</v>
@@ -2751,7 +2975,7 @@
       </c>
     </row>
     <row r="52" spans="1:16">
-      <c r="H52" s="9">
+      <c r="H52" s="8">
         <f>SUM(H2:H51)</f>
         <v>696</v>
       </c>
@@ -2762,7 +2986,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
@@ -2777,37 +3001,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" t="s">
         <v>81</v>
       </c>
-      <c r="E1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H1" t="s">
-        <v>93</v>
-      </c>
       <c r="I1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="J1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="K1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="L1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -2818,7 +3042,7 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D2">
         <v>74</v>
@@ -2833,7 +3057,7 @@
         <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="L2">
         <v>17</v>
@@ -2847,7 +3071,7 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D3">
         <v>72</v>
@@ -2876,7 +3100,7 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D4">
         <v>80</v>
@@ -2905,7 +3129,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D5">
         <v>60</v>
@@ -2920,7 +3144,7 @@
         <v>17</v>
       </c>
       <c r="J5" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2931,7 +3155,7 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D6">
         <v>71</v>
@@ -2954,7 +3178,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D7">
         <v>65</v>
@@ -2977,7 +3201,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D8">
         <v>72</v>
@@ -3000,7 +3224,7 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D9">
         <v>85</v>
@@ -3023,7 +3247,7 @@
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D10">
         <v>76</v>
@@ -3046,7 +3270,7 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D11">
         <v>80</v>
@@ -3072,7 +3296,7 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D12">
         <v>75</v>
@@ -3087,7 +3311,7 @@
         <v>27</v>
       </c>
       <c r="J12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -3098,7 +3322,7 @@
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D13">
         <v>80</v>
@@ -3121,7 +3345,7 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D14">
         <v>58</v>
@@ -3137,7 +3361,7 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="H15" s="9">
+      <c r="H15" s="8">
         <f>SUM(H1:H14)</f>
         <v>302</v>
       </c>
@@ -3148,7 +3372,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P21"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
@@ -3158,40 +3382,40 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E1" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="G1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="H1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="I1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="J1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="K1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="L1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="P1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -3202,7 +3426,7 @@
         <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D2">
         <v>57.5</v>
@@ -3219,7 +3443,7 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D3">
         <v>66.5</v>
@@ -3236,7 +3460,7 @@
         <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D4">
         <v>108.7</v>
@@ -3253,7 +3477,7 @@
         <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D5">
         <v>62.8</v>
@@ -3270,7 +3494,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D6">
         <v>61</v>
@@ -3296,7 +3520,7 @@
         <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D7">
         <v>71.8</v>
@@ -3322,7 +3546,7 @@
         <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D8">
         <v>100.5</v>
@@ -3348,7 +3572,7 @@
         <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D9">
         <v>60.7</v>
@@ -3374,7 +3598,7 @@
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D10">
         <v>71</v>
@@ -3391,7 +3615,7 @@
         <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D11">
         <v>67.5</v>
@@ -3408,7 +3632,7 @@
         <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D12">
         <v>94</v>
@@ -3425,7 +3649,7 @@
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D13">
         <v>54</v>
@@ -3442,7 +3666,7 @@
         <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D14">
         <v>67.900000000000006</v>
@@ -3462,7 +3686,7 @@
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D15">
         <v>98</v>
@@ -3482,7 +3706,7 @@
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D16">
         <v>61.9</v>
@@ -3502,7 +3726,7 @@
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D17">
         <v>64.7</v>
@@ -3522,7 +3746,7 @@
         <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D18">
         <v>85.5</v>
@@ -3539,7 +3763,7 @@
         <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D19">
         <v>67</v>
@@ -3556,7 +3780,7 @@
         <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D20">
         <v>74.599999999999994</v>
@@ -3573,7 +3797,7 @@
         <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D21">
         <v>82.1</v>
@@ -3588,7 +3812,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P58"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
@@ -3602,40 +3826,40 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E1" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="G1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="H1" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="J1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="K1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="L1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="P1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -3646,7 +3870,7 @@
         <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D2">
         <v>81.349999999999994</v>
@@ -3672,7 +3896,7 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D3">
         <v>58.1</v>
@@ -3698,7 +3922,7 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D4">
         <v>80.900000000000006</v>
@@ -3724,7 +3948,7 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D5">
         <v>67.599999999999994</v>
@@ -3747,7 +3971,7 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D6">
         <v>82</v>
@@ -3770,7 +3994,7 @@
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D7">
         <v>58.8</v>
@@ -3793,7 +4017,7 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D8">
         <v>59</v>
@@ -3816,7 +4040,7 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D9">
         <v>56.1</v>
@@ -3839,7 +4063,7 @@
         <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D10">
         <v>52.1</v>
@@ -3862,7 +4086,7 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D11">
         <v>71</v>
@@ -3885,7 +4109,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D12">
         <v>53.15</v>
@@ -3908,7 +4132,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D13">
         <v>65.150000000000006</v>
@@ -3927,32 +4151,32 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <v>25</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" s="10">
+      <c r="C14" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="9">
         <v>79.95</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>1.83</v>
       </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10">
-        <v>1</v>
-      </c>
-      <c r="H14" s="10">
+      <c r="F14" s="9"/>
+      <c r="G14" s="9">
+        <v>1</v>
+      </c>
+      <c r="H14" s="9">
         <v>22</v>
       </c>
-      <c r="I14" s="10" t="s">
-        <v>98</v>
+      <c r="I14" s="9" t="s">
+        <v>86</v>
       </c>
       <c r="K14">
         <v>4</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="9">
         <v>18</v>
       </c>
     </row>
@@ -3960,26 +4184,26 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <v>23</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" s="10">
+      <c r="C15" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="9">
         <v>54.8</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="9">
         <v>1.64</v>
       </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10">
-        <v>1</v>
-      </c>
-      <c r="H15" s="10">
+      <c r="F15" s="9"/>
+      <c r="G15" s="9">
+        <v>1</v>
+      </c>
+      <c r="H15" s="9">
         <v>21</v>
       </c>
-      <c r="I15" s="10"/>
+      <c r="I15" s="9"/>
       <c r="L15">
         <v>21</v>
       </c>
@@ -3988,26 +4212,26 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <v>21</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" s="10">
+      <c r="C16" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="9">
         <v>76.5</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="9">
         <v>1.82</v>
       </c>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10">
-        <v>1</v>
-      </c>
-      <c r="H16" s="10">
+      <c r="F16" s="9"/>
+      <c r="G16" s="9">
+        <v>1</v>
+      </c>
+      <c r="H16" s="9">
         <v>21</v>
       </c>
-      <c r="I16" s="10"/>
+      <c r="I16" s="9"/>
       <c r="L16">
         <v>21</v>
       </c>
@@ -4016,32 +4240,32 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <v>22</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" s="10">
+      <c r="C17" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="9">
         <v>74.599999999999994</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <v>1.82</v>
       </c>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10">
-        <v>1</v>
-      </c>
-      <c r="H17" s="10">
+      <c r="F17" s="9"/>
+      <c r="G17" s="9">
+        <v>1</v>
+      </c>
+      <c r="H17" s="9">
         <v>21</v>
       </c>
-      <c r="I17" s="10" t="s">
-        <v>99</v>
+      <c r="I17" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="K17">
         <v>2</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L17" s="9">
         <v>19</v>
       </c>
     </row>
@@ -4049,26 +4273,26 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <v>20</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D18" s="10">
+      <c r="C18" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="9">
         <v>56.45</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <v>1.65</v>
       </c>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10">
-        <v>1</v>
-      </c>
-      <c r="H18" s="10">
+      <c r="F18" s="9"/>
+      <c r="G18" s="9">
+        <v>1</v>
+      </c>
+      <c r="H18" s="9">
         <v>20</v>
       </c>
-      <c r="I18" s="10"/>
+      <c r="I18" s="9"/>
       <c r="L18">
         <v>20</v>
       </c>
@@ -4077,32 +4301,32 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <v>22</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="10">
+      <c r="C19" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="9">
         <v>78.3</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="9">
         <v>1.88</v>
       </c>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10">
-        <v>1</v>
-      </c>
-      <c r="H19" s="10">
+      <c r="F19" s="9"/>
+      <c r="G19" s="9">
+        <v>1</v>
+      </c>
+      <c r="H19" s="9">
         <v>21</v>
       </c>
-      <c r="I19" s="10" t="s">
-        <v>100</v>
+      <c r="I19" s="9" t="s">
+        <v>88</v>
       </c>
       <c r="K19">
         <v>21</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="9">
         <v>0</v>
       </c>
     </row>
@@ -4110,26 +4334,26 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="9">
         <v>22</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" s="10">
+      <c r="C20" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="9">
         <v>90.8</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="9">
         <v>1.92</v>
       </c>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10">
-        <v>1</v>
-      </c>
-      <c r="H20" s="10">
+      <c r="F20" s="9"/>
+      <c r="G20" s="9">
+        <v>1</v>
+      </c>
+      <c r="H20" s="9">
         <v>20</v>
       </c>
-      <c r="I20" s="10"/>
+      <c r="I20" s="9"/>
       <c r="L20">
         <v>20</v>
       </c>
@@ -4138,27 +4362,27 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <v>24</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" s="10">
+      <c r="C21" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="9">
         <v>72.2</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="9">
         <v>1.86</v>
       </c>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10">
-        <v>1</v>
-      </c>
-      <c r="H21" s="10">
+      <c r="F21" s="9"/>
+      <c r="G21" s="9">
+        <v>1</v>
+      </c>
+      <c r="H21" s="9">
         <v>20</v>
       </c>
-      <c r="I21" s="10"/>
-      <c r="L21" s="10">
+      <c r="I21" s="9"/>
+      <c r="L21" s="9">
         <v>20</v>
       </c>
     </row>
@@ -4166,26 +4390,26 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <v>22</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" s="10">
+      <c r="C22" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="9">
         <v>81.8</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="9">
         <v>1.87</v>
       </c>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10">
-        <v>1</v>
-      </c>
-      <c r="H22" s="10">
+      <c r="F22" s="9"/>
+      <c r="G22" s="9">
+        <v>1</v>
+      </c>
+      <c r="H22" s="9">
         <v>21</v>
       </c>
-      <c r="I22" s="10"/>
+      <c r="I22" s="9"/>
       <c r="L22">
         <v>21</v>
       </c>
@@ -4194,27 +4418,27 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="9">
         <v>21</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" s="10">
+      <c r="C23" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="9">
         <v>61.8</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="9">
         <v>1.67</v>
       </c>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10">
-        <v>1</v>
-      </c>
-      <c r="H23" s="10">
+      <c r="F23" s="9"/>
+      <c r="G23" s="9">
+        <v>1</v>
+      </c>
+      <c r="H23" s="9">
         <v>21</v>
       </c>
-      <c r="I23" s="10"/>
-      <c r="L23" s="10">
+      <c r="I23" s="9"/>
+      <c r="L23" s="9">
         <v>21</v>
       </c>
     </row>
@@ -4222,32 +4446,32 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="9">
         <v>30</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" s="10">
+      <c r="C24" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="9">
         <v>55.75</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="9">
         <v>1.61</v>
       </c>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10">
-        <v>1</v>
-      </c>
-      <c r="H24" s="10">
+      <c r="F24" s="9"/>
+      <c r="G24" s="9">
+        <v>1</v>
+      </c>
+      <c r="H24" s="9">
         <v>20</v>
       </c>
-      <c r="I24" s="10" t="s">
-        <v>101</v>
+      <c r="I24" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="K24">
         <v>20</v>
       </c>
-      <c r="L24" s="10">
+      <c r="L24" s="9">
         <v>0</v>
       </c>
     </row>
@@ -4255,16 +4479,16 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="9">
         <v>20</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" s="10">
+      <c r="C25" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="9">
         <v>69.75</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="9">
         <v>1.71</v>
       </c>
       <c r="G25">
@@ -4274,12 +4498,12 @@
         <v>23</v>
       </c>
       <c r="I25" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K25">
         <v>3</v>
       </c>
-      <c r="L25" s="10">
+      <c r="L25" s="9">
         <v>20</v>
       </c>
     </row>
@@ -4287,16 +4511,16 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="9">
         <v>22</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D26" s="10">
+      <c r="C26" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="9">
         <v>66.150000000000006</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="9">
         <v>1.7</v>
       </c>
       <c r="G26">
@@ -4306,12 +4530,12 @@
         <v>23</v>
       </c>
       <c r="I26" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K26">
         <v>3</v>
       </c>
-      <c r="L26" s="10">
+      <c r="L26" s="9">
         <v>20</v>
       </c>
     </row>
@@ -4319,16 +4543,16 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="9">
         <v>23</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D27" s="10">
+      <c r="C27" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="9">
         <v>73.349999999999994</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="9">
         <v>1.86</v>
       </c>
       <c r="G27">
@@ -4338,12 +4562,12 @@
         <v>22</v>
       </c>
       <c r="I27" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K27">
         <v>22</v>
       </c>
-      <c r="L27" s="10">
+      <c r="L27" s="9">
         <v>0</v>
       </c>
     </row>
@@ -4351,16 +4575,16 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="9">
         <v>22</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28" s="10">
+      <c r="C28" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="9">
         <v>71.75</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="9">
         <v>1.79</v>
       </c>
       <c r="G28">
@@ -4370,12 +4594,12 @@
         <v>22</v>
       </c>
       <c r="I28" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K28">
         <v>2</v>
       </c>
-      <c r="L28" s="10">
+      <c r="L28" s="9">
         <v>20</v>
       </c>
     </row>
@@ -4383,16 +4607,16 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="9">
         <v>19</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29" s="10">
+      <c r="C29" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" s="9">
         <v>77.75</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="9">
         <v>1.85</v>
       </c>
       <c r="G29">
@@ -4402,12 +4626,12 @@
         <v>21</v>
       </c>
       <c r="I29" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K29">
         <v>21</v>
       </c>
-      <c r="L29" s="10">
+      <c r="L29" s="9">
         <v>0</v>
       </c>
     </row>
@@ -4415,16 +4639,16 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="9">
         <v>29</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D30" s="10">
+      <c r="C30" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" s="9">
         <v>68.900000000000006</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="9">
         <v>1.75</v>
       </c>
       <c r="G30">
@@ -4436,7 +4660,7 @@
       <c r="K30">
         <v>0</v>
       </c>
-      <c r="L30" s="10">
+      <c r="L30" s="9">
         <v>20</v>
       </c>
     </row>
@@ -4444,16 +4668,16 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="9">
         <v>21</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31" s="10">
+      <c r="C31" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="9">
         <v>64.900000000000006</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="9">
         <v>1.81</v>
       </c>
       <c r="G31">
@@ -4465,7 +4689,7 @@
       <c r="K31">
         <v>0</v>
       </c>
-      <c r="L31" s="10">
+      <c r="L31" s="9">
         <v>18</v>
       </c>
     </row>
@@ -4473,16 +4697,16 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="9">
         <v>21</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" s="10">
+      <c r="C32" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" s="9">
         <v>80.8</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="9">
         <v>1.84</v>
       </c>
       <c r="G32">
@@ -4492,12 +4716,12 @@
         <v>20</v>
       </c>
       <c r="I32" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K32">
         <v>20</v>
       </c>
-      <c r="L32" s="10">
+      <c r="L32" s="9">
         <v>0</v>
       </c>
     </row>
@@ -4505,16 +4729,16 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="9">
         <v>23</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D33" s="10">
+      <c r="C33" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" s="9">
         <v>82.7</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="9">
         <v>1.82</v>
       </c>
       <c r="G33">
@@ -4524,12 +4748,12 @@
         <v>20</v>
       </c>
       <c r="I33" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K33">
         <v>20</v>
       </c>
-      <c r="L33" s="10">
+      <c r="L33" s="9">
         <v>0</v>
       </c>
     </row>
@@ -4537,16 +4761,16 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="9">
         <v>26</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D34" s="10">
+      <c r="C34" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" s="9">
         <v>54.9</v>
       </c>
-      <c r="E34" s="10">
+      <c r="E34" s="9">
         <v>1.63</v>
       </c>
       <c r="G34">
@@ -4556,23 +4780,23 @@
         <v>24</v>
       </c>
       <c r="K34" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="9">
         <v>21</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D35" s="10">
+      <c r="C35" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D35" s="9">
         <v>77.3</v>
       </c>
-      <c r="E35" s="10">
+      <c r="E35" s="9">
         <v>1.79</v>
       </c>
       <c r="G35">
@@ -4582,12 +4806,12 @@
         <v>22</v>
       </c>
       <c r="I35" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K35">
         <v>4</v>
       </c>
-      <c r="L35" s="10">
+      <c r="L35" s="9">
         <v>18</v>
       </c>
     </row>
@@ -4595,16 +4819,16 @@
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="9">
         <v>24</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D36" s="10">
+      <c r="C36" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" s="9">
         <v>94.2</v>
       </c>
-      <c r="E36" s="10">
+      <c r="E36" s="9">
         <v>1.91</v>
       </c>
     </row>
@@ -4612,16 +4836,16 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="9">
         <v>23</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D37" s="10">
+      <c r="C37" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" s="9">
         <v>69.5</v>
       </c>
-      <c r="E37" s="10">
+      <c r="E37" s="9">
         <v>1.88</v>
       </c>
     </row>
@@ -4629,16 +4853,16 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="9">
         <v>26</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D38" s="10">
+      <c r="C38" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D38" s="9">
         <v>72</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E38" s="9">
         <v>1.84</v>
       </c>
     </row>
@@ -4646,16 +4870,16 @@
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="9">
         <v>20</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D39" s="10">
+      <c r="C39" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39" s="9">
         <v>52.3</v>
       </c>
-      <c r="E39" s="10">
+      <c r="E39" s="9">
         <v>1.58</v>
       </c>
     </row>
@@ -4663,16 +4887,16 @@
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="9">
         <v>25</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D40" s="10">
+      <c r="C40" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D40" s="9">
         <v>60.4</v>
       </c>
-      <c r="E40" s="10">
+      <c r="E40" s="9">
         <v>1.68</v>
       </c>
     </row>
@@ -4680,16 +4904,16 @@
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="9">
         <v>23</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D41" s="10">
+      <c r="C41" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D41" s="9">
         <v>55</v>
       </c>
-      <c r="E41" s="10">
+      <c r="E41" s="9">
         <v>1.64</v>
       </c>
     </row>
@@ -4697,16 +4921,16 @@
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="9">
         <v>21</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D42" s="10">
+      <c r="C42" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D42" s="9">
         <v>69.7</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E42" s="9">
         <v>1.69</v>
       </c>
     </row>
@@ -4714,16 +4938,16 @@
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="9">
         <v>26</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D43" s="10">
+      <c r="C43" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="9">
         <v>59.3</v>
       </c>
-      <c r="E43" s="10">
+      <c r="E43" s="9">
         <v>1.69</v>
       </c>
     </row>
@@ -4731,16 +4955,16 @@
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="9">
         <v>25</v>
       </c>
-      <c r="C44" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D44" s="10">
+      <c r="C44" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" s="9">
         <v>54.5</v>
       </c>
-      <c r="E44" s="10">
+      <c r="E44" s="9">
         <v>1.67</v>
       </c>
     </row>
@@ -4748,16 +4972,16 @@
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B45" s="9">
         <v>23</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D45" s="10">
+      <c r="C45" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D45" s="9">
         <v>57.4</v>
       </c>
-      <c r="E45" s="10">
+      <c r="E45" s="9">
         <v>1.75</v>
       </c>
     </row>
@@ -4765,16 +4989,16 @@
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="9">
         <v>27</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D46" s="10">
+      <c r="C46" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D46" s="9">
         <v>47.3</v>
       </c>
-      <c r="E46" s="10">
+      <c r="E46" s="9">
         <v>1.6</v>
       </c>
     </row>
@@ -4786,7 +5010,7 @@
         <v>22</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D47">
         <v>61.4</v>
@@ -4803,7 +5027,7 @@
         <v>21</v>
       </c>
       <c r="C48" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D48">
         <v>82.3</v>
@@ -4820,7 +5044,7 @@
         <v>19</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D49">
         <v>65.599999999999994</v>
@@ -4837,7 +5061,7 @@
         <v>22</v>
       </c>
       <c r="C50" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D50">
         <v>56.7</v>
@@ -4854,7 +5078,7 @@
         <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D51">
         <v>56</v>
@@ -4871,7 +5095,7 @@
         <v>21</v>
       </c>
       <c r="C52" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D52">
         <v>69.099999999999994</v>
@@ -4888,7 +5112,7 @@
         <v>22</v>
       </c>
       <c r="C53" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D53">
         <v>62.1</v>
@@ -4905,7 +5129,7 @@
         <v>30</v>
       </c>
       <c r="C54" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D54">
         <v>80.7</v>
@@ -4922,7 +5146,7 @@
         <v>21</v>
       </c>
       <c r="C55" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D55">
         <v>91.2</v>
@@ -4939,7 +5163,7 @@
         <v>21</v>
       </c>
       <c r="C56" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D56">
         <v>69.5</v>
@@ -4956,7 +5180,7 @@
         <v>24</v>
       </c>
       <c r="C57" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D57">
         <v>67.5</v>
@@ -4973,7 +5197,7 @@
         <v>22</v>
       </c>
       <c r="C58" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D58">
         <v>62.1</v>
@@ -4988,7 +5212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:P52"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
@@ -5003,41 +5227,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>80</v>
+      <c r="A1" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="D1" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E1" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="G1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="H1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="I1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="J1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="K1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="L1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="P1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -5048,7 +5272,7 @@
         <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D2">
         <v>75.527861547542898</v>
@@ -5069,7 +5293,7 @@
         <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D3">
         <v>75.216410190148395</v>
@@ -5089,7 +5313,7 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D4">
         <v>90.178596065609895</v>
@@ -5109,7 +5333,7 @@
         <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D5">
         <v>68.752980738810905</v>
@@ -5129,7 +5353,7 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D6">
         <v>95.030180507290396</v>
@@ -5149,7 +5373,7 @@
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D7">
         <v>70.554727693756206</v>
@@ -5169,7 +5393,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D8">
         <v>90.784376337728006</v>
@@ -5189,7 +5413,7 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D9">
         <v>75.6063604141372</v>
@@ -5209,7 +5433,7 @@
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D10">
         <v>76.357363880860305</v>
@@ -5229,7 +5453,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D11">
         <v>57.273416314576401</v>
@@ -5249,7 +5473,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D12">
         <v>68.838643739611896</v>
@@ -5269,7 +5493,7 @@
         <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D13">
         <v>89.765031280522606</v>
@@ -5289,7 +5513,7 @@
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D14">
         <v>73.154918953797207</v>
@@ -5309,7 +5533,7 @@
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D15">
         <v>94.315477454296001</v>
@@ -5329,7 +5553,7 @@
         <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D16">
         <v>62.864201055909199</v>
@@ -5349,7 +5573,7 @@
         <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D17">
         <v>70.474324955046299</v>
@@ -5369,7 +5593,7 @@
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D18">
         <v>81.187589890170202</v>
@@ -5389,7 +5613,7 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D19">
         <v>73.292966162861603</v>
@@ -5409,7 +5633,7 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D20">
         <v>63.2347601966772</v>
@@ -5429,7 +5653,7 @@
         <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D21">
         <v>73.268840066888799</v>
@@ -5449,7 +5673,7 @@
         <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D22">
         <v>58.029067769687003</v>
@@ -5469,7 +5693,7 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D23">
         <v>85.818703009347004</v>
@@ -5489,7 +5713,7 @@
         <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D24">
         <v>76.065091739440305</v>
@@ -5509,7 +5733,7 @@
         <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D25">
         <v>84.500624785972605</v>
@@ -5529,7 +5753,7 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D26">
         <v>80.189139537331101</v>
@@ -5549,7 +5773,7 @@
         <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D27">
         <v>81.482945334893799</v>
@@ -5569,7 +5793,7 @@
         <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D28">
         <v>62.231371023998598</v>
@@ -5589,7 +5813,7 @@
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D29">
         <v>103.593135418738</v>
@@ -5609,7 +5833,7 @@
         <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D30">
         <v>89.521141517738698</v>
@@ -5629,7 +5853,7 @@
         <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D31">
         <v>68.862616007902801</v>
@@ -5649,7 +5873,7 @@
         <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D32">
         <v>80.579689644200002</v>
@@ -5664,7 +5888,7 @@
         <v>40</v>
       </c>
       <c r="I32" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="K32">
         <v>40</v>
@@ -5681,7 +5905,7 @@
         <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D33">
         <v>68.146280219349904</v>
@@ -5696,7 +5920,7 @@
         <v>44</v>
       </c>
       <c r="I33" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="K33">
         <v>3</v>
@@ -5713,7 +5937,7 @@
         <v>28</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D34">
         <v>76.350187907485605</v>
@@ -5728,7 +5952,7 @@
         <v>41</v>
       </c>
       <c r="I34" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="K34">
         <v>41</v>
@@ -5745,7 +5969,7 @@
         <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D35">
         <v>75.240691431495094</v>
@@ -5760,7 +5984,7 @@
         <v>41</v>
       </c>
       <c r="I35" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="K35">
         <v>41</v>
@@ -5777,7 +6001,7 @@
         <v>33</v>
       </c>
       <c r="C36" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D36">
         <v>84.462231629890397</v>
@@ -5792,7 +6016,7 @@
         <v>40</v>
       </c>
       <c r="I36" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="K36">
         <v>40</v>
@@ -5809,7 +6033,7 @@
         <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D37">
         <v>54.140492711229903</v>
@@ -5824,7 +6048,7 @@
         <v>40</v>
       </c>
       <c r="I37" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="K37">
         <v>40</v>
@@ -5841,7 +6065,7 @@
         <v>28</v>
       </c>
       <c r="C38" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D38">
         <v>90.3777449015748</v>
@@ -5856,7 +6080,7 @@
         <v>43</v>
       </c>
       <c r="I38" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="K38">
         <v>43</v>
@@ -5873,7 +6097,7 @@
         <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D39">
         <v>76.818976821680806</v>
@@ -5888,7 +6112,7 @@
         <v>40</v>
       </c>
       <c r="I39" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="K39">
         <v>6</v>
@@ -5905,7 +6129,7 @@
         <v>21</v>
       </c>
       <c r="C40" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D40">
         <v>63.023042292533198</v>
@@ -5920,7 +6144,7 @@
         <v>44</v>
       </c>
       <c r="I40" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="K40">
         <v>7</v>
@@ -5937,7 +6161,7 @@
         <v>28</v>
       </c>
       <c r="C41" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D41">
         <v>136.13657014312699</v>
@@ -5952,7 +6176,7 @@
         <v>40</v>
       </c>
       <c r="I41" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="K41">
         <v>40</v>
@@ -5969,7 +6193,7 @@
         <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D42">
         <v>85.778406001692602</v>
@@ -5989,7 +6213,7 @@
         <v>20</v>
       </c>
       <c r="C43" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D43">
         <v>79.409803278182807</v>
@@ -6009,7 +6233,7 @@
         <v>37</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D44">
         <v>61.022674401557197</v>
@@ -6029,7 +6253,7 @@
         <v>21</v>
       </c>
       <c r="C45" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D45">
         <v>61.324277567479101</v>
@@ -6049,7 +6273,7 @@
         <v>26</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D46">
         <v>79.018618686461394</v>
@@ -6069,7 +6293,7 @@
         <v>28</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D47">
         <v>64.610276323420507</v>
@@ -6089,7 +6313,7 @@
         <v>30</v>
       </c>
       <c r="C48" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D48">
         <v>61.061758542644803</v>
@@ -6109,7 +6333,7 @@
         <v>36</v>
       </c>
       <c r="C49" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D49">
         <v>68.4202597262979</v>
@@ -6129,7 +6353,7 @@
         <v>68</v>
       </c>
       <c r="C50" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D50">
         <v>80.633207153808499</v>
@@ -6149,7 +6373,7 @@
         <v>34</v>
       </c>
       <c r="C51" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D51">
         <v>96.299047509172397</v>
@@ -6169,7 +6393,7 @@
         <v>25</v>
       </c>
       <c r="C52" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D52">
         <v>65.733442413113394</v>
@@ -6187,7 +6411,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
@@ -6201,37 +6425,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E1" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="G1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="H1" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="J1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="K1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="L1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -6239,16 +6463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -6262,16 +6486,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -6285,16 +6509,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -6308,16 +6532,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -6331,16 +6555,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -6354,16 +6578,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -6377,16 +6601,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -6403,16 +6627,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -6429,16 +6653,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -6452,16 +6676,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -6471,13 +6695,13 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="H12" s="9">
+      <c r="H12" s="8">
         <f>SUM(H2:H11)</f>
         <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="H13" s="9"/>
+      <c r="H13" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6485,7 +6709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L9"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
@@ -6499,37 +6723,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E1" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="G1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="H1" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="J1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="K1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="L1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -6537,10 +6761,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D2">
         <v>69.86</v>
@@ -6552,7 +6776,7 @@
         <v>3</v>
       </c>
       <c r="I2" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -6563,10 +6787,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D3">
         <v>66.680000000000007</v>
@@ -6578,7 +6802,7 @@
         <v>4</v>
       </c>
       <c r="I3" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="L3">
         <v>3</v>
@@ -6589,10 +6813,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D4">
         <v>53.07</v>
@@ -6604,7 +6828,7 @@
         <v>3</v>
       </c>
       <c r="I4" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -6612,10 +6836,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D5">
         <v>71.67</v>
@@ -6632,10 +6856,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D6">
         <v>90.7</v>
@@ -6652,10 +6876,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D7">
         <v>48.99</v>
@@ -6672,10 +6896,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D8">
         <v>63.96</v>
@@ -6688,7 +6912,7 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <f>SUM(H1:H8)</f>
         <v>18</v>
       </c>

--- a/data/database_inventory.xlsx
+++ b/data/database_inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21AEE1D-4466-4A9B-AB40-8E8220E4BAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362B3391-BBAD-4F49-8484-EFC254490785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -608,7 +608,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -627,7 +627,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1024,7 +1023,7 @@
       <c r="P2">
         <v>2</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="11" t="s">
         <v>106</v>
       </c>
       <c r="R2" s="4" t="s">
@@ -1074,7 +1073,7 @@
       <c r="P3">
         <v>2</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="Q3" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1121,15 +1120,15 @@
       <c r="P4">
         <v>1</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="R4" s="11" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="57.6">
-      <c r="A5" s="10">
+      <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1174,10 +1173,10 @@
       <c r="P5">
         <v>3</v>
       </c>
-      <c r="Q5" s="12" t="s">
+      <c r="Q5" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="R5" s="11" t="s">
+      <c r="R5" s="10" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1209,7 +1208,7 @@
       <c r="I6">
         <v>33</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="12" t="s">
         <v>128</v>
       </c>
       <c r="K6" t="s">
@@ -1227,10 +1226,10 @@
       <c r="P6" s="1">
         <v>3</v>
       </c>
-      <c r="Q6" s="12" t="s">
+      <c r="Q6" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="R6" s="11" t="s">
+      <c r="R6" s="10" t="s">
         <v>114</v>
       </c>
       <c r="S6" s="1"/>
